--- a/bridgeCalc.xlsx
+++ b/bridgeCalc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="28125"/>
   <workbookPr autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="-34720" yWindow="1520" windowWidth="30280" windowHeight="17960"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="fourCellsChart" sheetId="8" r:id="rId1"/>
@@ -113,10 +113,10 @@
     <t>In</t>
   </si>
   <si>
-    <t>Samle</t>
+    <t>Rate</t>
   </si>
   <si>
-    <t>Rate</t>
+    <t>Sample</t>
   </si>
 </sst>
 </file>
@@ -1513,11 +1513,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-2114874280"/>
-        <c:axId val="-2114905800"/>
+        <c:axId val="2103905384"/>
+        <c:axId val="2103908440"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-2114874280"/>
+        <c:axId val="2103905384"/>
         <c:scaling>
           <c:logBase val="10.0"/>
           <c:orientation val="minMax"/>
@@ -1532,14 +1532,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2114905800"/>
+        <c:crossAx val="2103908440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10.0"/>
         <c:minorUnit val="10.0"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-2114905800"/>
+        <c:axId val="2103908440"/>
         <c:scaling>
           <c:logBase val="10.0"/>
           <c:orientation val="minMax"/>
@@ -1554,7 +1554,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2114874280"/>
+        <c:crossAx val="2103905384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10.0"/>
@@ -1585,7 +1585,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9211623" cy="5616039"/>
+    <xdr:ext cx="9214662" cy="5624286"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1"/>
@@ -1921,7 +1921,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>

--- a/bridgeCalc.xlsx
+++ b/bridgeCalc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="28125"/>
   <workbookPr autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16060" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16060"/>
   </bookViews>
   <sheets>
     <sheet name="fourCellsChart" sheetId="8" r:id="rId1"/>
@@ -256,623 +256,602 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:v>Samples per Cell</c:v>
-          </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>fourCells!$B$5:$B$104</c:f>
+              <c:f>fourCells!$B$5:$B$101</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.72267222010323</c:v>
+                  <c:v>10.74607828321317</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.49756995397736</c:v>
+                  <c:v>11.54781984689458</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.32846739442066</c:v>
+                  <c:v>12.40937760751719</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13.2194114846603</c:v>
+                  <c:v>13.33521432163324</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.17474162926806</c:v>
+                  <c:v>14.33012570236962</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.19911082952935</c:v>
+                  <c:v>15.39926526059491</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>16.29750834620645</c:v>
+                  <c:v>16.5481709994318</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17.47528400007685</c:v>
+                  <c:v>17.78279410038921</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18.73817422860386</c:v>
+                  <c:v>19.10952974970439</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20.0923300256505</c:v>
+                  <c:v>20.53525026457144</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>21.54434690031886</c:v>
+                  <c:v>22.06734069084587</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>23.10129700083163</c:v>
+                  <c:v>23.71373705661653</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>24.77076355991714</c:v>
+                  <c:v>25.48296747979343</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>26.5608778294669</c:v>
+                  <c:v>27.38419634264358</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>28.48035868435806</c:v>
+                  <c:v>29.42727176209277</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>30.5385550883342</c:v>
+                  <c:v>31.62277660168375</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>32.74549162877734</c:v>
+                  <c:v>33.98208328942554</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>35.11191734215137</c:v>
+                  <c:v>36.51741272548371</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>37.64935806792474</c:v>
+                  <c:v>39.24189758484529</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>40.37017258596562</c:v>
+                  <c:v>42.16965034285814</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>43.28761281083067</c:v>
+                  <c:v>45.3158363760081</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46.41588833612787</c:v>
+                  <c:v>48.69675251658621</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>49.7702356433212</c:v>
+                  <c:v>52.32991146814936</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>53.36699231206321</c:v>
+                  <c:v>56.23413251903478</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>57.2236765935023</c:v>
+                  <c:v>60.42963902381315</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>61.35907273413187</c:v>
+                  <c:v>64.93816315762098</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>65.79332246575695</c:v>
+                  <c:v>69.78305848598645</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>70.54802310718661</c:v>
+                  <c:v>74.98942093324538</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>75.64633275546308</c:v>
+                  <c:v>80.58421877614796</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>81.11308307896893</c:v>
+                  <c:v>86.59643233600629</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>86.97490026177857</c:v>
+                  <c:v>93.05720409296963</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>93.26033468832224</c:v>
+                  <c:v>99.9999999999997</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>100.0000000000003</c:v>
+                  <c:v>107.4607828321314</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>107.2267222010326</c:v>
+                  <c:v>115.4781984689455</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>114.9756995397739</c:v>
+                  <c:v>124.0937760751715</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>123.284673944207</c:v>
+                  <c:v>133.352143216332</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>132.1941148466033</c:v>
+                  <c:v>143.3012570236958</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>141.747416292681</c:v>
+                  <c:v>153.9926526059486</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>151.9911082952939</c:v>
+                  <c:v>165.4817099943175</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>162.975083462065</c:v>
+                  <c:v>177.8279410038916</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>174.752840000769</c:v>
+                  <c:v>191.0952974970433</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>187.3817422860391</c:v>
+                  <c:v>205.3525026457138</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>200.9233002565055</c:v>
+                  <c:v>220.6734069084581</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>215.4434690031892</c:v>
+                  <c:v>237.1373705661646</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>231.0129700083169</c:v>
+                  <c:v>254.8296747979336</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>247.7076355991721</c:v>
+                  <c:v>273.841963426435</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>265.6087782946697</c:v>
+                  <c:v>294.272717620927</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>284.8035868435813</c:v>
+                  <c:v>316.2277660168365</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>305.3855508833428</c:v>
+                  <c:v>339.8208328942544</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>327.4549162877743</c:v>
+                  <c:v>365.174127254836</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>351.1191734215147</c:v>
+                  <c:v>392.4189758484517</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>376.4935806792485</c:v>
+                  <c:v>421.6965034285802</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>403.7017258596574</c:v>
+                  <c:v>453.1583637600796</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>432.8761281083079</c:v>
+                  <c:v>486.9675251658607</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>464.1588833612802</c:v>
+                  <c:v>523.299114681492</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>497.7023564332136</c:v>
+                  <c:v>562.3413251903462</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>533.6699231206337</c:v>
+                  <c:v>604.2963902381296</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>572.2367659350248</c:v>
+                  <c:v>649.3816315762078</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>613.5907273413206</c:v>
+                  <c:v>697.8305848598626</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>657.9332246575716</c:v>
+                  <c:v>749.8942093324517</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>705.4802310718682</c:v>
+                  <c:v>805.8421877614774</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>756.4633275546332</c:v>
+                  <c:v>865.9643233600604</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>811.1308307896917</c:v>
+                  <c:v>930.5720409296936</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>869.7490026177885</c:v>
+                  <c:v>999.9999999999942</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>932.6033468832255</c:v>
+                  <c:v>1074.607828321311</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1000.000000000006</c:v>
+                  <c:v>1154.781984689451</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1072.26722201033</c:v>
+                  <c:v>1240.937760751712</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1149.756995397743</c:v>
+                  <c:v>1333.521432163316</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1232.846739442074</c:v>
+                  <c:v>1433.012570236954</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1321.941148466038</c:v>
+                  <c:v>1539.926526059482</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>1417.474162926815</c:v>
+                  <c:v>1654.817099943171</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>1519.911082952944</c:v>
+                  <c:v>1778.279410038911</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>1629.750834620655</c:v>
+                  <c:v>1910.952974970428</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>1747.528400007696</c:v>
+                  <c:v>2053.525026457132</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>1873.817422860397</c:v>
+                  <c:v>2206.734069084575</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>2009.233002565061</c:v>
+                  <c:v>2371.37370566164</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>2154.4346900319</c:v>
+                  <c:v>2548.29674797933</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>2310.129700083176</c:v>
+                  <c:v>2738.419634264343</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>2477.07635599173</c:v>
+                  <c:v>2942.727176209261</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>2656.087782946706</c:v>
+                  <c:v>3162.277660168357</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>2848.035868435823</c:v>
+                  <c:v>3398.208328942535</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>3053.855508833438</c:v>
+                  <c:v>3651.741272548351</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>3274.549162877753</c:v>
+                  <c:v>3924.189758484507</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>3511.191734215158</c:v>
+                  <c:v>4216.96503428579</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>3764.935806792498</c:v>
+                  <c:v>4531.583637600784</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>4037.017258596587</c:v>
+                  <c:v>4869.675251658593</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>4328.761281083093</c:v>
+                  <c:v>5232.991146814906</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>4641.588833612816</c:v>
+                  <c:v>5623.413251903447</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>4977.023564332151</c:v>
+                  <c:v>6042.963902381281</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>5336.699231206353</c:v>
+                  <c:v>6493.816315762061</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>5722.367659350264</c:v>
+                  <c:v>6978.305848598606</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>6135.907273413224</c:v>
+                  <c:v>7498.942093324496</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>6579.332246575735</c:v>
+                  <c:v>8058.421877614751</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>7054.802310718704</c:v>
+                  <c:v>8659.64323360058</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>7564.633275546355</c:v>
+                  <c:v>9305.72040929691</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>8111.308307896942</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>8697.490026177911</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>9326.03346883228</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>10000.00000000009</c:v>
+                  <c:v>9999.999999999913</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>fourCells!$H$5:$H$104</c:f>
+              <c:f>fourCells!$H$5:$H$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>5512.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5140.0</c:v>
+                  <c:v>5129.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4794.0</c:v>
+                  <c:v>4773.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4471.0</c:v>
+                  <c:v>4442.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4170.0</c:v>
+                  <c:v>4133.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3888.0</c:v>
+                  <c:v>3846.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3626.0</c:v>
+                  <c:v>6443.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3382.0</c:v>
+                  <c:v>5996.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3154.0</c:v>
+                  <c:v>5579.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5295.0</c:v>
+                  <c:v>5192.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4938.0</c:v>
+                  <c:v>4831.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4605.0</c:v>
+                  <c:v>4496.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4295.0</c:v>
+                  <c:v>6043.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4005.0</c:v>
+                  <c:v>5624.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5396.0</c:v>
+                  <c:v>5233.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5032.0</c:v>
+                  <c:v>6369.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4693.0</c:v>
+                  <c:v>5926.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4376.0</c:v>
+                  <c:v>5515.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5337.0</c:v>
+                  <c:v>6340.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4978.0</c:v>
+                  <c:v>5899.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4642.0</c:v>
+                  <c:v>5490.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5348.0</c:v>
+                  <c:v>6082.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4988.0</c:v>
+                  <c:v>5660.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4651.0</c:v>
+                  <c:v>6109.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5164.0</c:v>
+                  <c:v>6469.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4816.0</c:v>
+                  <c:v>6020.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5210.0</c:v>
+                  <c:v>6281.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4859.0</c:v>
+                  <c:v>6477.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5157.0</c:v>
+                  <c:v>6027.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5392.0</c:v>
+                  <c:v>6156.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5029.0</c:v>
+                  <c:v>6238.0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5197.0</c:v>
+                  <c:v>6279.0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>5319.0</c:v>
+                  <c:v>6284.0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5402.0</c:v>
+                  <c:v>6258.0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5449.0</c:v>
+                  <c:v>6205.0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5465.0</c:v>
+                  <c:v>6130.0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5455.0</c:v>
+                  <c:v>6366.0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5421.0</c:v>
+                  <c:v>6231.0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5366.0</c:v>
+                  <c:v>6371.0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5295.0</c:v>
+                  <c:v>6462.0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5479.0</c:v>
+                  <c:v>6261.0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>5362.0</c:v>
+                  <c:v>6288.0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>5471.0</c:v>
+                  <c:v>6281.0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>5322.0</c:v>
+                  <c:v>6444.0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>5373.0</c:v>
+                  <c:v>6369.0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>5392.0</c:v>
+                  <c:v>6446.0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>5385.0</c:v>
+                  <c:v>6481.0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>5354.0</c:v>
+                  <c:v>6481.0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>5458.0</c:v>
+                  <c:v>6449.0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>5379.0</c:v>
+                  <c:v>6391.0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>5420.0</c:v>
+                  <c:v>6430.0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>5432.0</c:v>
+                  <c:v>6433.0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>5417.0</c:v>
+                  <c:v>6405.0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>5489.0</c:v>
+                  <c:v>6447.0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>5424.0</c:v>
+                  <c:v>6452.0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>5439.0</c:v>
+                  <c:v>6425.0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>5427.0</c:v>
+                  <c:v>6450.0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>5474.0</c:v>
+                  <c:v>6440.0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>5490.0</c:v>
+                  <c:v>6468.0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>5480.0</c:v>
+                  <c:v>6461.0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>5446.0</c:v>
+                  <c:v>6483.0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>5454.0</c:v>
+                  <c:v>6471.0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>5494.0</c:v>
+                  <c:v>6480.0</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>5504.0</c:v>
+                  <c:v>6456.0</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>5488.0</c:v>
+                  <c:v>6449.0</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>5497.0</c:v>
+                  <c:v>6453.0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>5479.0</c:v>
+                  <c:v>6463.0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>5480.0</c:v>
+                  <c:v>6476.0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>5494.0</c:v>
+                  <c:v>6456.0</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>5481.0</c:v>
+                  <c:v>6470.0</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>5479.0</c:v>
+                  <c:v>6479.0</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>5483.0</c:v>
+                  <c:v>6482.0</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>5491.0</c:v>
+                  <c:v>6478.0</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>5499.0</c:v>
+                  <c:v>6467.0</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>5507.0</c:v>
+                  <c:v>6469.0</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>5489.0</c:v>
+                  <c:v>6479.0</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>5492.0</c:v>
+                  <c:v>6476.0</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>5511.0</c:v>
+                  <c:v>6476.0</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>5502.0</c:v>
+                  <c:v>6477.0</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>5505.0</c:v>
+                  <c:v>6477.0</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>5499.0</c:v>
+                  <c:v>6474.0</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>5500.0</c:v>
+                  <c:v>6478.0</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>5505.0</c:v>
+                  <c:v>6475.0</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>5511.0</c:v>
+                  <c:v>6475.0</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>5504.0</c:v>
+                  <c:v>6475.0</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>5508.0</c:v>
+                  <c:v>6483.0</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>5508.0</c:v>
+                  <c:v>6477.0</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>5503.0</c:v>
+                  <c:v>6482.0</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>5503.0</c:v>
+                  <c:v>6479.0</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>5504.0</c:v>
+                  <c:v>6482.0</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>5505.0</c:v>
+                  <c:v>6480.0</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>5512.0</c:v>
+                  <c:v>6479.0</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>5507.0</c:v>
+                  <c:v>6482.0</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>5511.0</c:v>
+                  <c:v>6480.0</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>5508.0</c:v>
+                  <c:v>6484.0</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>5510.0</c:v>
+                  <c:v>6484.0</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>5508.0</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>5507.0</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>5510.0</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>5509.0</c:v>
+                  <c:v>6483.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -882,324 +861,312 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:v>Cycles in Four Cells</c:v>
-          </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>fourCells!$B$5:$B$104</c:f>
+              <c:f>fourCells!$B$5:$B$101</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.72267222010323</c:v>
+                  <c:v>10.74607828321317</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.49756995397736</c:v>
+                  <c:v>11.54781984689458</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.32846739442066</c:v>
+                  <c:v>12.40937760751719</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13.2194114846603</c:v>
+                  <c:v>13.33521432163324</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.17474162926806</c:v>
+                  <c:v>14.33012570236962</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.19911082952935</c:v>
+                  <c:v>15.39926526059491</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>16.29750834620645</c:v>
+                  <c:v>16.5481709994318</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17.47528400007685</c:v>
+                  <c:v>17.78279410038921</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18.73817422860386</c:v>
+                  <c:v>19.10952974970439</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20.0923300256505</c:v>
+                  <c:v>20.53525026457144</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>21.54434690031886</c:v>
+                  <c:v>22.06734069084587</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>23.10129700083163</c:v>
+                  <c:v>23.71373705661653</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>24.77076355991714</c:v>
+                  <c:v>25.48296747979343</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>26.5608778294669</c:v>
+                  <c:v>27.38419634264358</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>28.48035868435806</c:v>
+                  <c:v>29.42727176209277</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>30.5385550883342</c:v>
+                  <c:v>31.62277660168375</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>32.74549162877734</c:v>
+                  <c:v>33.98208328942554</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>35.11191734215137</c:v>
+                  <c:v>36.51741272548371</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>37.64935806792474</c:v>
+                  <c:v>39.24189758484529</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>40.37017258596562</c:v>
+                  <c:v>42.16965034285814</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>43.28761281083067</c:v>
+                  <c:v>45.3158363760081</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46.41588833612787</c:v>
+                  <c:v>48.69675251658621</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>49.7702356433212</c:v>
+                  <c:v>52.32991146814936</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>53.36699231206321</c:v>
+                  <c:v>56.23413251903478</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>57.2236765935023</c:v>
+                  <c:v>60.42963902381315</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>61.35907273413187</c:v>
+                  <c:v>64.93816315762098</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>65.79332246575695</c:v>
+                  <c:v>69.78305848598645</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>70.54802310718661</c:v>
+                  <c:v>74.98942093324538</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>75.64633275546308</c:v>
+                  <c:v>80.58421877614796</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>81.11308307896893</c:v>
+                  <c:v>86.59643233600629</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>86.97490026177857</c:v>
+                  <c:v>93.05720409296963</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>93.26033468832224</c:v>
+                  <c:v>99.9999999999997</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>100.0000000000003</c:v>
+                  <c:v>107.4607828321314</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>107.2267222010326</c:v>
+                  <c:v>115.4781984689455</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>114.9756995397739</c:v>
+                  <c:v>124.0937760751715</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>123.284673944207</c:v>
+                  <c:v>133.352143216332</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>132.1941148466033</c:v>
+                  <c:v>143.3012570236958</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>141.747416292681</c:v>
+                  <c:v>153.9926526059486</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>151.9911082952939</c:v>
+                  <c:v>165.4817099943175</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>162.975083462065</c:v>
+                  <c:v>177.8279410038916</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>174.752840000769</c:v>
+                  <c:v>191.0952974970433</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>187.3817422860391</c:v>
+                  <c:v>205.3525026457138</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>200.9233002565055</c:v>
+                  <c:v>220.6734069084581</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>215.4434690031892</c:v>
+                  <c:v>237.1373705661646</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>231.0129700083169</c:v>
+                  <c:v>254.8296747979336</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>247.7076355991721</c:v>
+                  <c:v>273.841963426435</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>265.6087782946697</c:v>
+                  <c:v>294.272717620927</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>284.8035868435813</c:v>
+                  <c:v>316.2277660168365</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>305.3855508833428</c:v>
+                  <c:v>339.8208328942544</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>327.4549162877743</c:v>
+                  <c:v>365.174127254836</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>351.1191734215147</c:v>
+                  <c:v>392.4189758484517</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>376.4935806792485</c:v>
+                  <c:v>421.6965034285802</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>403.7017258596574</c:v>
+                  <c:v>453.1583637600796</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>432.8761281083079</c:v>
+                  <c:v>486.9675251658607</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>464.1588833612802</c:v>
+                  <c:v>523.299114681492</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>497.7023564332136</c:v>
+                  <c:v>562.3413251903462</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>533.6699231206337</c:v>
+                  <c:v>604.2963902381296</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>572.2367659350248</c:v>
+                  <c:v>649.3816315762078</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>613.5907273413206</c:v>
+                  <c:v>697.8305848598626</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>657.9332246575716</c:v>
+                  <c:v>749.8942093324517</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>705.4802310718682</c:v>
+                  <c:v>805.8421877614774</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>756.4633275546332</c:v>
+                  <c:v>865.9643233600604</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>811.1308307896917</c:v>
+                  <c:v>930.5720409296936</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>869.7490026177885</c:v>
+                  <c:v>999.9999999999942</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>932.6033468832255</c:v>
+                  <c:v>1074.607828321311</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1000.000000000006</c:v>
+                  <c:v>1154.781984689451</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1072.26722201033</c:v>
+                  <c:v>1240.937760751712</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1149.756995397743</c:v>
+                  <c:v>1333.521432163316</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1232.846739442074</c:v>
+                  <c:v>1433.012570236954</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1321.941148466038</c:v>
+                  <c:v>1539.926526059482</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>1417.474162926815</c:v>
+                  <c:v>1654.817099943171</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>1519.911082952944</c:v>
+                  <c:v>1778.279410038911</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>1629.750834620655</c:v>
+                  <c:v>1910.952974970428</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>1747.528400007696</c:v>
+                  <c:v>2053.525026457132</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>1873.817422860397</c:v>
+                  <c:v>2206.734069084575</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>2009.233002565061</c:v>
+                  <c:v>2371.37370566164</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>2154.4346900319</c:v>
+                  <c:v>2548.29674797933</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>2310.129700083176</c:v>
+                  <c:v>2738.419634264343</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>2477.07635599173</c:v>
+                  <c:v>2942.727176209261</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>2656.087782946706</c:v>
+                  <c:v>3162.277660168357</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>2848.035868435823</c:v>
+                  <c:v>3398.208328942535</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>3053.855508833438</c:v>
+                  <c:v>3651.741272548351</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>3274.549162877753</c:v>
+                  <c:v>3924.189758484507</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>3511.191734215158</c:v>
+                  <c:v>4216.96503428579</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>3764.935806792498</c:v>
+                  <c:v>4531.583637600784</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>4037.017258596587</c:v>
+                  <c:v>4869.675251658593</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>4328.761281083093</c:v>
+                  <c:v>5232.991146814906</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>4641.588833612816</c:v>
+                  <c:v>5623.413251903447</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>4977.023564332151</c:v>
+                  <c:v>6042.963902381281</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>5336.699231206353</c:v>
+                  <c:v>6493.816315762061</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>5722.367659350264</c:v>
+                  <c:v>6978.305848598606</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>6135.907273413224</c:v>
+                  <c:v>7498.942093324496</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>6579.332246575735</c:v>
+                  <c:v>8058.421877614751</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>7054.802310718704</c:v>
+                  <c:v>8659.64323360058</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>7564.633275546355</c:v>
+                  <c:v>9305.72040929691</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>8111.308307896942</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>8697.490026177911</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>9326.03346883228</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>10000.00000000009</c:v>
+                  <c:v>9999.999999999913</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>fourCells!$K$5:$K$104</c:f>
+              <c:f>fourCells!$K$5:$K$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>5.0</c:v>
                 </c:pt>
@@ -1207,298 +1174,289 @@
                   <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.000000000000001</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.000000000000001</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.0</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.000000000000001</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.000000000000001</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.0</c:v>
+                  <c:v>9.000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.999999999999998</c:v>
+                  <c:v>9.000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.0</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.000000000000001</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>13.0</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>13.0</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>17.0</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>17</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>17.0</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>21.0</c:v>
+                  <c:v>25.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>21.0</c:v>
+                  <c:v>25.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>21.0</c:v>
+                  <c:v>29.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>25.0</c:v>
+                  <c:v>33.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>25.0</c:v>
+                  <c:v>33.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>29.0</c:v>
+                  <c:v>37.00000000000001</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>29.0</c:v>
+                  <c:v>41.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>33.0</c:v>
+                  <c:v>41.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>37.00000000000001</c:v>
+                  <c:v>45.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>37.00000000000001</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>41.0</c:v>
+                  <c:v>53.0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>45.0</c:v>
+                  <c:v>57.0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>49.0</c:v>
+                  <c:v>61.0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>53.0</c:v>
+                  <c:v>65.0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>57.0</c:v>
+                  <c:v>69.0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>61.0</c:v>
+                  <c:v>77.00000000000001</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>65.0</c:v>
+                  <c:v>81.0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>69.00000000000001</c:v>
+                  <c:v>89.0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>73.0</c:v>
+                  <c:v>97.0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>80.99999999999998</c:v>
+                  <c:v>101.0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>84.99999999999998</c:v>
+                  <c:v>109.0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>92.99999999999998</c:v>
+                  <c:v>117.0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>97.0</c:v>
+                  <c:v>129.0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>105.0</c:v>
+                  <c:v>137.0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>113</c:v>
+                  <c:v>149.0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>121.0</c:v>
+                  <c:v>161.0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>129</c:v>
+                  <c:v>173.0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>141</c:v>
+                  <c:v>185.0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>149.0</c:v>
+                  <c:v>197.0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>161</c:v>
+                  <c:v>213.0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>173</c:v>
+                  <c:v>229.0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>185.0</c:v>
+                  <c:v>245.0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>201.0</c:v>
+                  <c:v>265.0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>213.0</c:v>
+                  <c:v>285.0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>229.0</c:v>
+                  <c:v>305.0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>245.0</c:v>
+                  <c:v>329.0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>265.0</c:v>
+                  <c:v>352.9999999999999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>285.0</c:v>
+                  <c:v>381.0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>305.0</c:v>
+                  <c:v>409.0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>325.0</c:v>
+                  <c:v>441.0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>349.0</c:v>
+                  <c:v>472.9999999999999</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>377.0</c:v>
+                  <c:v>509.0</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>405.0</c:v>
+                  <c:v>545.0</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>433.0</c:v>
+                  <c:v>585.0</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>465.0</c:v>
+                  <c:v>629.0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>497.0</c:v>
+                  <c:v>677.0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>532.9999999999999</c:v>
+                  <c:v>728.9999999999999</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>573.0000000000001</c:v>
+                  <c:v>781.0</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>613.0000000000001</c:v>
+                  <c:v>841.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>656.9999999999999</c:v>
+                  <c:v>905.0</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>704.9999999999999</c:v>
+                  <c:v>973.0</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>757.0000000000001</c:v>
+                  <c:v>1045.0</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>813.0</c:v>
+                  <c:v>1121.0</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>873.0</c:v>
+                  <c:v>1205.0</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>933.0</c:v>
+                  <c:v>1297</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>1001.0</c:v>
+                  <c:v>1393.0</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>1077.0</c:v>
+                  <c:v>1497.0</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>1153.0</c:v>
+                  <c:v>1609.0</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>1237.0</c:v>
+                  <c:v>1729.0</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>1325.0</c:v>
+                  <c:v>1857.0</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>1421</c:v>
+                  <c:v>1997.0</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>1525.0</c:v>
+                  <c:v>2145.0</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>1637.0</c:v>
+                  <c:v>2305.0</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>1753.0</c:v>
+                  <c:v>2477.0</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>1881.0</c:v>
+                  <c:v>2665.0</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>2017.0</c:v>
+                  <c:v>2861.0</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2161</c:v>
+                  <c:v>3077.0</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>2317.0</c:v>
+                  <c:v>3305.0</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>2485.0</c:v>
+                  <c:v>3553.0</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>2665.0</c:v>
+                  <c:v>3817.0</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>2861</c:v>
+                  <c:v>4101.0</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>3065.0</c:v>
+                  <c:v>4409.0</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>3289.0</c:v>
+                  <c:v>4737.0</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>3525.0</c:v>
+                  <c:v>5093.0</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>3781.0</c:v>
+                  <c:v>5473</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>4053.0</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>4345.0</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>4661.0</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>4997.0</c:v>
+                  <c:v>5881.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1513,11 +1471,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2103905384"/>
-        <c:axId val="2103908440"/>
+        <c:axId val="2083455384"/>
+        <c:axId val="2116245992"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="2103905384"/>
+        <c:axId val="2083455384"/>
         <c:scaling>
           <c:logBase val="10.0"/>
           <c:orientation val="minMax"/>
@@ -1532,14 +1490,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2103908440"/>
+        <c:crossAx val="2116245992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10.0"/>
         <c:minorUnit val="10.0"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2103908440"/>
+        <c:axId val="2116245992"/>
         <c:scaling>
           <c:logBase val="10.0"/>
           <c:orientation val="minMax"/>
@@ -1554,7 +1512,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2103905384"/>
+        <c:crossAx val="2083455384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10.0"/>
@@ -1570,6 +1528,398 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="118"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="18"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>fourCells!$J$5:$J$101</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000%</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>9.07111756167644E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.000151759724111189</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.000131643101269896</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.61638980568946E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.000191586969553459</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.000205693978162946</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.59334649946819E-5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.18365806998744E-5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.000149094676688</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.38723858120893E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.000193597279710467</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.000103172688927122</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.000159711300705245</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.13391443755606E-5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.000163993670928342</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.44387691318748E-5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.000151688250184412</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.36917516328539E-5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.98830016675533E-5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.000160034880351434</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.88291499374893E-5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.10979800085742E-5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.00957111659872E-6</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.000130037522385606</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.000127541130642284</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.000106032204035378</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.00011865649230991</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.87865699625845E-5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.000141074122495644</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.78663953030701E-5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.7485859032157E-5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.22014394900094E-5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.9783577342245E-5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.26715024733448E-5</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.000115524944252821</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.96383113463461E-5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6.19173351767976E-6</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.000128643948779317</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.000140466870774292</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7.6860307052895E-5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.000129570567937831</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>9.80098451361933E-5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8.21284820544665E-5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.000144559122726262</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>6.42819769491876E-5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5.656546797006E-5</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.000143813038915308</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7.52508872696733E-5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.000133442800583028</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5.98845545880522E-5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.000108753908846904</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.000116354273618224</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.88291499405979E-5</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3.86884735996684E-5</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6.700616191746E-5</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.000127353690273946</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>3.4036136196125E-5</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4.01490662120807E-5</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7.72836852320768E-5</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.000120121811918006</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>9.47927215673161E-5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>4.22281273559921E-5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4.92180604145798E-5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.000141800255144542</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>9.69142502771358E-5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4.04767606143608E-5</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>7.6243576561108E-5</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.000113492515644742</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.000152236185313681</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4.67741244736253E-5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.42046234969684E-5</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>7.46335099228723E-5</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.000124220466765079</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>7.21881593479523E-5</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>6.56118054074284E-5</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.000139533216553467</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5.26718295414952E-5</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.000100301956092785</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.000139880739886022</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.000114432039177492</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4.10025429913308E-5</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.000151335814479792</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.000152262908965195</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.000137600696820117</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.000149292276242496</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.000114652052568331</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5.19451158049744E-5</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.000108383237034992</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>9.69021179195728E-5</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>3.40303298724809E-5</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5.9298432247612E-5</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2.39183473329518E-5</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2.22668674758619E-5</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.000131202990855117</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2.13409077522986E-5</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>2.54211063988041E-5</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.00012378528459922</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="2124536296"/>
+        <c:axId val="2125192216"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2124536296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2125192216"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2125192216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="0.0000%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2124536296"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="1.0" l="0.75" r="0.75" t="1.0" header="0.5" footer="0.5"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
@@ -1605,6 +1955,41 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>863600</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1921,7 +2306,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1929,7 +2314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.5" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="9.5" style="1"/>
@@ -2053,7 +2438,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <f t="shared" ref="D5:D36" si="0">INT((B5/2-1)/4)</f>
+        <f>INT((B5/1.7-1)/4)</f>
         <v>1</v>
       </c>
       <c r="E5" s="1">
@@ -2061,27 +2446,27 @@
         <v>5</v>
       </c>
       <c r="F5" s="4">
-        <f t="shared" ref="F5:F36" si="1">1/B5/4</f>
+        <f t="shared" ref="F5:F36" si="0">1/B5/4</f>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" ref="G5:G36" si="2">E5*F5</f>
+        <f t="shared" ref="G5:G36" si="1">E5*F5</f>
         <v>0.125</v>
       </c>
       <c r="H5" s="5">
-        <f t="shared" ref="H5:H36" si="3">INT(G5*_rate)</f>
+        <f t="shared" ref="H5:H36" si="2">INT(G5*_rate)</f>
         <v>5512</v>
       </c>
       <c r="I5" s="2">
-        <f t="shared" ref="I5:I36" si="4">E5/H5/4*_rate</f>
+        <f t="shared" ref="I5:I36" si="3">E5/H5/4*_rate</f>
         <v>10.000907111756169</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" ref="J5:J36" si="5">(I5/B5-1)</f>
+        <f t="shared" ref="J5:J36" si="4">(I5/B5-1)</f>
         <v>9.071117561676445E-5</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" ref="K5:K36" si="6">4*I5*H5/_rate</f>
+        <f t="shared" ref="K5:K36" si="5">4*I5*H5/_rate</f>
         <v>5</v>
       </c>
       <c r="L5" s="2">
@@ -2094,15 +2479,15 @@
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <f t="shared" ref="B6:B37" si="7">B5*_mult</f>
-        <v>10.722672220103233</v>
+        <f t="shared" ref="B6:B37" si="6">B5*_mult</f>
+        <v>10.746078283213174</v>
       </c>
       <c r="C6" s="1">
         <f>C5+1</f>
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D6:D69" si="7">INT((B6/1.7-1)/4)</f>
         <v>1</v>
       </c>
       <c r="E6" s="1">
@@ -2110,48 +2495,48 @@
         <v>5</v>
       </c>
       <c r="F6" s="4">
+        <f t="shared" si="0"/>
+        <v>2.3264301023242475E-2</v>
+      </c>
+      <c r="G6" s="4">
         <f t="shared" si="1"/>
-        <v>2.3315083672080496E-2</v>
-      </c>
-      <c r="G6" s="4">
+        <v>0.11632150511621238</v>
+      </c>
+      <c r="H6" s="5">
         <f t="shared" si="2"/>
-        <v>0.11657541836040247</v>
-      </c>
-      <c r="H6" s="5">
+        <v>5129</v>
+      </c>
+      <c r="I6" s="2">
         <f t="shared" si="3"/>
-        <v>5140</v>
-      </c>
-      <c r="I6" s="2">
+        <v>10.747709105088711</v>
+      </c>
+      <c r="J6" s="8">
         <f t="shared" si="4"/>
-        <v>10.724708171206226</v>
-      </c>
-      <c r="J6" s="8">
+        <v>1.5175972411118899E-4</v>
+      </c>
+      <c r="K6" s="1">
         <f t="shared" si="5"/>
-        <v>1.8987348127419423E-4</v>
-      </c>
-      <c r="K6" s="1">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="L6" s="2">
         <f t="shared" ref="L6:L69" si="9">4*H6/K6</f>
-        <v>4112</v>
+        <v>4103.2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2">
-        <f t="shared" si="7"/>
-        <v>11.49756995397736</v>
+        <f t="shared" si="6"/>
+        <v>11.54781984689458</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" ref="C7:C70" si="10">C6+1</f>
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E7" s="1">
@@ -2159,32 +2544,32 @@
         <v>5</v>
       </c>
       <c r="F7" s="4">
+        <f t="shared" si="0"/>
+        <v>2.1649108084001636E-2</v>
+      </c>
+      <c r="G7" s="4">
         <f t="shared" si="1"/>
-        <v>2.1743725065444579E-2</v>
-      </c>
-      <c r="G7" s="4">
+        <v>0.10824554042000818</v>
+      </c>
+      <c r="H7" s="5">
         <f t="shared" si="2"/>
-        <v>0.1087186253272229</v>
-      </c>
-      <c r="H7" s="5">
+        <v>4773</v>
+      </c>
+      <c r="I7" s="2">
         <f t="shared" si="3"/>
-        <v>4794</v>
-      </c>
-      <c r="I7" s="2">
+        <v>11.549340037712131</v>
+      </c>
+      <c r="J7" s="8">
         <f t="shared" si="4"/>
-        <v>11.498748435544432</v>
-      </c>
-      <c r="J7" s="8">
+        <v>1.3164310126989598E-4</v>
+      </c>
+      <c r="K7" s="1">
         <f t="shared" si="5"/>
-        <v>1.0249831675634979E-4</v>
-      </c>
-      <c r="K7" s="1">
-        <f t="shared" si="6"/>
-        <v>5.0000000000000009</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2">
         <f t="shared" si="9"/>
-        <v>3835.1999999999994</v>
+        <v>3818.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2192,15 +2577,15 @@
         <v>2</v>
       </c>
       <c r="B8" s="2">
-        <f t="shared" si="7"/>
-        <v>12.328467394420665</v>
+        <f t="shared" si="6"/>
+        <v>12.409377607517193</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E8" s="1">
@@ -2208,49 +2593,49 @@
         <v>5</v>
       </c>
       <c r="F8" s="4">
+        <f t="shared" si="0"/>
+        <v>2.014605469403705E-2</v>
+      </c>
+      <c r="G8" s="4">
         <f t="shared" si="1"/>
-        <v>2.027827076974217E-2</v>
-      </c>
-      <c r="G8" s="4">
+        <v>0.10073027347018525</v>
+      </c>
+      <c r="H8" s="5">
         <f t="shared" si="2"/>
-        <v>0.10139135384871086</v>
-      </c>
-      <c r="H8" s="5">
+        <v>4442</v>
+      </c>
+      <c r="I8" s="2">
         <f t="shared" si="3"/>
-        <v>4471</v>
-      </c>
-      <c r="I8" s="2">
+        <v>12.409950472760016</v>
+      </c>
+      <c r="J8" s="8">
         <f t="shared" si="4"/>
-        <v>12.32945649742787</v>
-      </c>
-      <c r="J8" s="8">
+        <v>4.6163898056894581E-5</v>
+      </c>
+      <c r="K8" s="1">
         <f t="shared" si="5"/>
-        <v>8.0229194397096748E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <f t="shared" si="6"/>
-        <v>5.0000000000000009</v>
+        <v>4.9999999999999991</v>
       </c>
       <c r="L8" s="2">
         <f t="shared" si="9"/>
-        <v>3576.7999999999993</v>
+        <v>3553.6000000000008</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="3">
         <f>EXP(LN(10)/A7)</f>
-        <v>1.0722672220103233</v>
+        <v>1.0746078283213174</v>
       </c>
       <c r="B9" s="2">
-        <f t="shared" si="7"/>
-        <v>13.219411484660295</v>
+        <f t="shared" si="6"/>
+        <v>13.335214321633236</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E9" s="1">
@@ -2258,45 +2643,45 @@
         <v>5</v>
       </c>
       <c r="F9" s="4">
+        <f t="shared" si="0"/>
+        <v>1.8747355233311402E-2</v>
+      </c>
+      <c r="G9" s="4">
         <f t="shared" si="1"/>
-        <v>1.8911583188865714E-2</v>
-      </c>
-      <c r="G9" s="4">
+        <v>9.3736776166557012E-2</v>
+      </c>
+      <c r="H9" s="5">
         <f t="shared" si="2"/>
-        <v>9.4557915944328566E-2</v>
-      </c>
-      <c r="H9" s="5">
+        <v>4133</v>
+      </c>
+      <c r="I9" s="2">
         <f t="shared" si="3"/>
-        <v>4170</v>
-      </c>
-      <c r="I9" s="2">
+        <v>13.337769174933463</v>
+      </c>
+      <c r="J9" s="8">
         <f t="shared" si="4"/>
-        <v>13.219424460431654</v>
-      </c>
-      <c r="J9" s="8">
+        <v>1.9158696955345889E-4</v>
+      </c>
+      <c r="K9" s="1">
         <f t="shared" si="5"/>
-        <v>9.8156951788830327E-7</v>
-      </c>
-      <c r="K9" s="1">
-        <f t="shared" si="6"/>
-        <v>4.9999999999999991</v>
+        <v>5</v>
       </c>
       <c r="L9" s="2">
         <f t="shared" si="9"/>
-        <v>3336.0000000000005</v>
+        <v>3306.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="2">
-        <f t="shared" si="7"/>
-        <v>14.174741629268059</v>
+        <f t="shared" si="6"/>
+        <v>14.330125702369621</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E10" s="1">
@@ -2304,183 +2689,183 @@
         <v>5</v>
       </c>
       <c r="F10" s="4">
+        <f t="shared" si="0"/>
+        <v>1.7445764621496666E-2</v>
+      </c>
+      <c r="G10" s="4">
         <f t="shared" si="1"/>
-        <v>1.76370057767966E-2</v>
-      </c>
-      <c r="G10" s="4">
+        <v>8.7228823107483325E-2</v>
+      </c>
+      <c r="H10" s="5">
         <f t="shared" si="2"/>
-        <v>8.8185028883982997E-2</v>
-      </c>
-      <c r="H10" s="5">
+        <v>3846</v>
+      </c>
+      <c r="I10" s="2">
         <f t="shared" si="3"/>
-        <v>3888</v>
-      </c>
-      <c r="I10" s="2">
+        <v>14.333073322932917</v>
+      </c>
+      <c r="J10" s="8">
         <f t="shared" si="4"/>
-        <v>14.17824074074074</v>
-      </c>
-      <c r="J10" s="8">
+        <v>2.0569397816294632E-4</v>
+      </c>
+      <c r="K10" s="1">
         <f t="shared" si="5"/>
-        <v>2.4685539702939963E-4</v>
-      </c>
-      <c r="K10" s="1">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="L10" s="2">
         <f t="shared" si="9"/>
-        <v>3110.4</v>
+        <v>3076.8</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="2">
-        <f t="shared" si="7"/>
-        <v>15.199110829529346</v>
+        <f t="shared" si="6"/>
+        <v>15.399265260594911</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4">
+        <f t="shared" si="0"/>
+        <v>1.6234540789405293E-2</v>
+      </c>
+      <c r="G11" s="4">
         <f t="shared" si="1"/>
-        <v>1.6448330616439192E-2</v>
-      </c>
-      <c r="G11" s="4">
+        <v>0.14611086710464763</v>
+      </c>
+      <c r="H11" s="5">
         <f t="shared" si="2"/>
-        <v>8.2241653082195956E-2</v>
-      </c>
-      <c r="H11" s="5">
+        <v>6443</v>
+      </c>
+      <c r="I11" s="2">
         <f t="shared" si="3"/>
-        <v>3626</v>
-      </c>
-      <c r="I11" s="2">
+        <v>15.40043458016452</v>
+      </c>
+      <c r="J11" s="8">
         <f t="shared" si="4"/>
-        <v>15.202702702702704</v>
-      </c>
-      <c r="J11" s="8">
+        <v>7.5933464994681898E-5</v>
+      </c>
+      <c r="K11" s="1">
         <f t="shared" si="5"/>
-        <v>2.3632126995076774E-4</v>
-      </c>
-      <c r="K11" s="1">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L11" s="2">
         <f t="shared" si="9"/>
-        <v>2900.8</v>
+        <v>2863.5555555555557</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="2">
-        <f t="shared" si="7"/>
-        <v>16.297508346206453</v>
+        <f t="shared" si="6"/>
+        <v>16.548170999431804</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" s="4">
+        <f t="shared" si="0"/>
+        <v>1.510740975595333E-2</v>
+      </c>
+      <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>1.5339768183532923E-2</v>
-      </c>
-      <c r="G12" s="4">
+        <v>0.13596668780357996</v>
+      </c>
+      <c r="H12" s="5">
         <f t="shared" si="2"/>
-        <v>7.6698840917664615E-2</v>
-      </c>
-      <c r="H12" s="5">
+        <v>5996</v>
+      </c>
+      <c r="I12" s="2">
         <f t="shared" si="3"/>
-        <v>3382</v>
-      </c>
-      <c r="I12" s="2">
+        <v>16.548532354903269</v>
+      </c>
+      <c r="J12" s="8">
         <f t="shared" si="4"/>
-        <v>16.299526907155531</v>
-      </c>
-      <c r="J12" s="8">
+        <v>2.1836580699874375E-5</v>
+      </c>
+      <c r="K12" s="1">
         <f t="shared" si="5"/>
-        <v>1.2385702809281085E-4</v>
-      </c>
-      <c r="K12" s="1">
-        <f t="shared" si="6"/>
-        <v>5.0000000000000009</v>
+        <v>9</v>
       </c>
       <c r="L12" s="2">
         <f t="shared" si="9"/>
-        <v>2705.5999999999995</v>
+        <v>2664.8888888888887</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="2">
-        <f t="shared" si="7"/>
-        <v>17.475284000076851</v>
+        <f t="shared" si="6"/>
+        <v>17.782794100389214</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4058533129758738E-2</v>
+      </c>
+      <c r="G13" s="4">
         <f t="shared" si="1"/>
-        <v>1.4305919148375533E-2</v>
-      </c>
-      <c r="G13" s="4">
+        <v>0.12652679816782864</v>
+      </c>
+      <c r="H13" s="5">
         <f t="shared" si="2"/>
-        <v>7.1529595741877658E-2</v>
-      </c>
-      <c r="H13" s="5">
+        <v>5579</v>
+      </c>
+      <c r="I13" s="2">
         <f t="shared" si="3"/>
-        <v>3154</v>
-      </c>
-      <c r="I13" s="2">
+        <v>17.785445420326223</v>
+      </c>
+      <c r="J13" s="8">
         <f t="shared" si="4"/>
-        <v>17.477805960684847</v>
-      </c>
-      <c r="J13" s="8">
+        <v>1.4909467668799969E-4</v>
+      </c>
+      <c r="K13" s="1">
         <f t="shared" si="5"/>
-        <v>1.4431585821350623E-4</v>
-      </c>
-      <c r="K13" s="1">
-        <f t="shared" si="6"/>
-        <v>5.0000000000000009</v>
+        <v>9</v>
       </c>
       <c r="L13" s="2">
         <f t="shared" si="9"/>
-        <v>2523.1999999999994</v>
+        <v>2479.5555555555557</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="2">
-        <f t="shared" si="7"/>
-        <v>18.738174228603857</v>
+        <f t="shared" si="6"/>
+        <v>19.109529749704389</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E14" s="1">
@@ -2488,45 +2873,45 @@
         <v>9</v>
       </c>
       <c r="F14" s="4">
+        <f t="shared" si="0"/>
+        <v>1.3082477867037378E-2</v>
+      </c>
+      <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>1.3341748078015763E-2</v>
-      </c>
-      <c r="G14" s="4">
+        <v>0.11774230080333641</v>
+      </c>
+      <c r="H14" s="5">
         <f t="shared" si="2"/>
-        <v>0.12007573270214186</v>
-      </c>
-      <c r="H14" s="5">
+        <v>5192</v>
+      </c>
+      <c r="I14" s="2">
         <f t="shared" si="3"/>
-        <v>5295</v>
-      </c>
-      <c r="I14" s="2">
+        <v>19.111132511556242</v>
+      </c>
+      <c r="J14" s="8">
         <f t="shared" si="4"/>
-        <v>18.739376770538243</v>
-      </c>
-      <c r="J14" s="8">
+        <v>8.3872385812089334E-5</v>
+      </c>
+      <c r="K14" s="1">
         <f t="shared" si="5"/>
-        <v>6.4176046167263578E-5</v>
-      </c>
-      <c r="K14" s="1">
-        <f t="shared" si="6"/>
-        <v>9</v>
+        <v>9.0000000000000018</v>
       </c>
       <c r="L14" s="2">
         <f t="shared" si="9"/>
-        <v>2353.3333333333335</v>
+        <v>2307.5555555555552</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="2">
-        <f t="shared" si="7"/>
-        <v>20.09233002565049</v>
+        <f t="shared" si="6"/>
+        <v>20.535250264571442</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E15" s="1">
@@ -2534,45 +2919,45 @@
         <v>9</v>
       </c>
       <c r="F15" s="4">
+        <f t="shared" si="0"/>
+        <v>1.217418812914659E-2</v>
+      </c>
+      <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>1.2442558910830265E-2</v>
-      </c>
-      <c r="G15" s="4">
+        <v>0.1095676931623193</v>
+      </c>
+      <c r="H15" s="5">
         <f t="shared" si="2"/>
-        <v>0.11198303019747238</v>
-      </c>
-      <c r="H15" s="5">
+        <v>4831</v>
+      </c>
+      <c r="I15" s="2">
         <f t="shared" si="3"/>
-        <v>4938</v>
-      </c>
-      <c r="I15" s="2">
+        <v>20.539225833160838</v>
+      </c>
+      <c r="J15" s="8">
         <f t="shared" si="4"/>
-        <v>20.094167679222355</v>
-      </c>
-      <c r="J15" s="8">
+        <v>1.9359727971046681E-4</v>
+      </c>
+      <c r="K15" s="1">
         <f t="shared" si="5"/>
-        <v>9.1460451302483037E-5</v>
-      </c>
-      <c r="K15" s="1">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
+        <v>9.0000000000000018</v>
       </c>
       <c r="L15" s="2">
         <f t="shared" si="9"/>
-        <v>2194.666666666667</v>
+        <v>2147.1111111111109</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="2">
-        <f t="shared" si="7"/>
-        <v>21.54434690031886</v>
+        <f t="shared" si="6"/>
+        <v>22.067340690845874</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E16" s="1">
@@ -2580,137 +2965,137 @@
         <v>9</v>
       </c>
       <c r="F16" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1328959094002057E-2</v>
+      </c>
+      <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>1.1603972084031935E-2</v>
-      </c>
-      <c r="G16" s="4">
+        <v>0.10196063184601852</v>
+      </c>
+      <c r="H16" s="5">
         <f t="shared" si="2"/>
-        <v>0.10443574875628742</v>
-      </c>
-      <c r="H16" s="5">
+        <v>4496</v>
+      </c>
+      <c r="I16" s="2">
         <f t="shared" si="3"/>
-        <v>4605</v>
-      </c>
-      <c r="I16" s="2">
+        <v>22.069617437722421</v>
+      </c>
+      <c r="J16" s="8">
         <f t="shared" si="4"/>
-        <v>21.547231270358306</v>
-      </c>
-      <c r="J16" s="8">
+        <v>1.0317268892712228E-4</v>
+      </c>
+      <c r="K16" s="1">
         <f t="shared" si="5"/>
-        <v>1.338805976709434E-4</v>
-      </c>
-      <c r="K16" s="1">
-        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="L16" s="2">
         <f t="shared" si="9"/>
-        <v>2046.6666666666667</v>
+        <v>1998.2222222222222</v>
       </c>
     </row>
     <row r="17" spans="2:12">
       <c r="B17" s="2">
-        <f t="shared" si="7"/>
-        <v>23.101297000831625</v>
+        <f t="shared" si="6"/>
+        <v>23.713737056616527</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="8"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F17" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0542412585714568E-2</v>
+      </c>
+      <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>1.0821903202707633E-2</v>
-      </c>
-      <c r="G17" s="4">
+        <v>0.13705136361428938</v>
+      </c>
+      <c r="H17" s="5">
         <f t="shared" si="2"/>
-        <v>9.7397128824368698E-2</v>
-      </c>
-      <c r="H17" s="5">
+        <v>6043</v>
+      </c>
+      <c r="I17" s="2">
         <f t="shared" si="3"/>
-        <v>4295</v>
-      </c>
-      <c r="I17" s="2">
+        <v>23.717524408406419</v>
+      </c>
+      <c r="J17" s="8">
         <f t="shared" si="4"/>
-        <v>23.102444703143188</v>
-      </c>
-      <c r="J17" s="8">
+        <v>1.5971130070524531E-4</v>
+      </c>
+      <c r="K17" s="1">
         <f t="shared" si="5"/>
-        <v>4.9681293285086525E-5</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" si="6"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L17" s="2">
         <f t="shared" si="9"/>
-        <v>1908.8888888888889</v>
+        <v>1859.3846153846155</v>
       </c>
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="2">
-        <f t="shared" si="7"/>
-        <v>24.770763559917139</v>
+        <f t="shared" si="6"/>
+        <v>25.482967479793434</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="8"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F18" s="4">
+        <f t="shared" si="0"/>
+        <v>9.8104743962113515E-3</v>
+      </c>
+      <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>1.0092543146491374E-2</v>
-      </c>
-      <c r="G18" s="4">
+        <v>0.12753616715074756</v>
+      </c>
+      <c r="H18" s="5">
         <f t="shared" si="2"/>
-        <v>9.0832888318422358E-2</v>
-      </c>
-      <c r="H18" s="5">
+        <v>5624</v>
+      </c>
+      <c r="I18" s="2">
         <f t="shared" si="3"/>
-        <v>4005</v>
-      </c>
-      <c r="I18" s="2">
+        <v>25.484530583214795</v>
+      </c>
+      <c r="J18" s="8">
         <f t="shared" si="4"/>
-        <v>24.775280898876407</v>
-      </c>
-      <c r="J18" s="8">
+        <v>6.133914437556065E-5</v>
+      </c>
+      <c r="K18" s="1">
         <f t="shared" si="5"/>
-        <v>1.8236575341501471E-4</v>
-      </c>
-      <c r="K18" s="1">
-        <f t="shared" si="6"/>
-        <v>9.0000000000000018</v>
+        <v>13</v>
       </c>
       <c r="L18" s="2">
         <f t="shared" si="9"/>
-        <v>1779.9999999999995</v>
+        <v>1730.4615384615386</v>
       </c>
     </row>
     <row r="19" spans="2:12">
       <c r="B19" s="2">
-        <f t="shared" si="7"/>
-        <v>26.560877829466897</v>
+        <f t="shared" si="6"/>
+        <v>27.384196342643577</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="E19" s="1">
@@ -2718,3946 +3103,3809 @@
         <v>13</v>
       </c>
       <c r="F19" s="4">
+        <f t="shared" si="0"/>
+        <v>9.1293531813709545E-3</v>
+      </c>
+      <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>9.412339516981158E-3</v>
-      </c>
-      <c r="G19" s="4">
+        <v>0.11868159135782241</v>
+      </c>
+      <c r="H19" s="5">
         <f t="shared" si="2"/>
-        <v>0.12236041372075505</v>
-      </c>
-      <c r="H19" s="5">
+        <v>5233</v>
+      </c>
+      <c r="I19" s="2">
         <f t="shared" si="3"/>
-        <v>5396</v>
-      </c>
-      <c r="I19" s="2">
+        <v>27.388687177527231</v>
+      </c>
+      <c r="J19" s="8">
         <f t="shared" si="4"/>
-        <v>26.561341734618239</v>
-      </c>
-      <c r="J19" s="8">
+        <v>1.6399367092834183E-4</v>
+      </c>
+      <c r="K19" s="1">
         <f t="shared" si="5"/>
-        <v>1.7465731152466191E-5</v>
-      </c>
-      <c r="K19" s="1">
-        <f t="shared" si="6"/>
-        <v>13.000000000000002</v>
+        <v>13</v>
       </c>
       <c r="L19" s="2">
         <f t="shared" si="9"/>
-        <v>1660.3076923076922</v>
+        <v>1610.1538461538462</v>
       </c>
     </row>
     <row r="20" spans="2:12">
       <c r="B20" s="2">
-        <f t="shared" si="7"/>
-        <v>28.480358684358055</v>
+        <f t="shared" si="6"/>
+        <v>29.427271762092776</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F20" s="4">
+        <f t="shared" si="0"/>
+        <v>8.4955208223564099E-3</v>
+      </c>
+      <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>8.7779793355378163E-3</v>
-      </c>
-      <c r="G20" s="4">
+        <v>0.14442385398005897</v>
+      </c>
+      <c r="H20" s="5">
         <f t="shared" si="2"/>
-        <v>0.11411373136199161</v>
-      </c>
-      <c r="H20" s="5">
+        <v>6369</v>
+      </c>
+      <c r="I20" s="2">
         <f t="shared" si="3"/>
-        <v>5032</v>
-      </c>
-      <c r="I20" s="2">
+        <v>29.427696655675931</v>
+      </c>
+      <c r="J20" s="8">
         <f t="shared" si="4"/>
-        <v>28.482710651828295</v>
-      </c>
-      <c r="J20" s="8">
+        <v>1.4438769131874807E-5</v>
+      </c>
+      <c r="K20" s="1">
         <f t="shared" si="5"/>
-        <v>8.2582087406413152E-5</v>
-      </c>
-      <c r="K20" s="1">
-        <f t="shared" si="6"/>
-        <v>12.999999999999998</v>
+        <v>17</v>
       </c>
       <c r="L20" s="2">
         <f t="shared" si="9"/>
-        <v>1548.3076923076926</v>
+        <v>1498.5882352941176</v>
       </c>
     </row>
     <row r="21" spans="2:12">
       <c r="B21" s="2">
-        <f t="shared" si="7"/>
-        <v>30.538555088334199</v>
+        <f t="shared" si="6"/>
+        <v>31.622776601683746</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F21" s="4">
+        <f t="shared" si="0"/>
+        <v>7.90569415042096E-3</v>
+      </c>
+      <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>8.1863729071943083E-3</v>
-      </c>
-      <c r="G21" s="4">
+        <v>0.13439680055715633</v>
+      </c>
+      <c r="H21" s="5">
         <f t="shared" si="2"/>
-        <v>0.10642284779352601</v>
-      </c>
-      <c r="H21" s="5">
+        <v>5926</v>
+      </c>
+      <c r="I21" s="2">
         <f t="shared" si="3"/>
-        <v>4693</v>
-      </c>
-      <c r="I21" s="2">
+        <v>31.627573405332431</v>
+      </c>
+      <c r="J21" s="8">
         <f t="shared" si="4"/>
-        <v>30.54016620498615</v>
-      </c>
-      <c r="J21" s="8">
+        <v>1.516882501844119E-4</v>
+      </c>
+      <c r="K21" s="1">
         <f t="shared" si="5"/>
-        <v>5.2756806839360237E-5</v>
-      </c>
-      <c r="K21" s="1">
-        <f t="shared" si="6"/>
-        <v>13</v>
+        <v>16.999999999999996</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="9"/>
-        <v>1444</v>
+        <v>1394.3529411764709</v>
       </c>
     </row>
     <row r="22" spans="2:12">
       <c r="B22" s="2">
-        <f t="shared" si="7"/>
-        <v>32.745491628777337</v>
+        <f t="shared" si="6"/>
+        <v>33.982083289425539</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F22" s="4">
+        <f t="shared" si="0"/>
+        <v>7.3568179405232165E-3</v>
+      </c>
+      <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>7.6346387720835265E-3</v>
-      </c>
-      <c r="G22" s="4">
+        <v>0.12506590498889469</v>
+      </c>
+      <c r="H22" s="5">
         <f t="shared" si="2"/>
-        <v>9.9250304037085846E-2</v>
-      </c>
-      <c r="H22" s="5">
+        <v>5515</v>
+      </c>
+      <c r="I22" s="2">
         <f t="shared" si="3"/>
-        <v>4376</v>
-      </c>
-      <c r="I22" s="2">
+        <v>33.984587488667273</v>
+      </c>
+      <c r="J22" s="8">
         <f t="shared" si="4"/>
-        <v>32.752513711151735</v>
-      </c>
-      <c r="J22" s="8">
+        <v>7.3691751632853908E-5</v>
+      </c>
+      <c r="K22" s="1">
         <f t="shared" si="5"/>
-        <v>2.1444424942540508E-4</v>
-      </c>
-      <c r="K22" s="1">
-        <f t="shared" si="6"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L22" s="2">
         <f t="shared" si="9"/>
-        <v>1346.4615384615386</v>
+        <v>1297.6470588235295</v>
       </c>
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="2">
-        <f t="shared" si="7"/>
-        <v>35.111917342151372</v>
+        <f t="shared" si="6"/>
+        <v>36.517412725483709</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F23" s="4">
+        <f t="shared" si="0"/>
+        <v>6.8460490856609149E-3</v>
+      </c>
+      <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>7.1200896710894926E-3</v>
-      </c>
-      <c r="G23" s="4">
+        <v>0.1437670307988792</v>
+      </c>
+      <c r="H23" s="5">
         <f t="shared" si="2"/>
-        <v>0.12104152440852137</v>
-      </c>
-      <c r="H23" s="5">
+        <v>6340</v>
+      </c>
+      <c r="I23" s="2">
         <f t="shared" si="3"/>
-        <v>5337</v>
-      </c>
-      <c r="I23" s="2">
+        <v>36.518138801261827</v>
+      </c>
+      <c r="J23" s="8">
         <f t="shared" si="4"/>
-        <v>35.118043844856665</v>
-      </c>
-      <c r="J23" s="8">
+        <v>1.9883001667553302E-5</v>
+      </c>
+      <c r="K23" s="1">
         <f t="shared" si="5"/>
-        <v>1.7448499452732413E-4</v>
-      </c>
-      <c r="K23" s="1">
-        <f t="shared" si="6"/>
-        <v>17.000000000000004</v>
+        <v>20.999999999999996</v>
       </c>
       <c r="L23" s="2">
         <f t="shared" si="9"/>
-        <v>1255.7647058823527</v>
+        <v>1207.6190476190479</v>
       </c>
     </row>
     <row r="24" spans="2:12">
       <c r="B24" s="2">
-        <f t="shared" si="7"/>
-        <v>37.649358067924744</v>
+        <f t="shared" si="6"/>
+        <v>39.24189758484529</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F24" s="4">
+        <f t="shared" si="0"/>
+        <v>6.3707418699483773E-3</v>
+      </c>
+      <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>6.6402194573667046E-3</v>
-      </c>
-      <c r="G24" s="4">
+        <v>0.13378557926891593</v>
+      </c>
+      <c r="H24" s="5">
         <f t="shared" si="2"/>
-        <v>0.11288373077523398</v>
-      </c>
-      <c r="H24" s="5">
+        <v>5899</v>
+      </c>
+      <c r="I24" s="2">
         <f t="shared" si="3"/>
-        <v>4978</v>
-      </c>
-      <c r="I24" s="2">
+        <v>39.248177657230045</v>
+      </c>
+      <c r="J24" s="8">
         <f t="shared" si="4"/>
-        <v>37.650662916834065</v>
-      </c>
-      <c r="J24" s="8">
+        <v>1.6003488035143398E-4</v>
+      </c>
+      <c r="K24" s="1">
         <f t="shared" si="5"/>
-        <v>3.4657932466375385E-5</v>
-      </c>
-      <c r="K24" s="1">
-        <f t="shared" si="6"/>
-        <v>16.999999999999996</v>
+        <v>21.000000000000004</v>
       </c>
       <c r="L24" s="2">
         <f t="shared" si="9"/>
-        <v>1171.294117647059</v>
+        <v>1123.6190476190475</v>
       </c>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="2">
-        <f t="shared" si="7"/>
-        <v>40.370172585965619</v>
+        <f t="shared" si="6"/>
+        <v>42.169650342858148</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F25" s="4">
+        <f t="shared" si="0"/>
+        <v>5.9284342641541489E-3</v>
+      </c>
+      <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>6.1926908899792663E-3</v>
-      </c>
-      <c r="G25" s="4">
+        <v>0.12449711954723712</v>
+      </c>
+      <c r="H25" s="5">
         <f t="shared" si="2"/>
-        <v>0.10527574512964753</v>
-      </c>
-      <c r="H25" s="5">
+        <v>5490</v>
+      </c>
+      <c r="I25" s="2">
         <f t="shared" si="3"/>
-        <v>4642</v>
-      </c>
-      <c r="I25" s="2">
+        <v>42.172131147540981</v>
+      </c>
+      <c r="J25" s="8">
         <f t="shared" si="4"/>
-        <v>40.375915553640674</v>
-      </c>
-      <c r="J25" s="8">
+        <v>5.8829149937489333E-5</v>
+      </c>
+      <c r="K25" s="1">
         <f t="shared" si="5"/>
-        <v>1.4225769441100766E-4</v>
-      </c>
-      <c r="K25" s="1">
-        <f t="shared" si="6"/>
-        <v>17</v>
+        <v>20.999999999999996</v>
       </c>
       <c r="L25" s="2">
         <f t="shared" si="9"/>
-        <v>1092.2352941176471</v>
+        <v>1045.7142857142858</v>
       </c>
     </row>
     <row r="26" spans="2:12">
       <c r="B26" s="2">
-        <f t="shared" si="7"/>
-        <v>43.287612810830666</v>
+        <f t="shared" si="6"/>
+        <v>45.315836376008093</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="10"/>
         <v>22</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" si="8"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F26" s="4">
+        <f t="shared" si="0"/>
+        <v>5.5168351727114852E-3</v>
+      </c>
+      <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>5.7753242502078883E-3</v>
-      </c>
-      <c r="G26" s="4">
+        <v>0.13792087931778713</v>
+      </c>
+      <c r="H26" s="5">
         <f t="shared" si="2"/>
-        <v>0.12128180925436566</v>
-      </c>
-      <c r="H26" s="5">
+        <v>6082</v>
+      </c>
+      <c r="I26" s="2">
         <f t="shared" si="3"/>
-        <v>5348</v>
-      </c>
-      <c r="I26" s="2">
+        <v>45.318151923709308</v>
+      </c>
+      <c r="J26" s="8">
         <f t="shared" si="4"/>
-        <v>43.291884816753928</v>
-      </c>
-      <c r="J26" s="8">
+        <v>5.109798000857424E-5</v>
+      </c>
+      <c r="K26" s="1">
         <f t="shared" si="5"/>
-        <v>9.8688877622654658E-5</v>
-      </c>
-      <c r="K26" s="1">
-        <f t="shared" si="6"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L26" s="2">
         <f t="shared" si="9"/>
-        <v>1018.6666666666666</v>
+        <v>973.12</v>
       </c>
     </row>
     <row r="27" spans="2:12">
       <c r="B27" s="2">
-        <f t="shared" si="7"/>
-        <v>46.415888336127878</v>
+        <f t="shared" si="6"/>
+        <v>48.696752516586216</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="10"/>
         <v>23</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" si="8"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F27" s="4">
+        <f t="shared" si="0"/>
+        <v>5.1338125661428754E-3</v>
+      </c>
+      <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>5.3860867250796985E-3</v>
-      </c>
-      <c r="G27" s="4">
+        <v>0.12834531415357189</v>
+      </c>
+      <c r="H27" s="5">
         <f t="shared" si="2"/>
-        <v>0.11310782122667366</v>
-      </c>
-      <c r="H27" s="5">
+        <v>5660</v>
+      </c>
+      <c r="I27" s="2">
         <f t="shared" si="3"/>
-        <v>4988</v>
-      </c>
-      <c r="I27" s="2">
+        <v>48.696996466431095</v>
+      </c>
+      <c r="J27" s="8">
         <f t="shared" si="4"/>
-        <v>46.416399358460303</v>
-      </c>
-      <c r="J27" s="8">
+        <v>5.0095711165987211E-6</v>
+      </c>
+      <c r="K27" s="1">
         <f t="shared" si="5"/>
-        <v>1.1009642403525532E-5</v>
-      </c>
-      <c r="K27" s="1">
-        <f t="shared" si="6"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L27" s="2">
         <f t="shared" si="9"/>
-        <v>950.09523809523807</v>
+        <v>905.6</v>
       </c>
     </row>
     <row r="28" spans="2:12">
       <c r="B28" s="2">
-        <f t="shared" si="7"/>
-        <v>49.770235643321207</v>
+        <f t="shared" si="6"/>
+        <v>52.329911468149362</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="10"/>
         <v>24</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" si="8"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F28" s="4">
+        <f t="shared" si="0"/>
+        <v>4.7773824374261111E-3</v>
+      </c>
+      <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>5.0230825064126079E-3</v>
-      </c>
-      <c r="G28" s="4">
+        <v>0.13854409068535722</v>
+      </c>
+      <c r="H28" s="5">
         <f t="shared" si="2"/>
-        <v>0.10548473263466476</v>
-      </c>
-      <c r="H28" s="5">
+        <v>6109</v>
+      </c>
+      <c r="I28" s="2">
         <f t="shared" si="3"/>
-        <v>4651</v>
-      </c>
-      <c r="I28" s="2">
+        <v>52.336716320183335</v>
+      </c>
+      <c r="J28" s="8">
         <f t="shared" si="4"/>
-        <v>49.779617286605038</v>
-      </c>
-      <c r="J28" s="8">
+        <v>1.3003752238560651E-4</v>
+      </c>
+      <c r="K28" s="1">
         <f t="shared" si="5"/>
-        <v>1.8849907304163693E-4</v>
-      </c>
-      <c r="K28" s="1">
-        <f t="shared" si="6"/>
-        <v>21.000000000000004</v>
+        <v>29</v>
       </c>
       <c r="L28" s="2">
         <f t="shared" si="9"/>
-        <v>885.9047619047617</v>
+        <v>842.62068965517244</v>
       </c>
     </row>
     <row r="29" spans="2:12">
       <c r="B29" s="2">
-        <f t="shared" si="7"/>
-        <v>53.366992312063211</v>
+        <f t="shared" si="6"/>
+        <v>56.234132519034787</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="10"/>
         <v>25</v>
       </c>
       <c r="D29" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" si="8"/>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F29" s="4">
+        <f t="shared" si="0"/>
+        <v>4.4456985250973169E-3</v>
+      </c>
+      <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>4.6845435571509497E-3</v>
-      </c>
-      <c r="G29" s="4">
+        <v>0.14670805132821146</v>
+      </c>
+      <c r="H29" s="5">
         <f t="shared" si="2"/>
-        <v>0.11711358892877374</v>
-      </c>
-      <c r="H29" s="5">
+        <v>6469</v>
+      </c>
+      <c r="I29" s="2">
         <f t="shared" si="3"/>
-        <v>5164</v>
-      </c>
-      <c r="I29" s="2">
+        <v>56.241304683876947</v>
+      </c>
+      <c r="J29" s="8">
         <f t="shared" si="4"/>
-        <v>53.37432223082881</v>
-      </c>
-      <c r="J29" s="8">
+        <v>1.2754113064228356E-4</v>
+      </c>
+      <c r="K29" s="1">
         <f t="shared" si="5"/>
-        <v>1.373492949112709E-4</v>
-      </c>
-      <c r="K29" s="1">
-        <f t="shared" si="6"/>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L29" s="2">
         <f t="shared" si="9"/>
-        <v>826.24</v>
+        <v>784.12121212121212</v>
       </c>
     </row>
     <row r="30" spans="2:12">
       <c r="B30" s="2">
-        <f t="shared" si="7"/>
-        <v>57.223676593502297</v>
+        <f t="shared" si="6"/>
+        <v>60.429639023813145</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="8"/>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F30" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1370427498579627E-3</v>
+      </c>
+      <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>4.3688210000192001E-3</v>
-      </c>
-      <c r="G30" s="4">
+        <v>0.13652241074531277</v>
+      </c>
+      <c r="H30" s="5">
         <f t="shared" si="2"/>
-        <v>0.10922052500048</v>
-      </c>
-      <c r="H30" s="5">
+        <v>6020</v>
+      </c>
+      <c r="I30" s="2">
         <f t="shared" si="3"/>
-        <v>4816</v>
-      </c>
-      <c r="I30" s="2">
+        <v>60.436046511627907</v>
+      </c>
+      <c r="J30" s="8">
         <f t="shared" si="4"/>
-        <v>57.231104651162795</v>
-      </c>
-      <c r="J30" s="8">
+        <v>1.0603220403537783E-4</v>
+      </c>
+      <c r="K30" s="1">
         <f t="shared" si="5"/>
-        <v>1.2980741718604527E-4</v>
-      </c>
-      <c r="K30" s="1">
-        <f t="shared" si="6"/>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L30" s="2">
         <f t="shared" si="9"/>
-        <v>770.56</v>
+        <v>729.69696969696975</v>
       </c>
     </row>
     <row r="31" spans="2:12">
       <c r="B31" s="2">
-        <f t="shared" si="7"/>
-        <v>61.359072734131871</v>
+        <f t="shared" si="6"/>
+        <v>64.938163157620977</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>9</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" si="8"/>
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F31" s="4">
+        <f t="shared" si="0"/>
+        <v>3.849816315148739E-3</v>
+      </c>
+      <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>4.0743770865516015E-3</v>
-      </c>
-      <c r="G31" s="4">
+        <v>0.14244320366050334</v>
+      </c>
+      <c r="H31" s="5">
         <f t="shared" si="2"/>
-        <v>0.11815693550999644</v>
-      </c>
-      <c r="H31" s="5">
+        <v>6281</v>
+      </c>
+      <c r="I31" s="2">
         <f t="shared" si="3"/>
-        <v>5210</v>
-      </c>
-      <c r="I31" s="2">
+        <v>64.945868492278308</v>
+      </c>
+      <c r="J31" s="8">
         <f t="shared" si="4"/>
-        <v>61.367562380038386</v>
-      </c>
-      <c r="J31" s="8">
+        <v>1.1865649230990982E-4</v>
+      </c>
+      <c r="K31" s="1">
         <f t="shared" si="5"/>
-        <v>1.3836007501777381E-4</v>
-      </c>
-      <c r="K31" s="1">
-        <f t="shared" si="6"/>
-        <v>29</v>
+        <v>37.000000000000007</v>
       </c>
       <c r="L31" s="2">
         <f t="shared" si="9"/>
-        <v>718.62068965517244</v>
+        <v>679.02702702702686</v>
       </c>
     </row>
     <row r="32" spans="2:12">
       <c r="B32" s="2">
-        <f t="shared" si="7"/>
-        <v>65.793322465756958</v>
+        <f t="shared" si="6"/>
+        <v>69.783058485986459</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" si="8"/>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F32" s="4">
+        <f t="shared" si="0"/>
+        <v>3.5825314255924158E-3</v>
+      </c>
+      <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>3.7997777073823253E-3</v>
-      </c>
-      <c r="G32" s="4">
+        <v>0.14688378844928904</v>
+      </c>
+      <c r="H32" s="5">
         <f t="shared" si="2"/>
-        <v>0.11019355351408744</v>
-      </c>
-      <c r="H32" s="5">
+        <v>6477</v>
+      </c>
+      <c r="I32" s="2">
         <f t="shared" si="3"/>
-        <v>4859</v>
-      </c>
-      <c r="I32" s="2">
+        <v>69.789254284390921</v>
+      </c>
+      <c r="J32" s="8">
         <f t="shared" si="4"/>
-        <v>65.800576250257251</v>
-      </c>
-      <c r="J32" s="8">
+        <v>8.8786569962584494E-5</v>
+      </c>
+      <c r="K32" s="1">
         <f t="shared" si="5"/>
-        <v>1.1025107455342464E-4</v>
-      </c>
-      <c r="K32" s="1">
-        <f t="shared" si="6"/>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L32" s="2">
         <f t="shared" si="9"/>
-        <v>670.20689655172418</v>
+        <v>631.90243902439022</v>
       </c>
     </row>
     <row r="33" spans="2:12">
       <c r="B33" s="2">
-        <f t="shared" si="7"/>
-        <v>70.548023107186609</v>
+        <f t="shared" si="6"/>
+        <v>74.989420933245384</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" si="10"/>
         <v>29</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" si="8"/>
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F33" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3338035804083188E-3</v>
+      </c>
+      <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>3.5436854073170043E-3</v>
-      </c>
-      <c r="G33" s="4">
+        <v>0.13668594679674106</v>
+      </c>
+      <c r="H33" s="5">
         <f t="shared" si="2"/>
-        <v>0.11694161844146114</v>
-      </c>
-      <c r="H33" s="5">
+        <v>6027</v>
+      </c>
+      <c r="I33" s="2">
         <f t="shared" si="3"/>
-        <v>5157</v>
-      </c>
-      <c r="I33" s="2">
+        <v>75</v>
+      </c>
+      <c r="J33" s="8">
         <f t="shared" si="4"/>
-        <v>70.549738219895289</v>
-      </c>
-      <c r="J33" s="8">
+        <v>1.4107412249564355E-4</v>
+      </c>
+      <c r="K33" s="1">
         <f t="shared" si="5"/>
-        <v>2.4311279510635941E-5</v>
-      </c>
-      <c r="K33" s="1">
-        <f t="shared" si="6"/>
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L33" s="2">
         <f t="shared" si="9"/>
-        <v>625.09090909090912</v>
+        <v>588</v>
       </c>
     </row>
     <row r="34" spans="2:12">
       <c r="B34" s="2">
-        <f t="shared" si="7"/>
-        <v>75.646332755463078</v>
+        <f t="shared" si="6"/>
+        <v>80.584218776147964</v>
       </c>
       <c r="C34" s="1">
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f t="shared" si="7"/>
+        <v>11</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" si="8"/>
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F34" s="4">
+        <f t="shared" si="0"/>
+        <v>3.1023444018793071E-3</v>
+      </c>
+      <c r="G34" s="4">
         <f t="shared" si="1"/>
-        <v>3.3048528711650642E-3</v>
-      </c>
-      <c r="G34" s="4">
+        <v>0.13960549808456882</v>
+      </c>
+      <c r="H34" s="5">
         <f t="shared" si="2"/>
-        <v>0.12227955623310738</v>
-      </c>
-      <c r="H34" s="5">
+        <v>6156</v>
+      </c>
+      <c r="I34" s="2">
         <f t="shared" si="3"/>
-        <v>5392</v>
-      </c>
-      <c r="I34" s="2">
+        <v>80.59210526315789</v>
+      </c>
+      <c r="J34" s="8">
         <f t="shared" si="4"/>
-        <v>75.653746290801195</v>
-      </c>
-      <c r="J34" s="8">
+        <v>9.7866395303070064E-5</v>
+      </c>
+      <c r="K34" s="1">
         <f t="shared" si="5"/>
-        <v>9.8002574190569902E-5</v>
-      </c>
-      <c r="K34" s="1">
-        <f t="shared" si="6"/>
-        <v>37.000000000000007</v>
+        <v>45</v>
       </c>
       <c r="L34" s="2">
         <f t="shared" si="9"/>
-        <v>582.91891891891885</v>
+        <v>547.20000000000005</v>
       </c>
     </row>
     <row r="35" spans="2:12">
       <c r="B35" s="2">
-        <f t="shared" si="7"/>
-        <v>81.113083078968927</v>
+        <f t="shared" si="6"/>
+        <v>86.596432336006288</v>
       </c>
       <c r="C35" s="1">
         <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" si="8"/>
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F35" s="4">
+        <f t="shared" si="0"/>
+        <v>2.8869549617236536E-3</v>
+      </c>
+      <c r="G35" s="4">
         <f t="shared" si="1"/>
-        <v>3.0821168486051573E-3</v>
-      </c>
-      <c r="G35" s="4">
+        <v>0.14146079312445903</v>
+      </c>
+      <c r="H35" s="5">
         <f t="shared" si="2"/>
-        <v>0.11403832339839082</v>
-      </c>
-      <c r="H35" s="5">
+        <v>6238</v>
+      </c>
+      <c r="I35" s="2">
         <f t="shared" si="3"/>
-        <v>5029</v>
-      </c>
-      <c r="I35" s="2">
+        <v>86.6022763706316</v>
+      </c>
+      <c r="J35" s="8">
         <f t="shared" si="4"/>
-        <v>81.114535692980724</v>
-      </c>
-      <c r="J35" s="8">
+        <v>6.7485859032156981E-5</v>
+      </c>
+      <c r="K35" s="1">
         <f t="shared" si="5"/>
-        <v>1.7908504481134457E-5</v>
-      </c>
-      <c r="K35" s="1">
-        <f t="shared" si="6"/>
-        <v>37.000000000000007</v>
+        <v>48.999999999999993</v>
       </c>
       <c r="L35" s="2">
         <f t="shared" si="9"/>
-        <v>543.67567567567562</v>
+        <v>509.22448979591843</v>
       </c>
     </row>
     <row r="36" spans="2:12">
       <c r="B36" s="2">
-        <f t="shared" si="7"/>
-        <v>86.974900261778572</v>
+        <f t="shared" si="6"/>
+        <v>93.057204092969627</v>
       </c>
       <c r="C36" s="1">
         <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="7"/>
+        <v>13</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" si="8"/>
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F36" s="4">
+        <f t="shared" si="0"/>
+        <v>2.6865195708033014E-3</v>
+      </c>
+      <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>2.8743924884943317E-3</v>
-      </c>
-      <c r="G36" s="4">
+        <v>0.14238553725257497</v>
+      </c>
+      <c r="H36" s="5">
         <f t="shared" si="2"/>
-        <v>0.1178500920282676</v>
-      </c>
-      <c r="H36" s="5">
+        <v>6279</v>
+      </c>
+      <c r="I36" s="2">
         <f t="shared" si="3"/>
-        <v>5197</v>
-      </c>
-      <c r="I36" s="2">
+        <v>93.060200668896329</v>
+      </c>
+      <c r="J36" s="8">
         <f t="shared" si="4"/>
-        <v>86.978064267846833</v>
-      </c>
-      <c r="J36" s="8">
+        <v>3.220143949000942E-5</v>
+      </c>
+      <c r="K36" s="1">
         <f t="shared" si="5"/>
-        <v>3.6378381104595903E-5</v>
-      </c>
-      <c r="K36" s="1">
-        <f t="shared" si="6"/>
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="L36" s="2">
         <f t="shared" si="9"/>
-        <v>507.02439024390242</v>
+        <v>473.88679245283021</v>
       </c>
     </row>
     <row r="37" spans="2:12">
       <c r="B37" s="2">
-        <f t="shared" si="7"/>
-        <v>93.260334688322246</v>
+        <f t="shared" si="6"/>
+        <v>99.999999999999702</v>
       </c>
       <c r="C37" s="1">
         <f t="shared" si="10"/>
         <v>33</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" ref="D37:D68" si="11">INT((B37/2-1)/4)</f>
-        <v>11</v>
+        <f t="shared" si="7"/>
+        <v>14</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" si="8"/>
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F37" s="4">
-        <f t="shared" ref="F37:F68" si="12">1/B37/4</f>
-        <v>2.6806680550258005E-3</v>
+        <f t="shared" ref="F37:F68" si="11">1/B37/4</f>
+        <v>2.5000000000000074E-3</v>
       </c>
       <c r="G37" s="4">
-        <f t="shared" ref="G37:G68" si="13">E37*F37</f>
-        <v>0.12063006247616102</v>
+        <f t="shared" ref="G37:G68" si="12">E37*F37</f>
+        <v>0.14250000000000043</v>
       </c>
       <c r="H37" s="5">
-        <f t="shared" ref="H37:H68" si="14">INT(G37*_rate)</f>
-        <v>5319</v>
+        <f t="shared" ref="H37:H68" si="13">INT(G37*_rate)</f>
+        <v>6284</v>
       </c>
       <c r="I37" s="2">
-        <f t="shared" ref="I37:I68" si="15">E37/H37/4*_rate</f>
-        <v>93.274111675126903</v>
+        <f t="shared" ref="I37:I68" si="14">E37/H37/4*_rate</f>
+        <v>100.00397835773393</v>
       </c>
       <c r="J37" s="8">
-        <f t="shared" ref="J37:J68" si="16">(I37/B37-1)</f>
-        <v>1.4772611368707445E-4</v>
+        <f t="shared" ref="J37:J68" si="15">(I37/B37-1)</f>
+        <v>3.9783577342245025E-5</v>
       </c>
       <c r="K37" s="1">
-        <f t="shared" ref="K37:K68" si="17">4*I37*H37/_rate</f>
-        <v>45</v>
+        <f t="shared" ref="K37:K68" si="16">4*I37*H37/_rate</f>
+        <v>57</v>
       </c>
       <c r="L37" s="2">
         <f t="shared" si="9"/>
-        <v>472.8</v>
+        <v>440.98245614035091</v>
       </c>
     </row>
     <row r="38" spans="2:12">
       <c r="B38" s="2">
-        <f t="shared" ref="B38:B69" si="18">B37*_mult</f>
-        <v>100.00000000000028</v>
+        <f t="shared" ref="B38:B69" si="17">B37*_mult</f>
+        <v>107.46078283213141</v>
       </c>
       <c r="C38" s="1">
         <f t="shared" si="10"/>
         <v>34</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="11"/>
-        <v>12</v>
+        <f t="shared" si="7"/>
+        <v>15</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" si="8"/>
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F38" s="4">
+        <f t="shared" si="11"/>
+        <v>2.3264301023242545E-3</v>
+      </c>
+      <c r="G38" s="4">
         <f t="shared" si="12"/>
-        <v>2.4999999999999927E-3</v>
-      </c>
-      <c r="G38" s="4">
+        <v>0.14191223624177954</v>
+      </c>
+      <c r="H38" s="5">
         <f t="shared" si="13"/>
-        <v>0.12249999999999964</v>
-      </c>
-      <c r="H38" s="5">
+        <v>6258</v>
+      </c>
+      <c r="I38" s="2">
         <f t="shared" si="14"/>
-        <v>5402</v>
-      </c>
-      <c r="I38" s="2">
+        <v>107.46644295302013</v>
+      </c>
+      <c r="J38" s="8">
         <f t="shared" si="15"/>
-        <v>100.00462791558682</v>
-      </c>
-      <c r="J38" s="8">
+        <v>5.2671502473344844E-5</v>
+      </c>
+      <c r="K38" s="1">
         <f t="shared" si="16"/>
-        <v>4.6279155865303068E-5</v>
-      </c>
-      <c r="K38" s="1">
-        <f t="shared" si="17"/>
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L38" s="2">
         <f t="shared" si="9"/>
-        <v>440.9795918367347</v>
+        <v>410.36065573770492</v>
       </c>
     </row>
     <row r="39" spans="2:12">
       <c r="B39" s="2">
-        <f t="shared" si="18"/>
-        <v>107.22672220103264</v>
+        <f t="shared" si="17"/>
+        <v>115.47819846894545</v>
       </c>
       <c r="C39" s="1">
         <f t="shared" si="10"/>
         <v>35</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="11"/>
-        <v>13</v>
+        <f t="shared" si="7"/>
+        <v>16</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="8"/>
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F39" s="4">
+        <f t="shared" si="11"/>
+        <v>2.1649108084001701E-3</v>
+      </c>
+      <c r="G39" s="4">
         <f t="shared" si="12"/>
-        <v>2.3315083672080426E-3</v>
-      </c>
-      <c r="G39" s="4">
+        <v>0.14071920254601106</v>
+      </c>
+      <c r="H39" s="5">
         <f t="shared" si="13"/>
-        <v>0.12356994346202625</v>
-      </c>
-      <c r="H39" s="5">
+        <v>6205</v>
+      </c>
+      <c r="I39" s="2">
         <f t="shared" si="14"/>
-        <v>5449</v>
-      </c>
-      <c r="I39" s="2">
+        <v>115.49153908138598</v>
+      </c>
+      <c r="J39" s="8">
         <f t="shared" si="15"/>
-        <v>107.23527252706918</v>
-      </c>
-      <c r="J39" s="8">
+        <v>1.1552494425282056E-4</v>
+      </c>
+      <c r="K39" s="1">
         <f t="shared" si="16"/>
-        <v>7.9740626786284352E-5</v>
-      </c>
-      <c r="K39" s="1">
-        <f t="shared" si="17"/>
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="L39" s="2">
         <f t="shared" si="9"/>
-        <v>411.24528301886795</v>
+        <v>381.84615384615387</v>
       </c>
     </row>
     <row r="40" spans="2:12">
       <c r="B40" s="2">
-        <f t="shared" si="18"/>
-        <v>114.97569953977393</v>
+        <f t="shared" si="17"/>
+        <v>124.09377607517155</v>
       </c>
       <c r="C40" s="1">
         <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" si="11"/>
-        <v>14</v>
+        <f t="shared" si="7"/>
+        <v>17</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" si="8"/>
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F40" s="4">
+        <f t="shared" si="11"/>
+        <v>2.0146054694037113E-3</v>
+      </c>
+      <c r="G40" s="4">
         <f t="shared" si="12"/>
-        <v>2.1743725065444517E-3</v>
-      </c>
-      <c r="G40" s="4">
+        <v>0.13900777738885609</v>
+      </c>
+      <c r="H40" s="5">
         <f t="shared" si="13"/>
-        <v>0.12393923287303375</v>
-      </c>
-      <c r="H40" s="5">
+        <v>6130</v>
+      </c>
+      <c r="I40" s="2">
         <f t="shared" si="14"/>
-        <v>5465</v>
-      </c>
-      <c r="I40" s="2">
+        <v>124.09869494290375</v>
+      </c>
+      <c r="J40" s="8">
         <f t="shared" si="15"/>
-        <v>114.99085086916743</v>
-      </c>
-      <c r="J40" s="8">
+        <v>3.96383113463461E-5</v>
+      </c>
+      <c r="K40" s="1">
         <f t="shared" si="16"/>
-        <v>1.3177853628332237E-4</v>
-      </c>
-      <c r="K40" s="1">
-        <f t="shared" si="17"/>
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="L40" s="2">
         <f t="shared" si="9"/>
-        <v>383.50877192982455</v>
+        <v>355.36231884057969</v>
       </c>
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="2">
-        <f t="shared" si="18"/>
-        <v>123.284673944207</v>
+        <f t="shared" si="17"/>
+        <v>133.35214321633194</v>
       </c>
       <c r="C41" s="1">
         <f t="shared" si="10"/>
         <v>37</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="11"/>
-        <v>15</v>
+        <f t="shared" si="7"/>
+        <v>19</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="8"/>
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F41" s="4">
+        <f t="shared" si="11"/>
+        <v>1.874735523331146E-3</v>
+      </c>
+      <c r="G41" s="4">
         <f t="shared" si="12"/>
-        <v>2.0278270769742116E-3</v>
-      </c>
-      <c r="G41" s="4">
+        <v>0.14435463529649825</v>
+      </c>
+      <c r="H41" s="5">
         <f t="shared" si="13"/>
-        <v>0.12369745169542691</v>
-      </c>
-      <c r="H41" s="5">
+        <v>6366</v>
+      </c>
+      <c r="I41" s="2">
         <f t="shared" si="14"/>
-        <v>5455</v>
-      </c>
-      <c r="I41" s="2">
+        <v>133.35296889726675</v>
+      </c>
+      <c r="J41" s="8">
         <f t="shared" si="15"/>
-        <v>123.28597616865261</v>
-      </c>
-      <c r="J41" s="8">
+        <v>6.191733517679765E-6</v>
+      </c>
+      <c r="K41" s="1">
         <f t="shared" si="16"/>
-        <v>1.0562743964381838E-5</v>
-      </c>
-      <c r="K41" s="1">
-        <f t="shared" si="17"/>
-        <v>61</v>
+        <v>77.000000000000014</v>
       </c>
       <c r="L41" s="2">
         <f t="shared" si="9"/>
-        <v>357.70491803278691</v>
+        <v>330.70129870129864</v>
       </c>
     </row>
     <row r="42" spans="2:12">
       <c r="B42" s="2">
-        <f t="shared" si="18"/>
-        <v>132.19411484660333</v>
+        <f t="shared" si="17"/>
+        <v>143.30125702369577</v>
       </c>
       <c r="C42" s="1">
         <f t="shared" si="10"/>
         <v>38</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="11"/>
-        <v>16</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" si="8"/>
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F42" s="4">
+        <f t="shared" si="11"/>
+        <v>1.7445764621496719E-3</v>
+      </c>
+      <c r="G42" s="4">
         <f t="shared" si="12"/>
-        <v>1.8911583188865662E-3</v>
-      </c>
-      <c r="G42" s="4">
+        <v>0.14131069343412342</v>
+      </c>
+      <c r="H42" s="5">
         <f t="shared" si="13"/>
-        <v>0.1229252907276268</v>
-      </c>
-      <c r="H42" s="5">
+        <v>6231</v>
+      </c>
+      <c r="I42" s="2">
         <f t="shared" si="14"/>
-        <v>5421</v>
-      </c>
-      <c r="I42" s="2">
+        <v>143.31969186326432</v>
+      </c>
+      <c r="J42" s="8">
         <f t="shared" si="15"/>
-        <v>132.19424460431654</v>
-      </c>
-      <c r="J42" s="8">
+        <v>1.2864394877931673E-4</v>
+      </c>
+      <c r="K42" s="1">
         <f t="shared" si="16"/>
-        <v>9.815695150017234E-7</v>
-      </c>
-      <c r="K42" s="1">
-        <f t="shared" si="17"/>
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="L42" s="2">
         <f t="shared" si="9"/>
-        <v>333.6</v>
+        <v>307.7037037037037</v>
       </c>
     </row>
     <row r="43" spans="2:12">
       <c r="B43" s="2">
-        <f t="shared" si="18"/>
-        <v>141.74741629268098</v>
+        <f t="shared" si="17"/>
+        <v>153.99265260594865</v>
       </c>
       <c r="C43" s="1">
         <f t="shared" si="10"/>
         <v>39</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="11"/>
-        <v>17</v>
+        <f t="shared" si="7"/>
+        <v>22</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" si="8"/>
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F43" s="4">
+        <f t="shared" si="11"/>
+        <v>1.6234540789405341E-3</v>
+      </c>
+      <c r="G43" s="4">
         <f t="shared" si="12"/>
-        <v>1.7637005776796552E-3</v>
-      </c>
-      <c r="G43" s="4">
+        <v>0.14448741302570753</v>
+      </c>
+      <c r="H43" s="5">
         <f t="shared" si="13"/>
-        <v>0.12169533985989621</v>
-      </c>
-      <c r="H43" s="5">
+        <v>6371</v>
+      </c>
+      <c r="I43" s="2">
         <f t="shared" si="14"/>
-        <v>5366</v>
-      </c>
-      <c r="I43" s="2">
+        <v>154.01428347198242</v>
+      </c>
+      <c r="J43" s="8">
         <f t="shared" si="15"/>
-        <v>141.76761088333956</v>
-      </c>
-      <c r="J43" s="8">
+        <v>1.4046687077429176E-4</v>
+      </c>
+      <c r="K43" s="1">
         <f t="shared" si="16"/>
-        <v>1.4246884484214739E-4</v>
-      </c>
-      <c r="K43" s="1">
-        <f t="shared" si="17"/>
-        <v>69.000000000000014</v>
+        <v>89</v>
       </c>
       <c r="L43" s="2">
         <f t="shared" si="9"/>
-        <v>311.07246376811588</v>
+        <v>286.33707865168537</v>
       </c>
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="2">
-        <f t="shared" si="18"/>
-        <v>151.99110829529388</v>
+        <f t="shared" si="17"/>
+        <v>165.48170999431753</v>
       </c>
       <c r="C44" s="1">
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="11"/>
-        <v>18</v>
+        <f t="shared" si="7"/>
+        <v>24</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" si="8"/>
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="F44" s="4">
+        <f t="shared" si="11"/>
+        <v>1.5107409755953376E-3</v>
+      </c>
+      <c r="G44" s="4">
         <f t="shared" si="12"/>
-        <v>1.6448330616439144E-3</v>
-      </c>
-      <c r="G44" s="4">
+        <v>0.14654187463274776</v>
+      </c>
+      <c r="H44" s="5">
         <f t="shared" si="13"/>
-        <v>0.12007281350000576</v>
-      </c>
-      <c r="H44" s="5">
+        <v>6462</v>
+      </c>
+      <c r="I44" s="2">
         <f t="shared" si="14"/>
-        <v>5295</v>
-      </c>
-      <c r="I44" s="2">
+        <v>165.49442896935932</v>
+      </c>
+      <c r="J44" s="8">
         <f t="shared" si="15"/>
-        <v>151.9971671388102</v>
-      </c>
-      <c r="J44" s="8">
+        <v>7.6860307052895038E-5</v>
+      </c>
+      <c r="K44" s="1">
         <f t="shared" si="16"/>
-        <v>3.9863144523755167E-5</v>
-      </c>
-      <c r="K44" s="1">
-        <f t="shared" si="17"/>
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L44" s="2">
         <f t="shared" si="9"/>
-        <v>290.13698630136986</v>
+        <v>266.4742268041237</v>
       </c>
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="2">
-        <f t="shared" si="18"/>
-        <v>162.97508346206499</v>
+        <f t="shared" si="17"/>
+        <v>177.8279410038916</v>
       </c>
       <c r="C45" s="1">
         <f t="shared" si="10"/>
         <v>41</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" si="11"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="E45" s="1">
         <f t="shared" si="8"/>
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="F45" s="4">
+        <f t="shared" si="11"/>
+        <v>1.4058533129758782E-3</v>
+      </c>
+      <c r="G45" s="4">
         <f t="shared" si="12"/>
-        <v>1.533976818353288E-3</v>
-      </c>
-      <c r="G45" s="4">
+        <v>0.1419911846105637</v>
+      </c>
+      <c r="H45" s="5">
         <f t="shared" si="13"/>
-        <v>0.12425212228661632</v>
-      </c>
-      <c r="H45" s="5">
+        <v>6261</v>
+      </c>
+      <c r="I45" s="2">
         <f t="shared" si="14"/>
-        <v>5479</v>
-      </c>
-      <c r="I45" s="2">
+        <v>177.8509822712027</v>
+      </c>
+      <c r="J45" s="8">
         <f t="shared" si="15"/>
-        <v>162.99050921701038</v>
-      </c>
-      <c r="J45" s="8">
+        <v>1.2957056793783117E-4</v>
+      </c>
+      <c r="K45" s="1">
         <f t="shared" si="16"/>
-        <v>9.4651001967260839E-5</v>
-      </c>
-      <c r="K45" s="1">
-        <f t="shared" si="17"/>
-        <v>80.999999999999986</v>
+        <v>101</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="9"/>
-        <v>270.56790123456796</v>
+        <v>247.96039603960395</v>
       </c>
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="2">
-        <f t="shared" si="18"/>
-        <v>174.752840000769</v>
+        <f t="shared" si="17"/>
+        <v>191.0952974970433</v>
       </c>
       <c r="C46" s="1">
         <f t="shared" si="10"/>
         <v>42</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" si="11"/>
-        <v>21</v>
+        <f t="shared" si="7"/>
+        <v>27</v>
       </c>
       <c r="E46" s="1">
         <f t="shared" si="8"/>
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="F46" s="4">
+        <f t="shared" si="11"/>
+        <v>1.3082477867037419E-3</v>
+      </c>
+      <c r="G46" s="4">
         <f t="shared" si="12"/>
-        <v>1.4305919148375492E-3</v>
-      </c>
-      <c r="G46" s="4">
+        <v>0.14259900875070786</v>
+      </c>
+      <c r="H46" s="5">
         <f t="shared" si="13"/>
-        <v>0.12160031276119168</v>
-      </c>
-      <c r="H46" s="5">
+        <v>6288</v>
+      </c>
+      <c r="I46" s="2">
         <f t="shared" si="14"/>
-        <v>5362</v>
-      </c>
-      <c r="I46" s="2">
+        <v>191.11402671755724</v>
+      </c>
+      <c r="J46" s="8">
         <f t="shared" si="15"/>
-        <v>174.77154046997387</v>
-      </c>
-      <c r="J46" s="8">
+        <v>9.8009845136193263E-5</v>
+      </c>
+      <c r="K46" s="1">
         <f t="shared" si="16"/>
-        <v>1.0701096019261058E-4</v>
-      </c>
-      <c r="K46" s="1">
-        <f t="shared" si="17"/>
-        <v>84.999999999999986</v>
+        <v>109</v>
       </c>
       <c r="L46" s="2">
         <f t="shared" si="9"/>
-        <v>252.32941176470592</v>
+        <v>230.75229357798165</v>
       </c>
     </row>
     <row r="47" spans="2:12">
       <c r="B47" s="2">
-        <f t="shared" si="18"/>
-        <v>187.38174228603907</v>
+        <f t="shared" si="17"/>
+        <v>205.3525026457138</v>
       </c>
       <c r="C47" s="1">
         <f t="shared" si="10"/>
         <v>43</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" si="11"/>
-        <v>23</v>
+        <f t="shared" si="7"/>
+        <v>29</v>
       </c>
       <c r="E47" s="1">
         <f t="shared" si="8"/>
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="F47" s="4">
+        <f t="shared" si="11"/>
+        <v>1.2174188129146625E-3</v>
+      </c>
+      <c r="G47" s="4">
         <f t="shared" si="12"/>
-        <v>1.3341748078015726E-3</v>
-      </c>
-      <c r="G47" s="4">
+        <v>0.14243800111101551</v>
+      </c>
+      <c r="H47" s="5">
         <f t="shared" si="13"/>
-        <v>0.12407825712554625</v>
-      </c>
-      <c r="H47" s="5">
+        <v>6281</v>
+      </c>
+      <c r="I47" s="2">
         <f t="shared" si="14"/>
-        <v>5471</v>
-      </c>
-      <c r="I47" s="2">
+        <v>205.36936793504219</v>
+      </c>
+      <c r="J47" s="8">
         <f t="shared" si="15"/>
-        <v>187.41089380369218</v>
-      </c>
-      <c r="J47" s="8">
+        <v>8.2128482054466545E-5</v>
+      </c>
+      <c r="K47" s="1">
         <f t="shared" si="16"/>
-        <v>1.5557288184786522E-4</v>
-      </c>
-      <c r="K47" s="1">
-        <f t="shared" si="17"/>
-        <v>92.999999999999986</v>
+        <v>117</v>
       </c>
       <c r="L47" s="2">
         <f t="shared" si="9"/>
-        <v>235.31182795698928</v>
+        <v>214.73504273504273</v>
       </c>
     </row>
     <row r="48" spans="2:12">
       <c r="B48" s="2">
-        <f t="shared" si="18"/>
-        <v>200.92330025650546</v>
+        <f t="shared" si="17"/>
+        <v>220.67340690845811</v>
       </c>
       <c r="C48" s="1">
         <f t="shared" si="10"/>
         <v>44</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" si="11"/>
-        <v>24</v>
+        <f t="shared" si="7"/>
+        <v>32</v>
       </c>
       <c r="E48" s="1">
         <f t="shared" si="8"/>
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F48" s="4">
+        <f t="shared" si="11"/>
+        <v>1.1328959094002089E-3</v>
+      </c>
+      <c r="G48" s="4">
         <f t="shared" si="12"/>
-        <v>1.244255891083023E-3</v>
-      </c>
-      <c r="G48" s="4">
+        <v>0.14614357231262695</v>
+      </c>
+      <c r="H48" s="5">
         <f t="shared" si="13"/>
-        <v>0.12069282143505324</v>
-      </c>
-      <c r="H48" s="5">
+        <v>6444</v>
+      </c>
+      <c r="I48" s="2">
         <f t="shared" si="14"/>
-        <v>5322</v>
-      </c>
-      <c r="I48" s="2">
+        <v>220.70530726256982</v>
+      </c>
+      <c r="J48" s="8">
         <f t="shared" si="15"/>
-        <v>200.94419391206316</v>
-      </c>
-      <c r="J48" s="8">
+        <v>1.4455912272626215E-4</v>
+      </c>
+      <c r="K48" s="1">
         <f t="shared" si="16"/>
-        <v>1.0398821605561714E-4</v>
-      </c>
-      <c r="K48" s="1">
-        <f t="shared" si="17"/>
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L48" s="2">
         <f t="shared" si="9"/>
-        <v>219.46391752577318</v>
+        <v>199.81395348837211</v>
       </c>
     </row>
     <row r="49" spans="2:12">
       <c r="B49" s="2">
-        <f t="shared" si="18"/>
-        <v>215.44346900318919</v>
+        <f t="shared" si="17"/>
+        <v>237.13737056616458</v>
       </c>
       <c r="C49" s="1">
         <f t="shared" si="10"/>
         <v>45</v>
       </c>
       <c r="D49" s="1">
-        <f t="shared" si="11"/>
-        <v>26</v>
+        <f t="shared" si="7"/>
+        <v>34</v>
       </c>
       <c r="E49" s="1">
         <f t="shared" si="8"/>
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="F49" s="4">
+        <f t="shared" si="11"/>
+        <v>1.0542412585714598E-3</v>
+      </c>
+      <c r="G49" s="4">
         <f t="shared" si="12"/>
-        <v>1.1603972084031904E-3</v>
-      </c>
-      <c r="G49" s="4">
+        <v>0.14443105242429</v>
+      </c>
+      <c r="H49" s="5">
         <f t="shared" si="13"/>
-        <v>0.12184170688233499</v>
-      </c>
-      <c r="H49" s="5">
+        <v>6369</v>
+      </c>
+      <c r="I49" s="2">
         <f t="shared" si="14"/>
-        <v>5373</v>
-      </c>
-      <c r="I49" s="2">
+        <v>237.15261422515309</v>
+      </c>
+      <c r="J49" s="8">
         <f t="shared" si="15"/>
-        <v>215.45226130653265</v>
-      </c>
-      <c r="J49" s="8">
+        <v>6.428197694918758E-5</v>
+      </c>
+      <c r="K49" s="1">
         <f t="shared" si="16"/>
-        <v>4.0810257020629237E-5</v>
-      </c>
-      <c r="K49" s="1">
-        <f t="shared" si="17"/>
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="L49" s="2">
         <f t="shared" si="9"/>
-        <v>204.68571428571428</v>
+        <v>185.95620437956205</v>
       </c>
     </row>
     <row r="50" spans="2:12">
       <c r="B50" s="2">
-        <f t="shared" si="18"/>
-        <v>231.01297000831687</v>
+        <f t="shared" si="17"/>
+        <v>254.82967479793362</v>
       </c>
       <c r="C50" s="1">
         <f t="shared" si="10"/>
         <v>46</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" si="11"/>
-        <v>28</v>
+        <f t="shared" si="7"/>
+        <v>37</v>
       </c>
       <c r="E50" s="1">
         <f t="shared" si="8"/>
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F50" s="4">
+        <f t="shared" si="11"/>
+        <v>9.8104743962113797E-4</v>
+      </c>
+      <c r="G50" s="4">
         <f t="shared" si="12"/>
-        <v>1.0821903202707605E-3</v>
-      </c>
-      <c r="G50" s="4">
+        <v>0.14617606850354956</v>
+      </c>
+      <c r="H50" s="5">
         <f t="shared" si="13"/>
-        <v>0.12228750619059593</v>
-      </c>
-      <c r="H50" s="5">
+        <v>6446</v>
+      </c>
+      <c r="I50" s="2">
         <f t="shared" si="14"/>
-        <v>5392</v>
-      </c>
-      <c r="I50" s="2">
+        <v>254.84408935774124</v>
+      </c>
+      <c r="J50" s="8">
         <f t="shared" si="15"/>
-        <v>231.05063056379819</v>
-      </c>
-      <c r="J50" s="8">
+        <v>5.6565467970060013E-5</v>
+      </c>
+      <c r="K50" s="1">
         <f t="shared" si="16"/>
-        <v>1.6302355439168359E-4</v>
-      </c>
-      <c r="K50" s="1">
-        <f t="shared" si="17"/>
-        <v>112.99999999999999</v>
+        <v>149</v>
       </c>
       <c r="L50" s="2">
         <f t="shared" si="9"/>
-        <v>190.86725663716817</v>
+        <v>173.04697986577182</v>
       </c>
     </row>
     <row r="51" spans="2:12">
       <c r="B51" s="2">
-        <f t="shared" si="18"/>
-        <v>247.70763559917208</v>
+        <f t="shared" si="17"/>
+        <v>273.84196342643497</v>
       </c>
       <c r="C51" s="1">
         <f t="shared" si="10"/>
         <v>47</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" si="11"/>
-        <v>30</v>
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
       <c r="E51" s="1">
         <f t="shared" si="8"/>
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="F51" s="4">
+        <f t="shared" si="11"/>
+        <v>9.1293531813709807E-4</v>
+      </c>
+      <c r="G51" s="4">
         <f t="shared" si="12"/>
-        <v>1.0092543146491347E-3</v>
-      </c>
-      <c r="G51" s="4">
+        <v>0.14698258622007279</v>
+      </c>
+      <c r="H51" s="5">
         <f t="shared" si="13"/>
-        <v>0.12211977207254529</v>
-      </c>
-      <c r="H51" s="5">
+        <v>6481</v>
+      </c>
+      <c r="I51" s="2">
         <f t="shared" si="14"/>
-        <v>5385</v>
-      </c>
-      <c r="I51" s="2">
+        <v>273.88134547137787</v>
+      </c>
+      <c r="J51" s="8">
         <f t="shared" si="15"/>
-        <v>247.7298050139276</v>
-      </c>
-      <c r="J51" s="8">
+        <v>1.4381303891530806E-4</v>
+      </c>
+      <c r="K51" s="1">
         <f t="shared" si="16"/>
-        <v>8.9498309981062008E-5</v>
-      </c>
-      <c r="K51" s="1">
-        <f t="shared" si="17"/>
-        <v>121.00000000000001</v>
+        <v>161</v>
       </c>
       <c r="L51" s="2">
         <f t="shared" si="9"/>
-        <v>178.01652892561981</v>
+        <v>161.01863354037266</v>
       </c>
     </row>
     <row r="52" spans="2:12">
       <c r="B52" s="2">
-        <f t="shared" si="18"/>
-        <v>265.60877829466972</v>
+        <f t="shared" si="17"/>
+        <v>294.27271762092693</v>
       </c>
       <c r="C52" s="1">
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" si="11"/>
-        <v>32</v>
+        <f t="shared" si="7"/>
+        <v>43</v>
       </c>
       <c r="E52" s="1">
         <f t="shared" si="8"/>
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="F52" s="4">
+        <f t="shared" si="11"/>
+        <v>8.4955208223564348E-4</v>
+      </c>
+      <c r="G52" s="4">
         <f t="shared" si="12"/>
-        <v>9.4123395169811309E-4</v>
-      </c>
-      <c r="G52" s="4">
+        <v>0.14697251022676633</v>
+      </c>
+      <c r="H52" s="5">
         <f t="shared" si="13"/>
-        <v>0.12141917976905658</v>
-      </c>
-      <c r="H52" s="5">
+        <v>6481</v>
+      </c>
+      <c r="I52" s="2">
         <f t="shared" si="14"/>
-        <v>5354</v>
-      </c>
-      <c r="I52" s="2">
+        <v>294.29486190402719</v>
+      </c>
+      <c r="J52" s="8">
         <f t="shared" si="15"/>
-        <v>265.63784086664174</v>
-      </c>
-      <c r="J52" s="8">
+        <v>7.5250887269673328E-5</v>
+      </c>
+      <c r="K52" s="1">
         <f t="shared" si="16"/>
-        <v>1.0941871785496993E-4</v>
-      </c>
-      <c r="K52" s="1">
-        <f t="shared" si="17"/>
-        <v>128.99999999999997</v>
+        <v>173.00000000000003</v>
       </c>
       <c r="L52" s="2">
         <f t="shared" si="9"/>
-        <v>166.01550387596902</v>
+        <v>149.84971098265893</v>
       </c>
     </row>
     <row r="53" spans="2:12">
       <c r="B53" s="2">
-        <f t="shared" si="18"/>
-        <v>284.80358684358134</v>
+        <f t="shared" si="17"/>
+        <v>316.22776601683654</v>
       </c>
       <c r="C53" s="1">
         <f t="shared" si="10"/>
         <v>49</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" si="11"/>
-        <v>35</v>
+        <f t="shared" si="7"/>
+        <v>46</v>
       </c>
       <c r="E53" s="1">
         <f t="shared" si="8"/>
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="F53" s="4">
+        <f t="shared" si="11"/>
+        <v>7.9056941504209832E-4</v>
+      </c>
+      <c r="G53" s="4">
         <f t="shared" si="12"/>
-        <v>8.7779793355377924E-4</v>
-      </c>
-      <c r="G53" s="4">
+        <v>0.14625534178278818</v>
+      </c>
+      <c r="H53" s="5">
         <f t="shared" si="13"/>
-        <v>0.12376950863108287</v>
-      </c>
-      <c r="H53" s="5">
+        <v>6449</v>
+      </c>
+      <c r="I53" s="2">
         <f t="shared" si="14"/>
-        <v>5458</v>
-      </c>
-      <c r="I53" s="2">
+        <v>316.26996433555593</v>
+      </c>
+      <c r="J53" s="8">
         <f t="shared" si="15"/>
-        <v>284.81586661780869</v>
-      </c>
-      <c r="J53" s="8">
+        <v>1.3344280058302793E-4</v>
+      </c>
+      <c r="K53" s="1">
         <f t="shared" si="16"/>
-        <v>4.3116641765150732E-5</v>
-      </c>
-      <c r="K53" s="1">
-        <f t="shared" si="17"/>
-        <v>140.99999999999997</v>
+        <v>185.00000000000003</v>
       </c>
       <c r="L53" s="2">
         <f t="shared" si="9"/>
-        <v>154.83687943262416</v>
+        <v>139.4378378378378</v>
       </c>
     </row>
     <row r="54" spans="2:12">
       <c r="B54" s="2">
-        <f t="shared" si="18"/>
-        <v>305.38555088334283</v>
+        <f t="shared" si="17"/>
+        <v>339.82083289425441</v>
       </c>
       <c r="C54" s="1">
         <f t="shared" si="10"/>
         <v>50</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" si="11"/>
-        <v>37</v>
+        <f t="shared" si="7"/>
+        <v>49</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="8"/>
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="F54" s="4">
+        <f t="shared" si="11"/>
+        <v>7.3568179405232375E-4</v>
+      </c>
+      <c r="G54" s="4">
         <f t="shared" si="12"/>
-        <v>8.1863729071942866E-4</v>
-      </c>
-      <c r="G54" s="4">
+        <v>0.14492931342830778</v>
+      </c>
+      <c r="H54" s="5">
         <f t="shared" si="13"/>
-        <v>0.12197695631719487</v>
-      </c>
-      <c r="H54" s="5">
+        <v>6391</v>
+      </c>
+      <c r="I54" s="2">
         <f t="shared" si="14"/>
-        <v>5379</v>
-      </c>
-      <c r="I54" s="2">
+        <v>339.84118291347204</v>
+      </c>
+      <c r="J54" s="8">
         <f t="shared" si="15"/>
-        <v>305.39598438371445</v>
-      </c>
-      <c r="J54" s="8">
+        <v>5.9884554588052197E-5</v>
+      </c>
+      <c r="K54" s="1">
         <f t="shared" si="16"/>
-        <v>3.4165009907827226E-5</v>
-      </c>
-      <c r="K54" s="1">
-        <f t="shared" si="17"/>
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="L54" s="2">
         <f t="shared" si="9"/>
-        <v>144.40268456375838</v>
+        <v>129.76649746192894</v>
       </c>
     </row>
     <row r="55" spans="2:12">
       <c r="B55" s="2">
-        <f t="shared" si="18"/>
-        <v>327.45491628777427</v>
+        <f t="shared" si="17"/>
+        <v>365.17412725483604</v>
       </c>
       <c r="C55" s="1">
         <f t="shared" si="10"/>
         <v>51</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" si="11"/>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>53</v>
       </c>
       <c r="E55" s="1">
         <f t="shared" si="8"/>
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="F55" s="4">
+        <f t="shared" si="11"/>
+        <v>6.8460490856609346E-4</v>
+      </c>
+      <c r="G55" s="4">
         <f t="shared" si="12"/>
-        <v>7.6346387720835059E-4</v>
-      </c>
-      <c r="G55" s="4">
+        <v>0.14582084552457791</v>
+      </c>
+      <c r="H55" s="5">
         <f t="shared" si="13"/>
-        <v>0.12291768423054444</v>
-      </c>
-      <c r="H55" s="5">
+        <v>6430</v>
+      </c>
+      <c r="I55" s="2">
         <f t="shared" si="14"/>
-        <v>5420</v>
-      </c>
-      <c r="I55" s="2">
+        <v>365.21384136858478</v>
+      </c>
+      <c r="J55" s="8">
         <f t="shared" si="15"/>
-        <v>327.49538745387451</v>
-      </c>
-      <c r="J55" s="8">
+        <v>1.0875390884690361E-4</v>
+      </c>
+      <c r="K55" s="1">
         <f t="shared" si="16"/>
-        <v>1.2359309354414982E-4</v>
-      </c>
-      <c r="K55" s="1">
-        <f t="shared" si="17"/>
-        <v>160.99999999999997</v>
+        <v>213</v>
       </c>
       <c r="L55" s="2">
         <f t="shared" si="9"/>
-        <v>134.65838509316774</v>
+        <v>120.75117370892019</v>
       </c>
     </row>
     <row r="56" spans="2:12">
       <c r="B56" s="2">
-        <f t="shared" si="18"/>
-        <v>351.11917342151469</v>
+        <f t="shared" si="17"/>
+        <v>392.41897584845174</v>
       </c>
       <c r="C56" s="1">
         <f t="shared" si="10"/>
         <v>52</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" si="11"/>
-        <v>43</v>
+        <f t="shared" si="7"/>
+        <v>57</v>
       </c>
       <c r="E56" s="1">
         <f t="shared" si="8"/>
-        <v>173</v>
+        <v>229</v>
       </c>
       <c r="F56" s="4">
+        <f t="shared" si="11"/>
+        <v>6.370741869948396E-4</v>
+      </c>
+      <c r="G56" s="4">
         <f t="shared" si="12"/>
-        <v>7.1200896710894726E-4</v>
-      </c>
-      <c r="G56" s="4">
+        <v>0.14588998882181828</v>
+      </c>
+      <c r="H56" s="5">
         <f t="shared" si="13"/>
-        <v>0.12317755130984788</v>
-      </c>
-      <c r="H56" s="5">
+        <v>6433</v>
+      </c>
+      <c r="I56" s="2">
         <f t="shared" si="14"/>
-        <v>5432</v>
-      </c>
-      <c r="I56" s="2">
+        <v>392.46463547334059</v>
+      </c>
+      <c r="J56" s="8">
         <f t="shared" si="15"/>
-        <v>351.1275773195876</v>
-      </c>
-      <c r="J56" s="8">
+        <v>1.1635427361822437E-4</v>
+      </c>
+      <c r="K56" s="1">
         <f t="shared" si="16"/>
-        <v>2.3934603146313904E-5</v>
-      </c>
-      <c r="K56" s="1">
-        <f t="shared" si="17"/>
-        <v>172.99999999999997</v>
+        <v>229</v>
       </c>
       <c r="L56" s="2">
         <f t="shared" si="9"/>
-        <v>125.59537572254337</v>
+        <v>112.36681222707423</v>
       </c>
     </row>
     <row r="57" spans="2:12">
       <c r="B57" s="2">
-        <f t="shared" si="18"/>
-        <v>376.49358067924851</v>
+        <f t="shared" si="17"/>
+        <v>421.69650342858023</v>
       </c>
       <c r="C57" s="1">
         <f t="shared" si="10"/>
         <v>53</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" si="11"/>
-        <v>46</v>
+        <f t="shared" si="7"/>
+        <v>61</v>
       </c>
       <c r="E57" s="1">
         <f t="shared" si="8"/>
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="F57" s="4">
+        <f t="shared" si="11"/>
+        <v>5.9284342641541666E-4</v>
+      </c>
+      <c r="G57" s="4">
         <f t="shared" si="12"/>
-        <v>6.6402194573666855E-4</v>
-      </c>
-      <c r="G57" s="4">
+        <v>0.14524663947177707</v>
+      </c>
+      <c r="H57" s="5">
         <f t="shared" si="13"/>
-        <v>0.12284405996128368</v>
-      </c>
-      <c r="H57" s="5">
+        <v>6405</v>
+      </c>
+      <c r="I57" s="2">
         <f t="shared" si="14"/>
-        <v>5417</v>
-      </c>
-      <c r="I57" s="2">
+        <v>421.72131147540983</v>
+      </c>
+      <c r="J57" s="8">
         <f t="shared" si="15"/>
-        <v>376.52298320103381</v>
-      </c>
-      <c r="J57" s="8">
+        <v>5.8829149940597958E-5</v>
+      </c>
+      <c r="K57" s="1">
         <f t="shared" si="16"/>
-        <v>7.8095678901712873E-5</v>
-      </c>
-      <c r="K57" s="1">
-        <f t="shared" si="17"/>
-        <v>185.00000000000003</v>
+        <v>245</v>
       </c>
       <c r="L57" s="2">
         <f t="shared" si="9"/>
-        <v>117.12432432432431</v>
+        <v>104.57142857142857</v>
       </c>
     </row>
     <row r="58" spans="2:12">
       <c r="B58" s="2">
-        <f t="shared" si="18"/>
-        <v>403.70172585965736</v>
+        <f t="shared" si="17"/>
+        <v>453.15836376007957</v>
       </c>
       <c r="C58" s="1">
         <f t="shared" si="10"/>
         <v>54</v>
       </c>
       <c r="D58" s="1">
-        <f t="shared" si="11"/>
-        <v>50</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="E58" s="1">
         <f t="shared" si="8"/>
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="F58" s="4">
+        <f t="shared" si="11"/>
+        <v>5.5168351727115014E-4</v>
+      </c>
+      <c r="G58" s="4">
         <f t="shared" si="12"/>
-        <v>6.1926908899792479E-4</v>
-      </c>
-      <c r="G58" s="4">
+        <v>0.14619613207685478</v>
+      </c>
+      <c r="H58" s="5">
         <f t="shared" si="13"/>
-        <v>0.12447308688858288</v>
-      </c>
-      <c r="H58" s="5">
+        <v>6447</v>
+      </c>
+      <c r="I58" s="2">
         <f t="shared" si="14"/>
-        <v>5489</v>
-      </c>
-      <c r="I58" s="2">
+        <v>453.17589576547232</v>
+      </c>
+      <c r="J58" s="8">
         <f t="shared" si="15"/>
-        <v>403.72107852067768</v>
-      </c>
-      <c r="J58" s="8">
+        <v>3.8688473599668427E-5</v>
+      </c>
+      <c r="K58" s="1">
         <f t="shared" si="16"/>
-        <v>4.7938019039017732E-5</v>
-      </c>
-      <c r="K58" s="1">
-        <f t="shared" si="17"/>
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="L58" s="2">
         <f t="shared" si="9"/>
-        <v>109.23383084577114</v>
+        <v>97.31320754716981</v>
       </c>
     </row>
     <row r="59" spans="2:12">
       <c r="B59" s="2">
-        <f t="shared" si="18"/>
-        <v>432.87612810830791</v>
+        <f t="shared" si="17"/>
+        <v>486.96752516586071</v>
       </c>
       <c r="C59" s="1">
         <f t="shared" si="10"/>
         <v>55</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" si="11"/>
-        <v>53</v>
+        <f t="shared" si="7"/>
+        <v>71</v>
       </c>
       <c r="E59" s="1">
         <f t="shared" si="8"/>
-        <v>213</v>
+        <v>285</v>
       </c>
       <c r="F59" s="4">
+        <f t="shared" si="11"/>
+        <v>5.133812566142891E-4</v>
+      </c>
+      <c r="G59" s="4">
         <f t="shared" si="12"/>
-        <v>5.7753242502078719E-4</v>
-      </c>
-      <c r="G59" s="4">
+        <v>0.14631365813507238</v>
+      </c>
+      <c r="H59" s="5">
         <f t="shared" si="13"/>
-        <v>0.12301440652942768</v>
-      </c>
-      <c r="H59" s="5">
+        <v>6452</v>
+      </c>
+      <c r="I59" s="2">
         <f t="shared" si="14"/>
-        <v>5424</v>
-      </c>
-      <c r="I59" s="2">
+        <v>487.00015499070054</v>
+      </c>
+      <c r="J59" s="8">
         <f t="shared" si="15"/>
-        <v>432.95077433628319</v>
-      </c>
-      <c r="J59" s="8">
+        <v>6.7006161917460005E-5</v>
+      </c>
+      <c r="K59" s="1">
         <f t="shared" si="16"/>
-        <v>1.7244246824477116E-4</v>
-      </c>
-      <c r="K59" s="1">
-        <f t="shared" si="17"/>
-        <v>213</v>
+        <v>285</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" si="9"/>
-        <v>101.85915492957747</v>
+        <v>90.554385964912285</v>
       </c>
     </row>
     <row r="60" spans="2:12">
       <c r="B60" s="2">
-        <f t="shared" si="18"/>
-        <v>464.15888336128017</v>
+        <f t="shared" si="17"/>
+        <v>523.29911468149203</v>
       </c>
       <c r="C60" s="1">
         <f t="shared" si="10"/>
         <v>56</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="11"/>
-        <v>57</v>
+        <f t="shared" si="7"/>
+        <v>76</v>
       </c>
       <c r="E60" s="1">
         <f t="shared" si="8"/>
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="F60" s="4">
+        <f t="shared" si="11"/>
+        <v>4.7773824374261253E-4</v>
+      </c>
+      <c r="G60" s="4">
         <f t="shared" si="12"/>
-        <v>5.3860867250796825E-4</v>
-      </c>
-      <c r="G60" s="4">
+        <v>0.14571016434149683</v>
+      </c>
+      <c r="H60" s="5">
         <f t="shared" si="13"/>
-        <v>0.12334138600432473</v>
-      </c>
-      <c r="H60" s="5">
+        <v>6425</v>
+      </c>
+      <c r="I60" s="2">
         <f t="shared" si="14"/>
-        <v>5439</v>
-      </c>
-      <c r="I60" s="2">
+        <v>523.3657587548638</v>
+      </c>
+      <c r="J60" s="8">
         <f t="shared" si="15"/>
-        <v>464.18918918918922</v>
-      </c>
-      <c r="J60" s="8">
+        <v>1.2735369027394583E-4</v>
+      </c>
+      <c r="K60" s="1">
         <f t="shared" si="16"/>
-        <v>6.5291926957478097E-5</v>
-      </c>
-      <c r="K60" s="1">
-        <f t="shared" si="17"/>
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="L60" s="2">
         <f t="shared" si="9"/>
-        <v>95.004366812227076</v>
+        <v>84.26229508196721</v>
       </c>
     </row>
     <row r="61" spans="2:12">
       <c r="B61" s="2">
-        <f t="shared" si="18"/>
-        <v>497.70235643321359</v>
+        <f t="shared" si="17"/>
+        <v>562.3413251903462</v>
       </c>
       <c r="C61" s="1">
         <f t="shared" si="10"/>
         <v>57</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" si="11"/>
-        <v>61</v>
+        <f t="shared" si="7"/>
+        <v>82</v>
       </c>
       <c r="E61" s="1">
         <f t="shared" si="8"/>
-        <v>245</v>
+        <v>329</v>
       </c>
       <c r="F61" s="4">
+        <f t="shared" si="11"/>
+        <v>4.4456985250973296E-4</v>
+      </c>
+      <c r="G61" s="4">
         <f t="shared" si="12"/>
-        <v>5.023082506412593E-4</v>
-      </c>
-      <c r="G61" s="4">
+        <v>0.14626348147570215</v>
+      </c>
+      <c r="H61" s="5">
         <f t="shared" si="13"/>
-        <v>0.12306552140710852</v>
-      </c>
-      <c r="H61" s="5">
+        <v>6450</v>
+      </c>
+      <c r="I61" s="2">
         <f t="shared" si="14"/>
-        <v>5427</v>
-      </c>
-      <c r="I61" s="2">
+        <v>562.3604651162791</v>
+      </c>
+      <c r="J61" s="8">
         <f t="shared" si="15"/>
-        <v>497.71973466003323</v>
-      </c>
-      <c r="J61" s="8">
+        <v>3.4036136196125E-5</v>
+      </c>
+      <c r="K61" s="1">
         <f t="shared" si="16"/>
-        <v>3.4916906852089369E-5</v>
-      </c>
-      <c r="K61" s="1">
-        <f t="shared" si="17"/>
-        <v>245.00000000000003</v>
+        <v>329</v>
       </c>
       <c r="L61" s="2">
         <f t="shared" si="9"/>
-        <v>88.604081632653049</v>
+        <v>78.419452887538</v>
       </c>
     </row>
     <row r="62" spans="2:12">
       <c r="B62" s="2">
-        <f t="shared" si="18"/>
-        <v>533.66992312063371</v>
+        <f t="shared" si="17"/>
+        <v>604.29639023812967</v>
       </c>
       <c r="C62" s="1">
         <f t="shared" si="10"/>
         <v>58</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" si="11"/>
-        <v>66</v>
+        <f t="shared" si="7"/>
+        <v>88</v>
       </c>
       <c r="E62" s="1">
         <f t="shared" si="8"/>
-        <v>265</v>
+        <v>353</v>
       </c>
       <c r="F62" s="4">
+        <f t="shared" si="11"/>
+        <v>4.1370427498579751E-4</v>
+      </c>
+      <c r="G62" s="4">
         <f t="shared" si="12"/>
-        <v>4.684543557150936E-4</v>
-      </c>
-      <c r="G62" s="4">
+        <v>0.14603760906998653</v>
+      </c>
+      <c r="H62" s="5">
         <f t="shared" si="13"/>
-        <v>0.12414040426449981</v>
-      </c>
-      <c r="H62" s="5">
+        <v>6440</v>
+      </c>
+      <c r="I62" s="2">
         <f t="shared" si="14"/>
-        <v>5474</v>
-      </c>
-      <c r="I62" s="2">
+        <v>604.320652173913</v>
+      </c>
+      <c r="J62" s="8">
         <f t="shared" si="15"/>
-        <v>533.72762148337597</v>
-      </c>
-      <c r="J62" s="8">
+        <v>4.0149066212080697E-5</v>
+      </c>
+      <c r="K62" s="1">
         <f t="shared" si="16"/>
-        <v>1.0811619737705058E-4</v>
-      </c>
-      <c r="K62" s="1">
-        <f t="shared" si="17"/>
-        <v>265</v>
+        <v>352.99999999999994</v>
       </c>
       <c r="L62" s="2">
         <f t="shared" si="9"/>
-        <v>82.62641509433962</v>
+        <v>72.974504249291797</v>
       </c>
     </row>
     <row r="63" spans="2:12">
       <c r="B63" s="2">
-        <f t="shared" si="18"/>
-        <v>572.23676593502478</v>
+        <f t="shared" si="17"/>
+        <v>649.38163157620784</v>
       </c>
       <c r="C63" s="1">
         <f t="shared" si="10"/>
         <v>59</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="11"/>
-        <v>71</v>
+        <f t="shared" si="7"/>
+        <v>95</v>
       </c>
       <c r="E63" s="1">
         <f t="shared" si="8"/>
-        <v>285</v>
+        <v>381</v>
       </c>
       <c r="F63" s="4">
+        <f t="shared" si="11"/>
+        <v>3.8498163151487507E-4</v>
+      </c>
+      <c r="G63" s="4">
         <f t="shared" si="12"/>
-        <v>4.3688210000191862E-4</v>
-      </c>
-      <c r="G63" s="4">
+        <v>0.1466780016071674</v>
+      </c>
+      <c r="H63" s="5">
         <f t="shared" si="13"/>
-        <v>0.12451139850054681</v>
-      </c>
-      <c r="H63" s="5">
+        <v>6468</v>
+      </c>
+      <c r="I63" s="2">
         <f t="shared" si="14"/>
-        <v>5490</v>
-      </c>
-      <c r="I63" s="2">
+        <v>649.43181818181813</v>
+      </c>
+      <c r="J63" s="8">
         <f t="shared" si="15"/>
-        <v>572.3360655737705</v>
-      </c>
-      <c r="J63" s="8">
+        <v>7.7283685232076849E-5</v>
+      </c>
+      <c r="K63" s="1">
         <f t="shared" si="16"/>
-        <v>1.7352893881872333E-4</v>
-      </c>
-      <c r="K63" s="1">
-        <f t="shared" si="17"/>
-        <v>285</v>
+        <v>381</v>
       </c>
       <c r="L63" s="2">
         <f t="shared" si="9"/>
-        <v>77.05263157894737</v>
+        <v>67.905511811023615</v>
       </c>
     </row>
     <row r="64" spans="2:12">
       <c r="B64" s="2">
-        <f t="shared" si="18"/>
-        <v>613.59072734132064</v>
+        <f t="shared" si="17"/>
+        <v>697.8305848598626</v>
       </c>
       <c r="C64" s="1">
         <f t="shared" si="10"/>
         <v>60</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" si="11"/>
-        <v>76</v>
+        <f t="shared" si="7"/>
+        <v>102</v>
       </c>
       <c r="E64" s="1">
         <f t="shared" si="8"/>
-        <v>305</v>
+        <v>409</v>
       </c>
       <c r="F64" s="4">
+        <f t="shared" si="11"/>
+        <v>3.5825314255924262E-4</v>
+      </c>
+      <c r="G64" s="4">
         <f t="shared" si="12"/>
-        <v>4.0743770865515883E-4</v>
-      </c>
-      <c r="G64" s="4">
+        <v>0.14652553530673024</v>
+      </c>
+      <c r="H64" s="5">
         <f t="shared" si="13"/>
-        <v>0.12426850113982345</v>
-      </c>
-      <c r="H64" s="5">
+        <v>6461</v>
+      </c>
+      <c r="I64" s="2">
         <f t="shared" si="14"/>
-        <v>5480</v>
-      </c>
-      <c r="I64" s="2">
+        <v>697.9144095341278</v>
+      </c>
+      <c r="J64" s="8">
         <f t="shared" si="15"/>
-        <v>613.61770072992704</v>
-      </c>
-      <c r="J64" s="8">
+        <v>1.2012181191800586E-4</v>
+      </c>
+      <c r="K64" s="1">
         <f t="shared" si="16"/>
-        <v>4.3959902593870837E-5</v>
-      </c>
-      <c r="K64" s="1">
-        <f t="shared" si="17"/>
-        <v>305</v>
+        <v>409</v>
       </c>
       <c r="L64" s="2">
         <f t="shared" si="9"/>
-        <v>71.868852459016395</v>
+        <v>63.188264058679707</v>
       </c>
     </row>
     <row r="65" spans="2:12">
       <c r="B65" s="2">
-        <f t="shared" si="18"/>
-        <v>657.9332246575716</v>
+        <f t="shared" si="17"/>
+        <v>749.89420933245174</v>
       </c>
       <c r="C65" s="1">
         <f t="shared" si="10"/>
         <v>61</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" si="11"/>
-        <v>81</v>
+        <f t="shared" si="7"/>
+        <v>110</v>
       </c>
       <c r="E65" s="1">
         <f t="shared" si="8"/>
-        <v>325</v>
+        <v>441</v>
       </c>
       <c r="F65" s="4">
+        <f t="shared" si="11"/>
+        <v>3.333803580408328E-4</v>
+      </c>
+      <c r="G65" s="4">
         <f t="shared" si="12"/>
-        <v>3.7997777073823136E-4</v>
-      </c>
-      <c r="G65" s="4">
+        <v>0.14702073789600725</v>
+      </c>
+      <c r="H65" s="5">
         <f t="shared" si="13"/>
-        <v>0.1234927754899252</v>
-      </c>
-      <c r="H65" s="5">
+        <v>6483</v>
+      </c>
+      <c r="I65" s="2">
         <f t="shared" si="14"/>
-        <v>5446</v>
-      </c>
-      <c r="I65" s="2">
+        <v>749.96529384544192</v>
+      </c>
+      <c r="J65" s="8">
         <f t="shared" si="15"/>
-        <v>657.93701799485859</v>
-      </c>
-      <c r="J65" s="8">
+        <v>9.4792721567316107E-5</v>
+      </c>
+      <c r="K65" s="1">
         <f t="shared" si="16"/>
-        <v>5.7655353837837708E-6</v>
-      </c>
-      <c r="K65" s="1">
-        <f t="shared" si="17"/>
-        <v>325</v>
+        <v>441</v>
       </c>
       <c r="L65" s="2">
         <f t="shared" si="9"/>
-        <v>67.027692307692305</v>
+        <v>58.802721088435376</v>
       </c>
     </row>
     <row r="66" spans="2:12">
       <c r="B66" s="2">
-        <f t="shared" si="18"/>
-        <v>705.48023107186827</v>
+        <f t="shared" si="17"/>
+        <v>805.84218776147736</v>
       </c>
       <c r="C66" s="1">
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" si="11"/>
-        <v>87</v>
+        <f t="shared" si="7"/>
+        <v>118</v>
       </c>
       <c r="E66" s="1">
         <f t="shared" si="8"/>
-        <v>349</v>
+        <v>473</v>
       </c>
       <c r="F66" s="4">
+        <f t="shared" si="11"/>
+        <v>3.1023444018793162E-4</v>
+      </c>
+      <c r="G66" s="4">
         <f t="shared" si="12"/>
-        <v>3.543685407316993E-4</v>
-      </c>
-      <c r="G66" s="4">
+        <v>0.14674089020889167</v>
+      </c>
+      <c r="H66" s="5">
         <f t="shared" si="13"/>
-        <v>0.12367462071536306</v>
-      </c>
-      <c r="H66" s="5">
+        <v>6471</v>
+      </c>
+      <c r="I66" s="2">
         <f t="shared" si="14"/>
-        <v>5454</v>
-      </c>
-      <c r="I66" s="2">
+        <v>805.87621696801102</v>
+      </c>
+      <c r="J66" s="8">
         <f t="shared" si="15"/>
-        <v>705.486798679868</v>
-      </c>
-      <c r="J66" s="8">
+        <v>4.2228127355992129E-5</v>
+      </c>
+      <c r="K66" s="1">
         <f t="shared" si="16"/>
-        <v>9.3094146518257759E-6</v>
-      </c>
-      <c r="K66" s="1">
-        <f t="shared" si="17"/>
-        <v>349</v>
+        <v>472.99999999999994</v>
       </c>
       <c r="L66" s="2">
         <f t="shared" si="9"/>
-        <v>62.51002865329513</v>
+        <v>54.723044397463006</v>
       </c>
     </row>
     <row r="67" spans="2:12">
       <c r="B67" s="2">
-        <f t="shared" si="18"/>
-        <v>756.46332755463322</v>
+        <f t="shared" si="17"/>
+        <v>865.96432336006046</v>
       </c>
       <c r="C67" s="1">
         <f t="shared" si="10"/>
         <v>63</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" si="11"/>
-        <v>94</v>
+        <f t="shared" si="7"/>
+        <v>127</v>
       </c>
       <c r="E67" s="1">
         <f t="shared" si="8"/>
-        <v>377</v>
+        <v>509</v>
       </c>
       <c r="F67" s="4">
+        <f t="shared" si="11"/>
+        <v>2.8869549617236616E-4</v>
+      </c>
+      <c r="G67" s="4">
         <f t="shared" si="12"/>
-        <v>3.3048528711650537E-4</v>
-      </c>
-      <c r="G67" s="4">
+        <v>0.14694600755173437</v>
+      </c>
+      <c r="H67" s="5">
         <f t="shared" si="13"/>
-        <v>0.12459295324292252</v>
-      </c>
-      <c r="H67" s="5">
+        <v>6480</v>
+      </c>
+      <c r="I67" s="2">
         <f t="shared" si="14"/>
-        <v>5494</v>
-      </c>
-      <c r="I67" s="2">
+        <v>866.00694444444446</v>
+      </c>
+      <c r="J67" s="8">
         <f t="shared" si="15"/>
-        <v>756.53895158354567</v>
-      </c>
-      <c r="J67" s="8">
+        <v>4.9218060414579767E-5</v>
+      </c>
+      <c r="K67" s="1">
         <f t="shared" si="16"/>
-        <v>9.9970515632152868E-5</v>
-      </c>
-      <c r="K67" s="1">
-        <f t="shared" si="17"/>
-        <v>377</v>
+        <v>509</v>
       </c>
       <c r="L67" s="2">
         <f t="shared" si="9"/>
-        <v>58.291777188328915</v>
+        <v>50.923379174852656</v>
       </c>
     </row>
     <row r="68" spans="2:12">
       <c r="B68" s="2">
-        <f t="shared" si="18"/>
-        <v>811.1308307896918</v>
+        <f t="shared" si="17"/>
+        <v>930.57204092969369</v>
       </c>
       <c r="C68" s="1">
         <f t="shared" si="10"/>
         <v>64</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="11"/>
-        <v>101</v>
+        <f t="shared" si="7"/>
+        <v>136</v>
       </c>
       <c r="E68" s="1">
         <f t="shared" si="8"/>
-        <v>405</v>
+        <v>545</v>
       </c>
       <c r="F68" s="4">
+        <f t="shared" si="11"/>
+        <v>2.6865195708033091E-4</v>
+      </c>
+      <c r="G68" s="4">
         <f t="shared" si="12"/>
-        <v>3.0821168486051473E-4</v>
-      </c>
-      <c r="G68" s="4">
+        <v>0.14641531660878035</v>
+      </c>
+      <c r="H68" s="5">
         <f t="shared" si="13"/>
-        <v>0.12482573236850847</v>
-      </c>
-      <c r="H68" s="5">
+        <v>6456</v>
+      </c>
+      <c r="I68" s="2">
         <f t="shared" si="14"/>
-        <v>5504</v>
-      </c>
-      <c r="I68" s="2">
+        <v>930.7039962825279</v>
+      </c>
+      <c r="J68" s="8">
         <f t="shared" si="15"/>
-        <v>811.25090843023258</v>
-      </c>
-      <c r="J68" s="8">
+        <v>1.4180025514454186E-4</v>
+      </c>
+      <c r="K68" s="1">
         <f t="shared" si="16"/>
-        <v>1.4803732762058708E-4</v>
-      </c>
-      <c r="K68" s="1">
-        <f t="shared" si="17"/>
-        <v>405</v>
+        <v>545</v>
       </c>
       <c r="L68" s="2">
         <f t="shared" si="9"/>
-        <v>54.360493827160496</v>
+        <v>47.383486238532107</v>
       </c>
     </row>
     <row r="69" spans="2:12">
       <c r="B69" s="2">
-        <f t="shared" si="18"/>
-        <v>869.74900261778851</v>
+        <f t="shared" si="17"/>
+        <v>999.9999999999942</v>
       </c>
       <c r="C69" s="1">
         <f t="shared" si="10"/>
         <v>65</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" ref="D69:D104" si="19">INT((B69/2-1)/4)</f>
-        <v>108</v>
+        <f t="shared" si="7"/>
+        <v>146</v>
       </c>
       <c r="E69" s="1">
         <f t="shared" si="8"/>
-        <v>433</v>
+        <v>585</v>
       </c>
       <c r="F69" s="4">
-        <f t="shared" ref="F69:F104" si="20">1/B69/4</f>
-        <v>2.8743924884943223E-4</v>
+        <f t="shared" ref="F69:F95" si="18">1/B69/4</f>
+        <v>2.5000000000000147E-4</v>
       </c>
       <c r="G69" s="4">
-        <f t="shared" ref="G69:G100" si="21">E69*F69</f>
-        <v>0.12446119475180416</v>
+        <f t="shared" ref="G69:G95" si="19">E69*F69</f>
+        <v>0.14625000000000085</v>
       </c>
       <c r="H69" s="5">
-        <f t="shared" ref="H69:H100" si="22">INT(G69*_rate)</f>
-        <v>5488</v>
+        <f t="shared" ref="H69:H95" si="20">INT(G69*_rate)</f>
+        <v>6449</v>
       </c>
       <c r="I69" s="2">
-        <f t="shared" ref="I69:I100" si="23">E69/H69/4*_rate</f>
-        <v>869.86607142857144</v>
+        <f t="shared" ref="I69:I95" si="21">E69/H69/4*_rate</f>
+        <v>1000.0969142502714</v>
       </c>
       <c r="J69" s="8">
-        <f t="shared" ref="J69:J100" si="24">(I69/B69-1)</f>
-        <v>1.3460068414050674E-4</v>
+        <f t="shared" ref="J69:J95" si="22">(I69/B69-1)</f>
+        <v>9.6914250277135849E-5</v>
       </c>
       <c r="K69" s="1">
-        <f t="shared" ref="K69:K104" si="25">4*I69*H69/_rate</f>
-        <v>433</v>
+        <f t="shared" ref="K69:K95" si="23">4*I69*H69/_rate</f>
+        <v>585</v>
       </c>
       <c r="L69" s="2">
         <f t="shared" si="9"/>
-        <v>50.697459584295615</v>
+        <v>44.095726495726495</v>
       </c>
     </row>
     <row r="70" spans="2:12">
       <c r="B70" s="2">
-        <f t="shared" ref="B70:B104" si="26">B69*_mult</f>
-        <v>932.60334688322553</v>
+        <f t="shared" ref="B70:B101" si="24">B69*_mult</f>
+        <v>1074.6078283213112</v>
       </c>
       <c r="C70" s="1">
         <f t="shared" si="10"/>
         <v>66</v>
       </c>
       <c r="D70" s="1">
+        <f t="shared" ref="D70:D95" si="25">INT((B70/1.7-1)/4)</f>
+        <v>157</v>
+      </c>
+      <c r="E70" s="1">
+        <f t="shared" ref="E70:E95" si="26">4*D70+1</f>
+        <v>629</v>
+      </c>
+      <c r="F70" s="4">
+        <f t="shared" si="18"/>
+        <v>2.3264301023242611E-4</v>
+      </c>
+      <c r="G70" s="4">
         <f t="shared" si="19"/>
-        <v>116</v>
-      </c>
-      <c r="E70" s="1">
-        <f t="shared" ref="E70:E104" si="27">4*D70+1</f>
-        <v>465</v>
-      </c>
-      <c r="F70" s="4">
+        <v>0.14633245343619602</v>
+      </c>
+      <c r="H70" s="5">
         <f t="shared" si="20"/>
-        <v>2.6806680550257921E-4</v>
-      </c>
-      <c r="G70" s="4">
+        <v>6453</v>
+      </c>
+      <c r="I70" s="2">
         <f t="shared" si="21"/>
-        <v>0.12465106455869933</v>
-      </c>
-      <c r="H70" s="5">
+        <v>1074.6513249651325</v>
+      </c>
+      <c r="J70" s="8">
         <f t="shared" si="22"/>
-        <v>5497</v>
-      </c>
-      <c r="I70" s="2">
+        <v>4.0476760614360785E-5</v>
+      </c>
+      <c r="K70" s="1">
         <f t="shared" si="23"/>
-        <v>932.62233945788614</v>
-      </c>
-      <c r="J70" s="8">
-        <f t="shared" si="24"/>
-        <v>2.0365115270148948E-5</v>
-      </c>
-      <c r="K70" s="1">
-        <f t="shared" si="25"/>
-        <v>465</v>
+        <v>629</v>
       </c>
       <c r="L70" s="2">
-        <f t="shared" ref="L70:L104" si="28">4*H70/K70</f>
-        <v>47.286021505376347</v>
+        <f t="shared" ref="L70:L95" si="27">4*H70/K70</f>
+        <v>41.036565977742448</v>
       </c>
     </row>
     <row r="71" spans="2:12">
       <c r="B71" s="2">
+        <f t="shared" si="24"/>
+        <v>1154.7819846894513</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" ref="C71:C101" si="28">C70+1</f>
+        <v>67</v>
+      </c>
+      <c r="D71" s="1">
+        <f t="shared" si="25"/>
+        <v>169</v>
+      </c>
+      <c r="E71" s="1">
         <f t="shared" si="26"/>
-        <v>1000.0000000000061</v>
-      </c>
-      <c r="C71" s="1">
-        <f t="shared" ref="C71:C104" si="29">C70+1</f>
-        <v>67</v>
-      </c>
-      <c r="D71" s="1">
+        <v>677</v>
+      </c>
+      <c r="F71" s="4">
+        <f t="shared" si="18"/>
+        <v>2.1649108084001762E-4</v>
+      </c>
+      <c r="G71" s="4">
         <f t="shared" si="19"/>
-        <v>124</v>
-      </c>
-      <c r="E71" s="1">
+        <v>0.14656446172869192</v>
+      </c>
+      <c r="H71" s="5">
+        <f t="shared" si="20"/>
+        <v>6463</v>
+      </c>
+      <c r="I71" s="2">
+        <f t="shared" si="21"/>
+        <v>1154.8700293981124</v>
+      </c>
+      <c r="J71" s="8">
+        <f t="shared" si="22"/>
+        <v>7.6243576561108028E-5</v>
+      </c>
+      <c r="K71" s="1">
+        <f t="shared" si="23"/>
+        <v>677</v>
+      </c>
+      <c r="L71" s="2">
         <f t="shared" si="27"/>
-        <v>497</v>
-      </c>
-      <c r="F71" s="4">
-        <f t="shared" si="20"/>
-        <v>2.4999999999999849E-4</v>
-      </c>
-      <c r="G71" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12424999999999925</v>
-      </c>
-      <c r="H71" s="5">
-        <f t="shared" si="22"/>
-        <v>5479</v>
-      </c>
-      <c r="I71" s="2">
-        <f t="shared" si="23"/>
-        <v>1000.0775688994341</v>
-      </c>
-      <c r="J71" s="8">
-        <f t="shared" si="24"/>
-        <v>7.7568899427893356E-5</v>
-      </c>
-      <c r="K71" s="1">
-        <f t="shared" si="25"/>
-        <v>497</v>
-      </c>
-      <c r="L71" s="2">
-        <f t="shared" si="28"/>
-        <v>44.096579476861166</v>
+        <v>38.186115214180205</v>
       </c>
     </row>
     <row r="72" spans="2:12">
       <c r="B72" s="2">
+        <f t="shared" si="24"/>
+        <v>1240.9377607517119</v>
+      </c>
+      <c r="C72" s="1">
+        <f t="shared" si="28"/>
+        <v>68</v>
+      </c>
+      <c r="D72" s="1">
+        <f t="shared" si="25"/>
+        <v>182</v>
+      </c>
+      <c r="E72" s="1">
         <f t="shared" si="26"/>
-        <v>1072.26722201033</v>
-      </c>
-      <c r="C72" s="1">
-        <f t="shared" si="29"/>
-        <v>68</v>
-      </c>
-      <c r="D72" s="1">
+        <v>729</v>
+      </c>
+      <c r="F72" s="4">
+        <f t="shared" si="18"/>
+        <v>2.0146054694037169E-4</v>
+      </c>
+      <c r="G72" s="4">
         <f t="shared" si="19"/>
-        <v>133</v>
-      </c>
-      <c r="E72" s="1">
+        <v>0.14686473871953096</v>
+      </c>
+      <c r="H72" s="5">
+        <f t="shared" si="20"/>
+        <v>6476</v>
+      </c>
+      <c r="I72" s="2">
+        <f t="shared" si="21"/>
+        <v>1241.0785978999381</v>
+      </c>
+      <c r="J72" s="8">
+        <f t="shared" si="22"/>
+        <v>1.1349251564474194E-4</v>
+      </c>
+      <c r="K72" s="1">
+        <f t="shared" si="23"/>
+        <v>728.99999999999989</v>
+      </c>
+      <c r="L72" s="2">
         <f t="shared" si="27"/>
-        <v>533</v>
-      </c>
-      <c r="F72" s="4">
-        <f t="shared" si="20"/>
-        <v>2.3315083672080349E-4</v>
-      </c>
-      <c r="G72" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12426939597218825</v>
-      </c>
-      <c r="H72" s="5">
-        <f t="shared" si="22"/>
-        <v>5480</v>
-      </c>
-      <c r="I72" s="2">
-        <f t="shared" si="23"/>
-        <v>1072.3220802919707</v>
-      </c>
-      <c r="J72" s="8">
-        <f t="shared" si="24"/>
-        <v>5.1161017062373304E-5</v>
-      </c>
-      <c r="K72" s="1">
-        <f t="shared" si="25"/>
-        <v>532.99999999999989</v>
-      </c>
-      <c r="L72" s="2">
-        <f t="shared" si="28"/>
-        <v>41.125703564727964</v>
+        <v>35.533607681755832</v>
       </c>
     </row>
     <row r="73" spans="2:12">
       <c r="B73" s="2">
+        <f t="shared" si="24"/>
+        <v>1333.5214321633157</v>
+      </c>
+      <c r="C73" s="1">
+        <f t="shared" si="28"/>
+        <v>69</v>
+      </c>
+      <c r="D73" s="1">
+        <f t="shared" si="25"/>
+        <v>195</v>
+      </c>
+      <c r="E73" s="1">
         <f t="shared" si="26"/>
-        <v>1149.7569953977431</v>
-      </c>
-      <c r="C73" s="1">
-        <f t="shared" si="29"/>
-        <v>69</v>
-      </c>
-      <c r="D73" s="1">
+        <v>781</v>
+      </c>
+      <c r="F73" s="4">
+        <f t="shared" si="18"/>
+        <v>1.8747355233311513E-4</v>
+      </c>
+      <c r="G73" s="4">
         <f t="shared" si="19"/>
-        <v>143</v>
-      </c>
-      <c r="E73" s="1">
+        <v>0.14641684437216293</v>
+      </c>
+      <c r="H73" s="5">
+        <f t="shared" si="20"/>
+        <v>6456</v>
+      </c>
+      <c r="I73" s="2">
+        <f t="shared" si="21"/>
+        <v>1333.7244423791822</v>
+      </c>
+      <c r="J73" s="8">
+        <f t="shared" si="22"/>
+        <v>1.522361853136811E-4</v>
+      </c>
+      <c r="K73" s="1">
+        <f t="shared" si="23"/>
+        <v>781</v>
+      </c>
+      <c r="L73" s="2">
         <f t="shared" si="27"/>
-        <v>573</v>
-      </c>
-      <c r="F73" s="4">
-        <f t="shared" si="20"/>
-        <v>2.1743725065444445E-4</v>
-      </c>
-      <c r="G73" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12459154462499666</v>
-      </c>
-      <c r="H73" s="5">
-        <f t="shared" si="22"/>
-        <v>5494</v>
-      </c>
-      <c r="I73" s="2">
-        <f t="shared" si="23"/>
-        <v>1149.8589370222062</v>
-      </c>
-      <c r="J73" s="8">
-        <f t="shared" si="24"/>
-        <v>8.8663626202079016E-5</v>
-      </c>
-      <c r="K73" s="1">
-        <f t="shared" si="25"/>
-        <v>573.00000000000011</v>
-      </c>
-      <c r="L73" s="2">
-        <f t="shared" si="28"/>
-        <v>38.352530541012207</v>
+        <v>33.065300896286814</v>
       </c>
     </row>
     <row r="74" spans="2:12">
       <c r="B74" s="2">
+        <f t="shared" si="24"/>
+        <v>1433.0125702369537</v>
+      </c>
+      <c r="C74" s="1">
+        <f t="shared" si="28"/>
+        <v>70</v>
+      </c>
+      <c r="D74" s="1">
+        <f t="shared" si="25"/>
+        <v>210</v>
+      </c>
+      <c r="E74" s="1">
         <f t="shared" si="26"/>
-        <v>1232.8467394420741</v>
-      </c>
-      <c r="C74" s="1">
-        <f t="shared" si="29"/>
-        <v>70</v>
-      </c>
-      <c r="D74" s="1">
+        <v>841</v>
+      </c>
+      <c r="F74" s="4">
+        <f t="shared" si="18"/>
+        <v>1.7445764621496767E-4</v>
+      </c>
+      <c r="G74" s="4">
         <f t="shared" si="19"/>
-        <v>153</v>
-      </c>
-      <c r="E74" s="1">
+        <v>0.1467188804667878</v>
+      </c>
+      <c r="H74" s="5">
+        <f t="shared" si="20"/>
+        <v>6470</v>
+      </c>
+      <c r="I74" s="2">
+        <f t="shared" si="21"/>
+        <v>1433.0795981452861</v>
+      </c>
+      <c r="J74" s="8">
+        <f t="shared" si="22"/>
+        <v>4.6774124473625278E-5</v>
+      </c>
+      <c r="K74" s="1">
+        <f t="shared" si="23"/>
+        <v>841.00000000000011</v>
+      </c>
+      <c r="L74" s="2">
         <f t="shared" si="27"/>
-        <v>613</v>
-      </c>
-      <c r="F74" s="4">
-        <f t="shared" si="20"/>
-        <v>2.0278270769742048E-4</v>
-      </c>
-      <c r="G74" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12430579981851875</v>
-      </c>
-      <c r="H74" s="5">
-        <f t="shared" si="22"/>
-        <v>5481</v>
-      </c>
-      <c r="I74" s="2">
-        <f t="shared" si="23"/>
-        <v>1233.0459770114944</v>
-      </c>
-      <c r="J74" s="8">
-        <f t="shared" si="24"/>
-        <v>1.6160773520845773E-4</v>
-      </c>
-      <c r="K74" s="1">
-        <f t="shared" si="25"/>
-        <v>613.00000000000011</v>
-      </c>
-      <c r="L74" s="2">
-        <f t="shared" si="28"/>
-        <v>35.765089722675363</v>
+        <v>30.772889417360282</v>
       </c>
     </row>
     <row r="75" spans="2:12">
       <c r="B75" s="2">
+        <f t="shared" si="24"/>
+        <v>1539.9265260594821</v>
+      </c>
+      <c r="C75" s="1">
+        <f t="shared" si="28"/>
+        <v>71</v>
+      </c>
+      <c r="D75" s="1">
+        <f t="shared" si="25"/>
+        <v>226</v>
+      </c>
+      <c r="E75" s="1">
         <f t="shared" si="26"/>
-        <v>1321.9411484660377</v>
-      </c>
-      <c r="C75" s="1">
-        <f t="shared" si="29"/>
-        <v>71</v>
-      </c>
-      <c r="D75" s="1">
+        <v>905</v>
+      </c>
+      <c r="F75" s="4">
+        <f t="shared" si="18"/>
+        <v>1.6234540789405387E-4</v>
+      </c>
+      <c r="G75" s="4">
         <f t="shared" si="19"/>
-        <v>164</v>
-      </c>
-      <c r="E75" s="1">
+        <v>0.14692259414411873</v>
+      </c>
+      <c r="H75" s="5">
+        <f t="shared" si="20"/>
+        <v>6479</v>
+      </c>
+      <c r="I75" s="2">
+        <f t="shared" si="21"/>
+        <v>1539.9945979317795</v>
+      </c>
+      <c r="J75" s="8">
+        <f t="shared" si="22"/>
+        <v>4.4204623496968409E-5</v>
+      </c>
+      <c r="K75" s="1">
+        <f t="shared" si="23"/>
+        <v>905</v>
+      </c>
+      <c r="L75" s="2">
         <f t="shared" si="27"/>
-        <v>657</v>
-      </c>
-      <c r="F75" s="4">
-        <f t="shared" si="20"/>
-        <v>1.8911583188865598E-4</v>
-      </c>
-      <c r="G75" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12424910155084698</v>
-      </c>
-      <c r="H75" s="5">
-        <f t="shared" si="22"/>
-        <v>5479</v>
-      </c>
-      <c r="I75" s="2">
-        <f t="shared" si="23"/>
-        <v>1322.0341303157509</v>
-      </c>
-      <c r="J75" s="8">
-        <f t="shared" si="24"/>
-        <v>7.0337359436178915E-5</v>
-      </c>
-      <c r="K75" s="1">
-        <f t="shared" si="25"/>
-        <v>656.99999999999989</v>
-      </c>
-      <c r="L75" s="2">
-        <f t="shared" si="28"/>
-        <v>33.357686453576868</v>
+        <v>28.636464088397791</v>
       </c>
     </row>
     <row r="76" spans="2:12">
       <c r="B76" s="2">
+        <f t="shared" si="24"/>
+        <v>1654.8170999431707</v>
+      </c>
+      <c r="C76" s="1">
+        <f t="shared" si="28"/>
+        <v>72</v>
+      </c>
+      <c r="D76" s="1">
+        <f t="shared" si="25"/>
+        <v>243</v>
+      </c>
+      <c r="E76" s="1">
         <f t="shared" si="26"/>
-        <v>1417.4741629268146</v>
-      </c>
-      <c r="C76" s="1">
-        <f t="shared" si="29"/>
-        <v>72</v>
-      </c>
-      <c r="D76" s="1">
+        <v>973</v>
+      </c>
+      <c r="F76" s="4">
+        <f t="shared" si="18"/>
+        <v>1.5107409755953419E-4</v>
+      </c>
+      <c r="G76" s="4">
         <f t="shared" si="19"/>
-        <v>176</v>
-      </c>
-      <c r="E76" s="1">
+        <v>0.14699509692542678</v>
+      </c>
+      <c r="H76" s="5">
+        <f t="shared" si="20"/>
+        <v>6482</v>
+      </c>
+      <c r="I76" s="2">
+        <f t="shared" si="21"/>
+        <v>1654.9406047516197</v>
+      </c>
+      <c r="J76" s="8">
+        <f t="shared" si="22"/>
+        <v>7.4633509922872321E-5</v>
+      </c>
+      <c r="K76" s="1">
+        <f t="shared" si="23"/>
+        <v>973</v>
+      </c>
+      <c r="L76" s="2">
         <f t="shared" si="27"/>
-        <v>705</v>
-      </c>
-      <c r="F76" s="4">
-        <f t="shared" si="20"/>
-        <v>1.7637005776796491E-4</v>
-      </c>
-      <c r="G76" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12434089072641526</v>
-      </c>
-      <c r="H76" s="5">
-        <f t="shared" si="22"/>
-        <v>5483</v>
-      </c>
-      <c r="I76" s="2">
-        <f t="shared" si="23"/>
-        <v>1417.5861754513951</v>
-      </c>
-      <c r="J76" s="8">
-        <f t="shared" si="24"/>
-        <v>7.9022621723989772E-5</v>
-      </c>
-      <c r="K76" s="1">
-        <f t="shared" si="25"/>
-        <v>704.99999999999989</v>
-      </c>
-      <c r="L76" s="2">
-        <f t="shared" si="28"/>
-        <v>31.109219858156035</v>
+        <v>26.647482014388491</v>
       </c>
     </row>
     <row r="77" spans="2:12">
       <c r="B77" s="2">
+        <f t="shared" si="24"/>
+        <v>1778.279410038911</v>
+      </c>
+      <c r="C77" s="1">
+        <f t="shared" si="28"/>
+        <v>73</v>
+      </c>
+      <c r="D77" s="1">
+        <f t="shared" si="25"/>
+        <v>261</v>
+      </c>
+      <c r="E77" s="1">
         <f t="shared" si="26"/>
-        <v>1519.9110829529441</v>
-      </c>
-      <c r="C77" s="1">
-        <f t="shared" si="29"/>
-        <v>73</v>
-      </c>
-      <c r="D77" s="1">
+        <v>1045</v>
+      </c>
+      <c r="F77" s="4">
+        <f t="shared" si="18"/>
+        <v>1.405853312975882E-4</v>
+      </c>
+      <c r="G77" s="4">
         <f t="shared" si="19"/>
-        <v>189</v>
-      </c>
-      <c r="E77" s="1">
+        <v>0.14691167120597967</v>
+      </c>
+      <c r="H77" s="5">
+        <f t="shared" si="20"/>
+        <v>6478</v>
+      </c>
+      <c r="I77" s="2">
+        <f t="shared" si="21"/>
+        <v>1778.5003087372647</v>
+      </c>
+      <c r="J77" s="8">
+        <f t="shared" si="22"/>
+        <v>1.2422046676507925E-4</v>
+      </c>
+      <c r="K77" s="1">
+        <f t="shared" si="23"/>
+        <v>1045</v>
+      </c>
+      <c r="L77" s="2">
         <f t="shared" si="27"/>
-        <v>757</v>
-      </c>
-      <c r="F77" s="4">
-        <f t="shared" si="20"/>
-        <v>1.6448330616439087E-4</v>
-      </c>
-      <c r="G77" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12451386276644388</v>
-      </c>
-      <c r="H77" s="5">
-        <f t="shared" si="22"/>
-        <v>5491</v>
-      </c>
-      <c r="I77" s="2">
-        <f t="shared" si="23"/>
-        <v>1519.928064104899</v>
-      </c>
-      <c r="J77" s="8">
-        <f t="shared" si="24"/>
-        <v>1.1172464064124199E-5</v>
-      </c>
-      <c r="K77" s="1">
-        <f t="shared" si="25"/>
-        <v>757.00000000000011</v>
-      </c>
-      <c r="L77" s="2">
-        <f t="shared" si="28"/>
-        <v>29.014531043593127</v>
+        <v>24.796172248803828</v>
       </c>
     </row>
     <row r="78" spans="2:12">
       <c r="B78" s="2">
+        <f t="shared" si="24"/>
+        <v>1910.9529749704277</v>
+      </c>
+      <c r="C78" s="1">
+        <f t="shared" si="28"/>
+        <v>74</v>
+      </c>
+      <c r="D78" s="1">
+        <f t="shared" si="25"/>
+        <v>280</v>
+      </c>
+      <c r="E78" s="1">
         <f t="shared" si="26"/>
-        <v>1629.7508346206555</v>
-      </c>
-      <c r="C78" s="1">
-        <f t="shared" si="29"/>
-        <v>74</v>
-      </c>
-      <c r="D78" s="1">
+        <v>1121</v>
+      </c>
+      <c r="F78" s="4">
+        <f t="shared" si="18"/>
+        <v>1.3082477867037455E-4</v>
+      </c>
+      <c r="G78" s="4">
         <f t="shared" si="19"/>
-        <v>203</v>
-      </c>
-      <c r="E78" s="1">
+        <v>0.14665457688948988</v>
+      </c>
+      <c r="H78" s="5">
+        <f t="shared" si="20"/>
+        <v>6467</v>
+      </c>
+      <c r="I78" s="2">
+        <f t="shared" si="21"/>
+        <v>1911.0909231482913</v>
+      </c>
+      <c r="J78" s="8">
+        <f t="shared" si="22"/>
+        <v>7.2188159347952308E-5</v>
+      </c>
+      <c r="K78" s="1">
+        <f t="shared" si="23"/>
+        <v>1121</v>
+      </c>
+      <c r="L78" s="2">
         <f t="shared" si="27"/>
-        <v>813</v>
-      </c>
-      <c r="F78" s="4">
-        <f t="shared" si="20"/>
-        <v>1.5339768183532826E-4</v>
-      </c>
-      <c r="G78" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12471231533212188</v>
-      </c>
-      <c r="H78" s="5">
-        <f t="shared" si="22"/>
-        <v>5499</v>
-      </c>
-      <c r="I78" s="2">
-        <f t="shared" si="23"/>
-        <v>1629.9918166939442</v>
-      </c>
-      <c r="J78" s="8">
-        <f t="shared" si="24"/>
-        <v>1.4786436562541638E-4</v>
-      </c>
-      <c r="K78" s="1">
-        <f t="shared" si="25"/>
-        <v>813</v>
-      </c>
-      <c r="L78" s="2">
-        <f t="shared" si="28"/>
-        <v>27.055350553505534</v>
+        <v>23.075825156110614</v>
       </c>
     </row>
     <row r="79" spans="2:12">
       <c r="B79" s="2">
+        <f t="shared" si="24"/>
+        <v>2053.5250264571323</v>
+      </c>
+      <c r="C79" s="1">
+        <f t="shared" si="28"/>
+        <v>75</v>
+      </c>
+      <c r="D79" s="1">
+        <f t="shared" si="25"/>
+        <v>301</v>
+      </c>
+      <c r="E79" s="1">
         <f t="shared" si="26"/>
-        <v>1747.5284000076961</v>
-      </c>
-      <c r="C79" s="1">
-        <f t="shared" si="29"/>
-        <v>75</v>
-      </c>
-      <c r="D79" s="1">
+        <v>1205</v>
+      </c>
+      <c r="F79" s="4">
+        <f t="shared" si="18"/>
+        <v>1.217418812914666E-4</v>
+      </c>
+      <c r="G79" s="4">
         <f t="shared" si="19"/>
-        <v>218</v>
-      </c>
-      <c r="E79" s="1">
+        <v>0.14669896695621726</v>
+      </c>
+      <c r="H79" s="5">
+        <f t="shared" si="20"/>
+        <v>6469</v>
+      </c>
+      <c r="I79" s="2">
+        <f t="shared" si="21"/>
+        <v>2053.6597619415675</v>
+      </c>
+      <c r="J79" s="8">
+        <f t="shared" si="22"/>
+        <v>6.5611805407428392E-5</v>
+      </c>
+      <c r="K79" s="1">
+        <f t="shared" si="23"/>
+        <v>1205</v>
+      </c>
+      <c r="L79" s="2">
         <f t="shared" si="27"/>
-        <v>873</v>
-      </c>
-      <c r="F79" s="4">
-        <f t="shared" si="20"/>
-        <v>1.4305919148375443E-4</v>
-      </c>
-      <c r="G79" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12489067416531761</v>
-      </c>
-      <c r="H79" s="5">
-        <f t="shared" si="22"/>
-        <v>5507</v>
-      </c>
-      <c r="I79" s="2">
-        <f t="shared" si="23"/>
-        <v>1747.7437806428184</v>
-      </c>
-      <c r="J79" s="8">
-        <f t="shared" si="24"/>
-        <v>1.2324871808733207E-4</v>
-      </c>
-      <c r="K79" s="1">
-        <f t="shared" si="25"/>
-        <v>873</v>
-      </c>
-      <c r="L79" s="2">
-        <f t="shared" si="28"/>
-        <v>25.232531500572737</v>
+        <v>21.473858921161824</v>
       </c>
     </row>
     <row r="80" spans="2:12">
       <c r="B80" s="2">
+        <f t="shared" si="24"/>
+        <v>2206.7340690845749</v>
+      </c>
+      <c r="C80" s="1">
+        <f t="shared" si="28"/>
+        <v>76</v>
+      </c>
+      <c r="D80" s="1">
+        <f t="shared" si="25"/>
+        <v>324</v>
+      </c>
+      <c r="E80" s="1">
         <f t="shared" si="26"/>
-        <v>1873.8174228603973</v>
-      </c>
-      <c r="C80" s="1">
-        <f t="shared" si="29"/>
-        <v>76</v>
-      </c>
-      <c r="D80" s="1">
+        <v>1297</v>
+      </c>
+      <c r="F80" s="4">
+        <f t="shared" si="18"/>
+        <v>1.1328959094002121E-4</v>
+      </c>
+      <c r="G80" s="4">
         <f t="shared" si="19"/>
-        <v>233</v>
-      </c>
-      <c r="E80" s="1">
+        <v>0.14693659944920751</v>
+      </c>
+      <c r="H80" s="5">
+        <f t="shared" si="20"/>
+        <v>6479</v>
+      </c>
+      <c r="I80" s="2">
+        <f t="shared" si="21"/>
+        <v>2207.0419817873126</v>
+      </c>
+      <c r="J80" s="8">
+        <f t="shared" si="22"/>
+        <v>1.3953321655346684E-4</v>
+      </c>
+      <c r="K80" s="1">
+        <f t="shared" si="23"/>
+        <v>1296.9999999999998</v>
+      </c>
+      <c r="L80" s="2">
         <f t="shared" si="27"/>
-        <v>933</v>
-      </c>
-      <c r="F80" s="4">
-        <f t="shared" si="20"/>
-        <v>1.334174807801568E-4</v>
-      </c>
-      <c r="G80" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12447850956788629</v>
-      </c>
-      <c r="H80" s="5">
-        <f t="shared" si="22"/>
-        <v>5489</v>
-      </c>
-      <c r="I80" s="2">
-        <f t="shared" si="23"/>
-        <v>1873.9888868646385</v>
-      </c>
-      <c r="J80" s="8">
-        <f t="shared" si="24"/>
-        <v>9.1505181961437643E-5</v>
-      </c>
-      <c r="K80" s="1">
-        <f t="shared" si="25"/>
-        <v>933</v>
-      </c>
-      <c r="L80" s="2">
-        <f t="shared" si="28"/>
-        <v>23.532690246516612</v>
+        <v>19.981495759444876</v>
       </c>
     </row>
     <row r="81" spans="2:12">
       <c r="B81" s="2">
+        <f t="shared" si="24"/>
+        <v>2371.3737056616392</v>
+      </c>
+      <c r="C81" s="1">
+        <f t="shared" si="28"/>
+        <v>77</v>
+      </c>
+      <c r="D81" s="1">
+        <f t="shared" si="25"/>
+        <v>348</v>
+      </c>
+      <c r="E81" s="1">
         <f t="shared" si="26"/>
-        <v>2009.2330025650615</v>
-      </c>
-      <c r="C81" s="1">
-        <f t="shared" si="29"/>
-        <v>77</v>
-      </c>
-      <c r="D81" s="1">
+        <v>1393</v>
+      </c>
+      <c r="F81" s="4">
+        <f t="shared" si="18"/>
+        <v>1.0542412585714628E-4</v>
+      </c>
+      <c r="G81" s="4">
         <f t="shared" si="19"/>
-        <v>250</v>
-      </c>
-      <c r="E81" s="1">
+        <v>0.14685580731900477</v>
+      </c>
+      <c r="H81" s="5">
+        <f t="shared" si="20"/>
+        <v>6476</v>
+      </c>
+      <c r="I81" s="2">
+        <f t="shared" si="21"/>
+        <v>2371.498610253243</v>
+      </c>
+      <c r="J81" s="8">
+        <f t="shared" si="22"/>
+        <v>5.2671829541495185E-5</v>
+      </c>
+      <c r="K81" s="1">
+        <f t="shared" si="23"/>
+        <v>1393.0000000000002</v>
+      </c>
+      <c r="L81" s="2">
         <f t="shared" si="27"/>
-        <v>1001</v>
-      </c>
-      <c r="F81" s="4">
-        <f t="shared" si="20"/>
-        <v>1.2442558910830188E-4</v>
-      </c>
-      <c r="G81" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12455001469741019</v>
-      </c>
-      <c r="H81" s="5">
-        <f t="shared" si="22"/>
-        <v>5492</v>
-      </c>
-      <c r="I81" s="2">
-        <f t="shared" si="23"/>
-        <v>2009.4728696285506</v>
-      </c>
-      <c r="J81" s="8">
-        <f t="shared" si="24"/>
-        <v>1.1938240272924006E-4</v>
-      </c>
-      <c r="K81" s="1">
-        <f t="shared" si="25"/>
-        <v>1001</v>
-      </c>
-      <c r="L81" s="2">
-        <f t="shared" si="28"/>
-        <v>21.946053946053947</v>
+        <v>18.595836324479539</v>
       </c>
     </row>
     <row r="82" spans="2:12">
       <c r="B82" s="2">
+        <f t="shared" si="24"/>
+        <v>2548.2967479793292</v>
+      </c>
+      <c r="C82" s="1">
+        <f t="shared" si="28"/>
+        <v>78</v>
+      </c>
+      <c r="D82" s="1">
+        <f t="shared" si="25"/>
+        <v>374</v>
+      </c>
+      <c r="E82" s="1">
         <f t="shared" si="26"/>
-        <v>2154.4346900318992</v>
-      </c>
-      <c r="C82" s="1">
-        <f t="shared" si="29"/>
-        <v>78</v>
-      </c>
-      <c r="D82" s="1">
+        <v>1497</v>
+      </c>
+      <c r="F82" s="4">
+        <f t="shared" si="18"/>
+        <v>9.8104743962114063E-5</v>
+      </c>
+      <c r="G82" s="4">
         <f t="shared" si="19"/>
-        <v>269</v>
-      </c>
-      <c r="E82" s="1">
+        <v>0.14686280171128474</v>
+      </c>
+      <c r="H82" s="5">
+        <f t="shared" si="20"/>
+        <v>6476</v>
+      </c>
+      <c r="I82" s="2">
+        <f t="shared" si="21"/>
+        <v>2548.5523471278566</v>
+      </c>
+      <c r="J82" s="8">
+        <f t="shared" si="22"/>
+        <v>1.0030195609278536E-4</v>
+      </c>
+      <c r="K82" s="1">
+        <f t="shared" si="23"/>
+        <v>1497</v>
+      </c>
+      <c r="L82" s="2">
         <f t="shared" si="27"/>
-        <v>1077</v>
-      </c>
-      <c r="F82" s="4">
-        <f t="shared" si="20"/>
-        <v>1.1603972084031863E-4</v>
-      </c>
-      <c r="G82" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12497477934502317</v>
-      </c>
-      <c r="H82" s="5">
-        <f t="shared" si="22"/>
-        <v>5511</v>
-      </c>
-      <c r="I82" s="2">
-        <f t="shared" si="23"/>
-        <v>2154.5862819814915</v>
-      </c>
-      <c r="J82" s="8">
-        <f t="shared" si="24"/>
-        <v>7.0362750049346445E-5</v>
-      </c>
-      <c r="K82" s="1">
-        <f t="shared" si="25"/>
-        <v>1077</v>
-      </c>
-      <c r="L82" s="2">
-        <f t="shared" si="28"/>
-        <v>20.467966573816156</v>
+        <v>17.303941215764862</v>
       </c>
     </row>
     <row r="83" spans="2:12">
       <c r="B83" s="2">
+        <f t="shared" si="24"/>
+        <v>2738.4196342643427</v>
+      </c>
+      <c r="C83" s="1">
+        <f t="shared" si="28"/>
+        <v>79</v>
+      </c>
+      <c r="D83" s="1">
+        <f t="shared" si="25"/>
+        <v>402</v>
+      </c>
+      <c r="E83" s="1">
         <f t="shared" si="26"/>
-        <v>2310.1297000831764</v>
-      </c>
-      <c r="C83" s="1">
-        <f t="shared" si="29"/>
-        <v>79</v>
-      </c>
-      <c r="D83" s="1">
+        <v>1609</v>
+      </c>
+      <c r="F83" s="4">
+        <f t="shared" si="18"/>
+        <v>9.1293531813710048E-5</v>
+      </c>
+      <c r="G83" s="4">
         <f t="shared" si="19"/>
-        <v>288</v>
-      </c>
-      <c r="E83" s="1">
+        <v>0.14689129268825946</v>
+      </c>
+      <c r="H83" s="5">
+        <f t="shared" si="20"/>
+        <v>6477</v>
+      </c>
+      <c r="I83" s="2">
+        <f t="shared" si="21"/>
+        <v>2738.8026864289022</v>
+      </c>
+      <c r="J83" s="8">
+        <f t="shared" si="22"/>
+        <v>1.3988073988602245E-4</v>
+      </c>
+      <c r="K83" s="1">
+        <f t="shared" si="23"/>
+        <v>1609</v>
+      </c>
+      <c r="L83" s="2">
         <f t="shared" si="27"/>
-        <v>1153</v>
-      </c>
-      <c r="F83" s="4">
-        <f t="shared" si="20"/>
-        <v>1.0821903202707568E-4</v>
-      </c>
-      <c r="G83" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12477654392721826</v>
-      </c>
-      <c r="H83" s="5">
-        <f t="shared" si="22"/>
-        <v>5502</v>
-      </c>
-      <c r="I83" s="2">
-        <f t="shared" si="23"/>
-        <v>2310.4007633587785</v>
-      </c>
-      <c r="J83" s="8">
-        <f t="shared" si="24"/>
-        <v>1.1733682121506384E-4</v>
-      </c>
-      <c r="K83" s="1">
-        <f t="shared" si="25"/>
-        <v>1153</v>
-      </c>
-      <c r="L83" s="2">
-        <f t="shared" si="28"/>
-        <v>19.087597571552472</v>
+        <v>16.101926662523308</v>
       </c>
     </row>
     <row r="84" spans="2:12">
       <c r="B84" s="2">
+        <f t="shared" si="24"/>
+        <v>2942.7271762092614</v>
+      </c>
+      <c r="C84" s="1">
+        <f t="shared" si="28"/>
+        <v>80</v>
+      </c>
+      <c r="D84" s="1">
+        <f t="shared" si="25"/>
+        <v>432</v>
+      </c>
+      <c r="E84" s="1">
         <f t="shared" si="26"/>
-        <v>2477.0763559917291</v>
-      </c>
-      <c r="C84" s="1">
-        <f t="shared" si="29"/>
-        <v>80</v>
-      </c>
-      <c r="D84" s="1">
+        <v>1729</v>
+      </c>
+      <c r="F84" s="4">
+        <f t="shared" si="18"/>
+        <v>8.4955208223564573E-5</v>
+      </c>
+      <c r="G84" s="4">
         <f t="shared" si="19"/>
-        <v>309</v>
-      </c>
-      <c r="E84" s="1">
+        <v>0.14688755501854314</v>
+      </c>
+      <c r="H84" s="5">
+        <f t="shared" si="20"/>
+        <v>6477</v>
+      </c>
+      <c r="I84" s="2">
+        <f t="shared" si="21"/>
+        <v>2943.0639184807783</v>
+      </c>
+      <c r="J84" s="8">
+        <f t="shared" si="22"/>
+        <v>1.1443203917749223E-4</v>
+      </c>
+      <c r="K84" s="1">
+        <f t="shared" si="23"/>
+        <v>1729</v>
+      </c>
+      <c r="L84" s="2">
         <f t="shared" si="27"/>
-        <v>1237</v>
-      </c>
-      <c r="F84" s="4">
-        <f t="shared" si="20"/>
-        <v>1.0092543146491313E-4</v>
-      </c>
-      <c r="G84" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12484475872209753</v>
-      </c>
-      <c r="H84" s="5">
-        <f t="shared" si="22"/>
-        <v>5505</v>
-      </c>
-      <c r="I84" s="2">
-        <f t="shared" si="23"/>
-        <v>2477.3705722070845</v>
-      </c>
-      <c r="J84" s="8">
-        <f t="shared" si="24"/>
-        <v>1.1877559391493264E-4</v>
-      </c>
-      <c r="K84" s="1">
-        <f t="shared" si="25"/>
-        <v>1237</v>
-      </c>
-      <c r="L84" s="2">
-        <f t="shared" si="28"/>
-        <v>17.801131770412287</v>
+        <v>14.984384037015616</v>
       </c>
     </row>
     <row r="85" spans="2:12">
       <c r="B85" s="2">
+        <f t="shared" si="24"/>
+        <v>3162.2776601683572</v>
+      </c>
+      <c r="C85" s="1">
+        <f t="shared" si="28"/>
+        <v>81</v>
+      </c>
+      <c r="D85" s="1">
+        <f t="shared" si="25"/>
+        <v>464</v>
+      </c>
+      <c r="E85" s="1">
         <f t="shared" si="26"/>
-        <v>2656.0877829467058</v>
-      </c>
-      <c r="C85" s="1">
-        <f t="shared" si="29"/>
-        <v>81</v>
-      </c>
-      <c r="D85" s="1">
+        <v>1857</v>
+      </c>
+      <c r="F85" s="4">
+        <f t="shared" si="18"/>
+        <v>7.9056941504210041E-5</v>
+      </c>
+      <c r="G85" s="4">
         <f t="shared" si="19"/>
-        <v>331</v>
-      </c>
-      <c r="E85" s="1">
+        <v>0.14680874037331804</v>
+      </c>
+      <c r="H85" s="5">
+        <f t="shared" si="20"/>
+        <v>6474</v>
+      </c>
+      <c r="I85" s="2">
+        <f t="shared" si="21"/>
+        <v>3162.4073215940689</v>
+      </c>
+      <c r="J85" s="8">
+        <f t="shared" si="22"/>
+        <v>4.100254299133077E-5</v>
+      </c>
+      <c r="K85" s="1">
+        <f t="shared" si="23"/>
+        <v>1857.0000000000002</v>
+      </c>
+      <c r="L85" s="2">
         <f t="shared" si="27"/>
-        <v>1325</v>
-      </c>
-      <c r="F85" s="4">
-        <f t="shared" si="20"/>
-        <v>9.4123395169811011E-5</v>
-      </c>
-      <c r="G85" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12471349859999958</v>
-      </c>
-      <c r="H85" s="5">
-        <f t="shared" si="22"/>
-        <v>5499</v>
-      </c>
-      <c r="I85" s="2">
-        <f t="shared" si="23"/>
-        <v>2656.5057283142391</v>
-      </c>
-      <c r="J85" s="8">
-        <f t="shared" si="24"/>
-        <v>1.5735374795089463E-4</v>
-      </c>
-      <c r="K85" s="1">
-        <f t="shared" si="25"/>
-        <v>1325.0000000000002</v>
-      </c>
-      <c r="L85" s="2">
-        <f t="shared" si="28"/>
-        <v>16.600754716981129</v>
+        <v>13.945072697899837</v>
       </c>
     </row>
     <row r="86" spans="2:12">
       <c r="B86" s="2">
+        <f t="shared" si="24"/>
+        <v>3398.2083289425354</v>
+      </c>
+      <c r="C86" s="1">
+        <f t="shared" si="28"/>
+        <v>82</v>
+      </c>
+      <c r="D86" s="1">
+        <f t="shared" si="25"/>
+        <v>499</v>
+      </c>
+      <c r="E86" s="1">
         <f t="shared" si="26"/>
-        <v>2848.035868435823</v>
-      </c>
-      <c r="C86" s="1">
-        <f t="shared" si="29"/>
-        <v>82</v>
-      </c>
-      <c r="D86" s="1">
+        <v>1997</v>
+      </c>
+      <c r="F86" s="4">
+        <f t="shared" si="18"/>
+        <v>7.3568179405232557E-5</v>
+      </c>
+      <c r="G86" s="4">
         <f t="shared" si="19"/>
-        <v>355</v>
-      </c>
-      <c r="E86" s="1">
+        <v>0.14691565427224942</v>
+      </c>
+      <c r="H86" s="5">
+        <f t="shared" si="20"/>
+        <v>6478</v>
+      </c>
+      <c r="I86" s="2">
+        <f t="shared" si="21"/>
+        <v>3398.7225995677677</v>
+      </c>
+      <c r="J86" s="8">
+        <f t="shared" si="22"/>
+        <v>1.5133581447979161E-4</v>
+      </c>
+      <c r="K86" s="1">
+        <f t="shared" si="23"/>
+        <v>1997</v>
+      </c>
+      <c r="L86" s="2">
         <f t="shared" si="27"/>
-        <v>1421</v>
-      </c>
-      <c r="F86" s="4">
-        <f t="shared" si="20"/>
-        <v>8.7779793355377623E-5</v>
-      </c>
-      <c r="G86" s="4">
-        <f t="shared" si="21"/>
-        <v>0.1247350863579916</v>
-      </c>
-      <c r="H86" s="5">
-        <f t="shared" si="22"/>
-        <v>5500</v>
-      </c>
-      <c r="I86" s="2">
-        <f t="shared" si="23"/>
-        <v>2848.4590909090907</v>
-      </c>
-      <c r="J86" s="8">
-        <f t="shared" si="24"/>
-        <v>1.4860152498719081E-4</v>
-      </c>
-      <c r="K86" s="1">
-        <f t="shared" si="25"/>
-        <v>1420.9999999999998</v>
-      </c>
-      <c r="L86" s="2">
-        <f t="shared" si="28"/>
-        <v>15.482054890921889</v>
+        <v>12.975463194792189</v>
       </c>
     </row>
     <row r="87" spans="2:12">
       <c r="B87" s="2">
+        <f t="shared" si="24"/>
+        <v>3651.7412725483509</v>
+      </c>
+      <c r="C87" s="1">
+        <f t="shared" si="28"/>
+        <v>83</v>
+      </c>
+      <c r="D87" s="1">
+        <f t="shared" si="25"/>
+        <v>536</v>
+      </c>
+      <c r="E87" s="1">
         <f t="shared" si="26"/>
-        <v>3053.8555088334388</v>
-      </c>
-      <c r="C87" s="1">
-        <f t="shared" si="29"/>
-        <v>83</v>
-      </c>
-      <c r="D87" s="1">
+        <v>2145</v>
+      </c>
+      <c r="F87" s="4">
+        <f t="shared" si="18"/>
+        <v>6.8460490856609528E-5</v>
+      </c>
+      <c r="G87" s="4">
         <f t="shared" si="19"/>
-        <v>381</v>
-      </c>
-      <c r="E87" s="1">
+        <v>0.14684775288742744</v>
+      </c>
+      <c r="H87" s="5">
+        <f t="shared" si="20"/>
+        <v>6475</v>
+      </c>
+      <c r="I87" s="2">
+        <f t="shared" si="21"/>
+        <v>3652.2972972972975</v>
+      </c>
+      <c r="J87" s="8">
+        <f t="shared" si="22"/>
+        <v>1.5226290896519501E-4</v>
+      </c>
+      <c r="K87" s="1">
+        <f t="shared" si="23"/>
+        <v>2145</v>
+      </c>
+      <c r="L87" s="2">
         <f t="shared" si="27"/>
-        <v>1525</v>
-      </c>
-      <c r="F87" s="4">
-        <f t="shared" si="20"/>
-        <v>8.1863729071942587E-5</v>
-      </c>
-      <c r="G87" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12484218683471245</v>
-      </c>
-      <c r="H87" s="5">
-        <f t="shared" si="22"/>
-        <v>5505</v>
-      </c>
-      <c r="I87" s="2">
-        <f t="shared" si="23"/>
-        <v>3054.1553133514985</v>
-      </c>
-      <c r="J87" s="8">
-        <f t="shared" si="24"/>
-        <v>9.817246336396579E-5</v>
-      </c>
-      <c r="K87" s="1">
-        <f t="shared" si="25"/>
-        <v>1525</v>
-      </c>
-      <c r="L87" s="2">
-        <f t="shared" si="28"/>
-        <v>14.439344262295082</v>
+        <v>12.074592074592074</v>
       </c>
     </row>
     <row r="88" spans="2:12">
       <c r="B88" s="2">
+        <f t="shared" si="24"/>
+        <v>3924.1897584845074</v>
+      </c>
+      <c r="C88" s="1">
+        <f t="shared" si="28"/>
+        <v>84</v>
+      </c>
+      <c r="D88" s="1">
+        <f t="shared" si="25"/>
+        <v>576</v>
+      </c>
+      <c r="E88" s="1">
         <f t="shared" si="26"/>
-        <v>3274.5491628777536</v>
-      </c>
-      <c r="C88" s="1">
-        <f t="shared" si="29"/>
-        <v>84</v>
-      </c>
-      <c r="D88" s="1">
+        <v>2305</v>
+      </c>
+      <c r="F88" s="4">
+        <f t="shared" si="18"/>
+        <v>6.3707418699484119E-5</v>
+      </c>
+      <c r="G88" s="4">
         <f t="shared" si="19"/>
-        <v>409</v>
-      </c>
-      <c r="E88" s="1">
+        <v>0.1468456001023109</v>
+      </c>
+      <c r="H88" s="5">
+        <f t="shared" si="20"/>
+        <v>6475</v>
+      </c>
+      <c r="I88" s="2">
+        <f t="shared" si="21"/>
+        <v>3924.7297297297296</v>
+      </c>
+      <c r="J88" s="8">
+        <f t="shared" si="22"/>
+        <v>1.3760069682011711E-4</v>
+      </c>
+      <c r="K88" s="1">
+        <f t="shared" si="23"/>
+        <v>2305</v>
+      </c>
+      <c r="L88" s="2">
         <f t="shared" si="27"/>
-        <v>1637</v>
-      </c>
-      <c r="F88" s="4">
-        <f t="shared" si="20"/>
-        <v>7.6346387720834798E-5</v>
-      </c>
-      <c r="G88" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12497903669900656</v>
-      </c>
-      <c r="H88" s="5">
-        <f t="shared" si="22"/>
-        <v>5511</v>
-      </c>
-      <c r="I88" s="2">
-        <f t="shared" si="23"/>
-        <v>3274.8911268372349</v>
-      </c>
-      <c r="J88" s="8">
-        <f t="shared" si="24"/>
-        <v>1.0443085214850711E-4</v>
-      </c>
-      <c r="K88" s="1">
-        <f t="shared" si="25"/>
-        <v>1637</v>
-      </c>
-      <c r="L88" s="2">
-        <f t="shared" si="28"/>
-        <v>13.46609651802077</v>
+        <v>11.23644251626898</v>
       </c>
     </row>
     <row r="89" spans="2:12">
       <c r="B89" s="2">
+        <f t="shared" si="24"/>
+        <v>4216.9650342857913</v>
+      </c>
+      <c r="C89" s="1">
+        <f t="shared" si="28"/>
+        <v>85</v>
+      </c>
+      <c r="D89" s="1">
+        <f t="shared" si="25"/>
+        <v>619</v>
+      </c>
+      <c r="E89" s="1">
         <f t="shared" si="26"/>
-        <v>3511.1917342151587</v>
-      </c>
-      <c r="C89" s="1">
-        <f t="shared" si="29"/>
-        <v>85</v>
-      </c>
-      <c r="D89" s="1">
+        <v>2477</v>
+      </c>
+      <c r="F89" s="4">
+        <f t="shared" si="18"/>
+        <v>5.9284342641541818E-5</v>
+      </c>
+      <c r="G89" s="4">
         <f t="shared" si="19"/>
-        <v>438</v>
-      </c>
-      <c r="E89" s="1">
+        <v>0.14684731672309909</v>
+      </c>
+      <c r="H89" s="5">
+        <f t="shared" si="20"/>
+        <v>6475</v>
+      </c>
+      <c r="I89" s="2">
+        <f t="shared" si="21"/>
+        <v>4217.594594594595</v>
+      </c>
+      <c r="J89" s="8">
+        <f t="shared" si="22"/>
+        <v>1.4929227624249641E-4</v>
+      </c>
+      <c r="K89" s="1">
+        <f t="shared" si="23"/>
+        <v>2477.0000000000005</v>
+      </c>
+      <c r="L89" s="2">
         <f t="shared" si="27"/>
-        <v>1753</v>
-      </c>
-      <c r="F89" s="4">
-        <f t="shared" si="20"/>
-        <v>7.1200896710894485E-5</v>
-      </c>
-      <c r="G89" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12481517193419803</v>
-      </c>
-      <c r="H89" s="5">
-        <f t="shared" si="22"/>
-        <v>5504</v>
-      </c>
-      <c r="I89" s="2">
-        <f t="shared" si="23"/>
-        <v>3511.4144258720935</v>
-      </c>
-      <c r="J89" s="8">
-        <f t="shared" si="24"/>
-        <v>6.3423382655081184E-5</v>
-      </c>
-      <c r="K89" s="1">
-        <f t="shared" si="25"/>
-        <v>1753.0000000000002</v>
-      </c>
-      <c r="L89" s="2">
-        <f t="shared" si="28"/>
-        <v>12.559041642897888</v>
+        <v>10.456197012515137</v>
       </c>
     </row>
     <row r="90" spans="2:12">
       <c r="B90" s="2">
+        <f t="shared" si="24"/>
+        <v>4531.5836376007837</v>
+      </c>
+      <c r="C90" s="1">
+        <f t="shared" si="28"/>
+        <v>86</v>
+      </c>
+      <c r="D90" s="1">
+        <f t="shared" si="25"/>
+        <v>666</v>
+      </c>
+      <c r="E90" s="1">
         <f t="shared" si="26"/>
-        <v>3764.9358067924977</v>
-      </c>
-      <c r="C90" s="1">
-        <f t="shared" si="29"/>
-        <v>86</v>
-      </c>
-      <c r="D90" s="1">
+        <v>2665</v>
+      </c>
+      <c r="F90" s="4">
+        <f t="shared" si="18"/>
+        <v>5.5168351727115164E-5</v>
+      </c>
+      <c r="G90" s="4">
         <f t="shared" si="19"/>
-        <v>470</v>
-      </c>
-      <c r="E90" s="1">
+        <v>0.14702365735276191</v>
+      </c>
+      <c r="H90" s="5">
+        <f t="shared" si="20"/>
+        <v>6483</v>
+      </c>
+      <c r="I90" s="2">
+        <f t="shared" si="21"/>
+        <v>4532.1031929662195</v>
+      </c>
+      <c r="J90" s="8">
+        <f t="shared" si="22"/>
+        <v>1.1465205256833144E-4</v>
+      </c>
+      <c r="K90" s="1">
+        <f t="shared" si="23"/>
+        <v>2665</v>
+      </c>
+      <c r="L90" s="2">
         <f t="shared" si="27"/>
-        <v>1881</v>
-      </c>
-      <c r="F90" s="4">
-        <f t="shared" si="20"/>
-        <v>6.6402194573666633E-5</v>
-      </c>
-      <c r="G90" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12490252799306693</v>
-      </c>
-      <c r="H90" s="5">
-        <f t="shared" si="22"/>
-        <v>5508</v>
-      </c>
-      <c r="I90" s="2">
-        <f t="shared" si="23"/>
-        <v>3765.0735294117649</v>
-      </c>
-      <c r="J90" s="8">
-        <f t="shared" si="24"/>
-        <v>3.6580336647107359E-5</v>
-      </c>
-      <c r="K90" s="1">
-        <f t="shared" si="25"/>
-        <v>1881</v>
-      </c>
-      <c r="L90" s="2">
-        <f t="shared" si="28"/>
-        <v>11.712918660287082</v>
+        <v>9.7305816135084431</v>
       </c>
     </row>
     <row r="91" spans="2:12">
       <c r="B91" s="2">
+        <f t="shared" si="24"/>
+        <v>4869.6752516585939</v>
+      </c>
+      <c r="C91" s="1">
+        <f t="shared" si="28"/>
+        <v>87</v>
+      </c>
+      <c r="D91" s="1">
+        <f t="shared" si="25"/>
+        <v>715</v>
+      </c>
+      <c r="E91" s="1">
         <f t="shared" si="26"/>
-        <v>4037.017258596587</v>
-      </c>
-      <c r="C91" s="1">
-        <f t="shared" si="29"/>
-        <v>87</v>
-      </c>
-      <c r="D91" s="1">
+        <v>2861</v>
+      </c>
+      <c r="F91" s="4">
+        <f t="shared" si="18"/>
+        <v>5.1338125661429046E-5</v>
+      </c>
+      <c r="G91" s="4">
         <f t="shared" si="19"/>
-        <v>504</v>
-      </c>
-      <c r="E91" s="1">
+        <v>0.1468783775173485</v>
+      </c>
+      <c r="H91" s="5">
+        <f t="shared" si="20"/>
+        <v>6477</v>
+      </c>
+      <c r="I91" s="2">
+        <f t="shared" si="21"/>
+        <v>4869.9282075034744</v>
+      </c>
+      <c r="J91" s="8">
+        <f t="shared" si="22"/>
+        <v>5.1945115804974407E-5</v>
+      </c>
+      <c r="K91" s="1">
+        <f t="shared" si="23"/>
+        <v>2861.0000000000005</v>
+      </c>
+      <c r="L91" s="2">
         <f t="shared" si="27"/>
-        <v>2017</v>
-      </c>
-      <c r="F91" s="4">
-        <f t="shared" si="20"/>
-        <v>6.1926908899792278E-5</v>
-      </c>
-      <c r="G91" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12490657525088103</v>
-      </c>
-      <c r="H91" s="5">
-        <f t="shared" si="22"/>
-        <v>5508</v>
-      </c>
-      <c r="I91" s="2">
-        <f t="shared" si="23"/>
-        <v>4037.295751633987</v>
-      </c>
-      <c r="J91" s="8">
-        <f t="shared" si="24"/>
-        <v>6.8984851825160121E-5</v>
-      </c>
-      <c r="K91" s="1">
-        <f t="shared" si="25"/>
-        <v>2017</v>
-      </c>
-      <c r="L91" s="2">
-        <f t="shared" si="28"/>
-        <v>10.923153197818543</v>
+        <v>9.0555749737853883</v>
       </c>
     </row>
     <row r="92" spans="2:12">
       <c r="B92" s="2">
+        <f t="shared" si="24"/>
+        <v>5232.9911468149066</v>
+      </c>
+      <c r="C92" s="1">
+        <f t="shared" si="28"/>
+        <v>88</v>
+      </c>
+      <c r="D92" s="1">
+        <f t="shared" si="25"/>
+        <v>769</v>
+      </c>
+      <c r="E92" s="1">
         <f t="shared" si="26"/>
-        <v>4328.7612810830933</v>
-      </c>
-      <c r="C92" s="1">
-        <f t="shared" si="29"/>
-        <v>88</v>
-      </c>
-      <c r="D92" s="1">
+        <v>3077</v>
+      </c>
+      <c r="F92" s="4">
+        <f t="shared" si="18"/>
+        <v>4.7773824374261378E-5</v>
+      </c>
+      <c r="G92" s="4">
         <f t="shared" si="19"/>
-        <v>540</v>
-      </c>
-      <c r="E92" s="1">
+        <v>0.14700005759960225</v>
+      </c>
+      <c r="H92" s="5">
+        <f t="shared" si="20"/>
+        <v>6482</v>
+      </c>
+      <c r="I92" s="2">
+        <f t="shared" si="21"/>
+        <v>5233.5583153347734</v>
+      </c>
+      <c r="J92" s="8">
+        <f t="shared" si="22"/>
+        <v>1.0838323703499242E-4</v>
+      </c>
+      <c r="K92" s="1">
+        <f t="shared" si="23"/>
+        <v>3077</v>
+      </c>
+      <c r="L92" s="2">
         <f t="shared" si="27"/>
-        <v>2161</v>
-      </c>
-      <c r="F92" s="4">
-        <f t="shared" si="20"/>
-        <v>5.7753242502078525E-5</v>
-      </c>
-      <c r="G92" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12480475704699169</v>
-      </c>
-      <c r="H92" s="5">
-        <f t="shared" si="22"/>
-        <v>5503</v>
-      </c>
-      <c r="I92" s="2">
-        <f t="shared" si="23"/>
-        <v>4329.461202980192</v>
-      </c>
-      <c r="J92" s="8">
-        <f t="shared" si="24"/>
-        <v>1.6169103622254433E-4</v>
-      </c>
-      <c r="K92" s="1">
-        <f t="shared" si="25"/>
-        <v>2160.9999999999995</v>
-      </c>
-      <c r="L92" s="2">
-        <f t="shared" si="28"/>
-        <v>10.186024988431283</v>
+        <v>8.4263893402664927</v>
       </c>
     </row>
     <row r="93" spans="2:12">
       <c r="B93" s="2">
+        <f t="shared" si="24"/>
+        <v>5623.4132519034474</v>
+      </c>
+      <c r="C93" s="1">
+        <f t="shared" si="28"/>
+        <v>89</v>
+      </c>
+      <c r="D93" s="1">
+        <f t="shared" si="25"/>
+        <v>826</v>
+      </c>
+      <c r="E93" s="1">
         <f t="shared" si="26"/>
-        <v>4641.5888336128164</v>
-      </c>
-      <c r="C93" s="1">
-        <f t="shared" si="29"/>
-        <v>89</v>
-      </c>
-      <c r="D93" s="1">
+        <v>3305</v>
+      </c>
+      <c r="F93" s="4">
+        <f t="shared" si="18"/>
+        <v>4.4456985250973413E-5</v>
+      </c>
+      <c r="G93" s="4">
         <f t="shared" si="19"/>
-        <v>579</v>
-      </c>
-      <c r="E93" s="1">
+        <v>0.14693033625446714</v>
+      </c>
+      <c r="H93" s="5">
+        <f t="shared" si="20"/>
+        <v>6479</v>
+      </c>
+      <c r="I93" s="2">
+        <f t="shared" si="21"/>
+        <v>5623.9581725574935</v>
+      </c>
+      <c r="J93" s="8">
+        <f t="shared" si="22"/>
+        <v>9.6902117919572817E-5</v>
+      </c>
+      <c r="K93" s="1">
+        <f t="shared" si="23"/>
+        <v>3305</v>
+      </c>
+      <c r="L93" s="2">
         <f t="shared" si="27"/>
-        <v>2317</v>
-      </c>
-      <c r="F93" s="4">
-        <f t="shared" si="20"/>
-        <v>5.3860867250796658E-5</v>
-      </c>
-      <c r="G93" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12479562942009585</v>
-      </c>
-      <c r="H93" s="5">
-        <f t="shared" si="22"/>
-        <v>5503</v>
-      </c>
-      <c r="I93" s="2">
-        <f t="shared" si="23"/>
-        <v>4641.9998182809377</v>
-      </c>
-      <c r="J93" s="8">
-        <f t="shared" si="24"/>
-        <v>8.8543962607268156E-5</v>
-      </c>
-      <c r="K93" s="1">
-        <f t="shared" si="25"/>
-        <v>2317</v>
-      </c>
-      <c r="L93" s="2">
-        <f t="shared" si="28"/>
-        <v>9.5002157962883036</v>
+        <v>7.8414523449319216</v>
       </c>
     </row>
     <row r="94" spans="2:12">
       <c r="B94" s="2">
+        <f t="shared" si="24"/>
+        <v>6042.9639023812806</v>
+      </c>
+      <c r="C94" s="1">
+        <f t="shared" si="28"/>
+        <v>90</v>
+      </c>
+      <c r="D94" s="1">
+        <f t="shared" si="25"/>
+        <v>888</v>
+      </c>
+      <c r="E94" s="1">
         <f t="shared" si="26"/>
-        <v>4977.0235643321512</v>
-      </c>
-      <c r="C94" s="1">
-        <f t="shared" si="29"/>
-        <v>90</v>
-      </c>
-      <c r="D94" s="1">
+        <v>3553</v>
+      </c>
+      <c r="F94" s="4">
+        <f t="shared" si="18"/>
+        <v>4.1370427498579863E-5</v>
+      </c>
+      <c r="G94" s="4">
         <f t="shared" si="19"/>
-        <v>621</v>
-      </c>
-      <c r="E94" s="1">
+        <v>0.14698912890245425</v>
+      </c>
+      <c r="H94" s="5">
+        <f t="shared" si="20"/>
+        <v>6482</v>
+      </c>
+      <c r="I94" s="2">
+        <f t="shared" si="21"/>
+        <v>6043.1695464362856</v>
+      </c>
+      <c r="J94" s="8">
+        <f t="shared" si="22"/>
+        <v>3.4030329872480891E-5</v>
+      </c>
+      <c r="K94" s="1">
+        <f t="shared" si="23"/>
+        <v>3553</v>
+      </c>
+      <c r="L94" s="2">
         <f t="shared" si="27"/>
-        <v>2485</v>
-      </c>
-      <c r="F94" s="4">
-        <f t="shared" si="20"/>
-        <v>5.023082506412577E-5</v>
-      </c>
-      <c r="G94" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12482360028435253</v>
-      </c>
-      <c r="H94" s="5">
-        <f t="shared" si="22"/>
-        <v>5504</v>
-      </c>
-      <c r="I94" s="2">
-        <f t="shared" si="23"/>
-        <v>4977.6753270348836</v>
-      </c>
-      <c r="J94" s="8">
-        <f t="shared" si="24"/>
-        <v>1.3095431321707984E-4</v>
-      </c>
-      <c r="K94" s="1">
-        <f t="shared" si="25"/>
-        <v>2485</v>
-      </c>
-      <c r="L94" s="2">
-        <f t="shared" si="28"/>
-        <v>8.8595573440643864</v>
+        <v>7.2974950745848579</v>
       </c>
     </row>
     <row r="95" spans="2:12">
       <c r="B95" s="2">
+        <f t="shared" si="24"/>
+        <v>6493.8163157620611</v>
+      </c>
+      <c r="C95" s="1">
+        <f t="shared" si="28"/>
+        <v>91</v>
+      </c>
+      <c r="D95" s="1">
+        <f t="shared" si="25"/>
+        <v>954</v>
+      </c>
+      <c r="E95" s="1">
         <f t="shared" si="26"/>
-        <v>5336.699231206353</v>
-      </c>
-      <c r="C95" s="1">
-        <f t="shared" si="29"/>
-        <v>91</v>
-      </c>
-      <c r="D95" s="1">
+        <v>3817</v>
+      </c>
+      <c r="F95" s="4">
+        <f t="shared" si="18"/>
+        <v>3.849816315148761E-5</v>
+      </c>
+      <c r="G95" s="4">
         <f t="shared" si="19"/>
-        <v>666</v>
-      </c>
-      <c r="E95" s="1">
+        <v>0.14694748874922819</v>
+      </c>
+      <c r="H95" s="5">
+        <f t="shared" si="20"/>
+        <v>6480</v>
+      </c>
+      <c r="I95" s="2">
+        <f t="shared" si="21"/>
+        <v>6494.2013888888896</v>
+      </c>
+      <c r="J95" s="8">
+        <f t="shared" si="22"/>
+        <v>5.9298432247611998E-5</v>
+      </c>
+      <c r="K95" s="1">
+        <f t="shared" si="23"/>
+        <v>3817.0000000000005</v>
+      </c>
+      <c r="L95" s="2">
         <f t="shared" si="27"/>
-        <v>2665</v>
-      </c>
-      <c r="F95" s="4">
-        <f t="shared" si="20"/>
-        <v>4.6845435571509223E-5</v>
-      </c>
-      <c r="G95" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12484308579807207</v>
-      </c>
-      <c r="H95" s="5">
-        <f t="shared" si="22"/>
-        <v>5505</v>
-      </c>
-      <c r="I95" s="2">
-        <f t="shared" si="23"/>
-        <v>5337.2615803814715</v>
-      </c>
-      <c r="J95" s="8">
-        <f t="shared" si="24"/>
-        <v>1.0537396820686773E-4</v>
-      </c>
-      <c r="K95" s="1">
-        <f t="shared" si="25"/>
-        <v>2665</v>
-      </c>
-      <c r="L95" s="2">
-        <f t="shared" si="28"/>
-        <v>8.2626641651031889</v>
+        <v>6.7906733036416025</v>
       </c>
     </row>
     <row r="96" spans="2:12">
       <c r="B96" s="2">
-        <f t="shared" si="26"/>
-        <v>5722.3676593502641</v>
+        <f t="shared" si="24"/>
+        <v>6978.3058485986066</v>
       </c>
       <c r="C96" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>92</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="19"/>
-        <v>715</v>
+        <f t="shared" ref="D96:D99" si="29">INT((B96/1.7-1)/4)</f>
+        <v>1025</v>
       </c>
       <c r="E96" s="1">
-        <f t="shared" si="27"/>
-        <v>2861</v>
+        <f t="shared" ref="E96:E99" si="30">4*D96+1</f>
+        <v>4101</v>
       </c>
       <c r="F96" s="4">
-        <f t="shared" si="20"/>
-        <v>4.3688210000191741E-5</v>
+        <f t="shared" ref="F96:F99" si="31">1/B96/4</f>
+        <v>3.582531425592436E-5</v>
       </c>
       <c r="G96" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12499196881054857</v>
+        <f t="shared" ref="G96:G99" si="32">E96*F96</f>
+        <v>0.14691961376354579</v>
       </c>
       <c r="H96" s="5">
-        <f t="shared" si="22"/>
-        <v>5512</v>
+        <f t="shared" ref="H96:H99" si="33">INT(G96*_rate)</f>
+        <v>6479</v>
       </c>
       <c r="I96" s="2">
-        <f t="shared" si="23"/>
-        <v>5722.519049346879</v>
+        <f t="shared" ref="I96:I99" si="34">E96/H96/4*_rate</f>
+        <v>6978.4727581416882</v>
       </c>
       <c r="J96" s="8">
-        <f t="shared" si="24"/>
-        <v>2.6455831856120327E-5</v>
+        <f t="shared" ref="J96:J99" si="35">(I96/B96-1)</f>
+        <v>2.3918347332951839E-5</v>
       </c>
       <c r="K96" s="1">
-        <f t="shared" si="25"/>
-        <v>2860.9999999999995</v>
+        <f t="shared" ref="K96:K99" si="36">4*I96*H96/_rate</f>
+        <v>4101</v>
       </c>
       <c r="L96" s="2">
-        <f t="shared" si="28"/>
-        <v>7.7063963649073761</v>
+        <f t="shared" ref="L96:L99" si="37">4*H96/K96</f>
+        <v>6.3194342843208977</v>
       </c>
     </row>
     <row r="97" spans="2:12">
       <c r="B97" s="2">
-        <f t="shared" si="26"/>
-        <v>6135.9072734132242</v>
+        <f t="shared" si="24"/>
+        <v>7498.9420933244965</v>
       </c>
       <c r="C97" s="1">
+        <f t="shared" si="28"/>
+        <v>93</v>
+      </c>
+      <c r="D97" s="1">
         <f t="shared" si="29"/>
-        <v>93</v>
-      </c>
-      <c r="D97" s="1">
-        <f t="shared" si="19"/>
-        <v>766</v>
+        <v>1102</v>
       </c>
       <c r="E97" s="1">
-        <f t="shared" si="27"/>
-        <v>3065</v>
+        <f t="shared" si="30"/>
+        <v>4409</v>
       </c>
       <c r="F97" s="4">
-        <f t="shared" si="20"/>
-        <v>4.0743770865515768E-5</v>
+        <f t="shared" si="31"/>
+        <v>3.3338035804083377E-5</v>
       </c>
       <c r="G97" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12487965770280583</v>
+        <f t="shared" si="32"/>
+        <v>0.14698739986020362</v>
       </c>
       <c r="H97" s="5">
-        <f t="shared" si="22"/>
-        <v>5507</v>
+        <f t="shared" si="33"/>
+        <v>6482</v>
       </c>
       <c r="I97" s="2">
-        <f t="shared" si="23"/>
-        <v>6136.1222080987836</v>
+        <f t="shared" si="34"/>
+        <v>7499.109071274298</v>
       </c>
       <c r="J97" s="8">
-        <f t="shared" si="24"/>
-        <v>3.5028998317976345E-5</v>
+        <f t="shared" si="35"/>
+        <v>2.2266867475861929E-5</v>
       </c>
       <c r="K97" s="1">
-        <f t="shared" si="25"/>
-        <v>3065</v>
+        <f t="shared" si="36"/>
+        <v>4409</v>
       </c>
       <c r="L97" s="2">
-        <f t="shared" si="28"/>
-        <v>7.1869494290375204</v>
+        <f t="shared" si="37"/>
+        <v>5.880698571104559</v>
       </c>
     </row>
     <row r="98" spans="2:12">
       <c r="B98" s="2">
-        <f t="shared" si="26"/>
-        <v>6579.3322465757356</v>
+        <f t="shared" si="24"/>
+        <v>8058.4218776147509</v>
       </c>
       <c r="C98" s="1">
+        <f t="shared" si="28"/>
+        <v>94</v>
+      </c>
+      <c r="D98" s="1">
         <f t="shared" si="29"/>
-        <v>94</v>
-      </c>
-      <c r="D98" s="1">
-        <f t="shared" si="19"/>
-        <v>822</v>
+        <v>1184</v>
       </c>
       <c r="E98" s="1">
-        <f t="shared" si="27"/>
-        <v>3289</v>
+        <f t="shared" si="30"/>
+        <v>4737</v>
       </c>
       <c r="F98" s="4">
-        <f t="shared" si="20"/>
-        <v>3.7997777073823022E-5</v>
+        <f t="shared" si="31"/>
+        <v>3.1023444018793248E-5</v>
       </c>
       <c r="G98" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12497468879580392</v>
+        <f t="shared" si="32"/>
+        <v>0.14695805431702361</v>
       </c>
       <c r="H98" s="5">
-        <f t="shared" si="22"/>
-        <v>5511</v>
+        <f t="shared" si="33"/>
+        <v>6480</v>
       </c>
       <c r="I98" s="2">
-        <f t="shared" si="23"/>
-        <v>6579.7904191616763</v>
+        <f t="shared" si="34"/>
+        <v>8059.479166666667</v>
       </c>
       <c r="J98" s="8">
-        <f t="shared" si="24"/>
-        <v>6.9638159127638488E-5</v>
+        <f t="shared" si="35"/>
+        <v>1.3120299085511711E-4</v>
       </c>
       <c r="K98" s="1">
-        <f t="shared" si="25"/>
-        <v>3289</v>
+        <f t="shared" si="36"/>
+        <v>4737</v>
       </c>
       <c r="L98" s="2">
-        <f t="shared" si="28"/>
-        <v>6.7023411371237458</v>
+        <f t="shared" si="37"/>
+        <v>5.4718176060797976</v>
       </c>
     </row>
     <row r="99" spans="2:12">
       <c r="B99" s="2">
-        <f t="shared" si="26"/>
-        <v>7054.8023107187037</v>
+        <f t="shared" si="24"/>
+        <v>8659.6432336005801</v>
       </c>
       <c r="C99" s="1">
+        <f t="shared" si="28"/>
+        <v>95</v>
+      </c>
+      <c r="D99" s="1">
         <f t="shared" si="29"/>
-        <v>95</v>
-      </c>
-      <c r="D99" s="1">
-        <f t="shared" si="19"/>
-        <v>881</v>
+        <v>1273</v>
       </c>
       <c r="E99" s="1">
-        <f t="shared" si="27"/>
-        <v>3525</v>
+        <f t="shared" si="30"/>
+        <v>5093</v>
       </c>
       <c r="F99" s="4">
-        <f t="shared" si="20"/>
-        <v>3.543685407316983E-5</v>
+        <f t="shared" si="31"/>
+        <v>2.8869549617236699E-5</v>
       </c>
       <c r="G99" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12491491060792365</v>
+        <f t="shared" si="32"/>
+        <v>0.1470326162005865</v>
       </c>
       <c r="H99" s="5">
-        <f t="shared" si="22"/>
-        <v>5508</v>
+        <f t="shared" si="33"/>
+        <v>6484</v>
       </c>
       <c r="I99" s="2">
-        <f t="shared" si="23"/>
-        <v>7055.7598039215691</v>
+        <f t="shared" si="34"/>
+        <v>8659.8280382479952</v>
       </c>
       <c r="J99" s="8">
-        <f t="shared" si="24"/>
-        <v>1.3572218762392119E-4</v>
+        <f t="shared" si="35"/>
+        <v>2.1340907752298577E-5</v>
       </c>
       <c r="K99" s="1">
-        <f t="shared" si="25"/>
-        <v>3525</v>
+        <f t="shared" si="36"/>
+        <v>5093</v>
       </c>
       <c r="L99" s="2">
-        <f t="shared" si="28"/>
-        <v>6.2502127659574471</v>
+        <f t="shared" si="37"/>
+        <v>5.0924798743373261</v>
       </c>
     </row>
     <row r="100" spans="2:12">
       <c r="B100" s="2">
-        <f t="shared" si="26"/>
-        <v>7564.6332755463545</v>
+        <f t="shared" si="24"/>
+        <v>9305.7204092969096</v>
       </c>
       <c r="C100" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>96</v>
       </c>
       <c r="D100" s="1">
-        <f t="shared" si="19"/>
-        <v>945</v>
+        <f t="shared" ref="D100:D101" si="38">INT((B100/1.7-1)/4)</f>
+        <v>1368</v>
       </c>
       <c r="E100" s="1">
-        <f t="shared" si="27"/>
-        <v>3781</v>
+        <f t="shared" ref="E100:E101" si="39">4*D100+1</f>
+        <v>5473</v>
       </c>
       <c r="F100" s="4">
-        <f t="shared" si="20"/>
-        <v>3.3048528711650442E-5</v>
+        <f t="shared" ref="F100:F101" si="40">1/B100/4</f>
+        <v>2.6865195708033168E-5</v>
       </c>
       <c r="G100" s="4">
-        <f t="shared" si="21"/>
-        <v>0.12495648705875032</v>
+        <f t="shared" ref="G100:G101" si="41">E100*F100</f>
+        <v>0.14703321611006553</v>
       </c>
       <c r="H100" s="5">
-        <f t="shared" si="22"/>
-        <v>5510</v>
+        <f t="shared" ref="H100:H101" si="42">INT(G100*_rate)</f>
+        <v>6484</v>
       </c>
       <c r="I100" s="2">
-        <f t="shared" si="23"/>
-        <v>7565.4310344827591</v>
+        <f t="shared" ref="I100:I101" si="43">E100/H100/4*_rate</f>
+        <v>9305.9569710055512</v>
       </c>
       <c r="J100" s="8">
-        <f t="shared" si="24"/>
-        <v>1.054590364588659E-4</v>
+        <f t="shared" ref="J100:J101" si="44">(I100/B100-1)</f>
+        <v>2.5421106398804127E-5</v>
       </c>
       <c r="K100" s="1">
-        <f t="shared" si="25"/>
-        <v>3781</v>
+        <f t="shared" ref="K100:K101" si="45">4*I100*H100/_rate</f>
+        <v>5472.9999999999991</v>
       </c>
       <c r="L100" s="2">
-        <f t="shared" si="28"/>
-        <v>5.8291457286432165</v>
+        <f t="shared" ref="L100:L101" si="46">4*H100/K100</f>
+        <v>4.738900054814545</v>
       </c>
     </row>
     <row r="101" spans="2:12">
       <c r="B101" s="2">
-        <f t="shared" si="26"/>
-        <v>8111.3083078969421</v>
+        <f t="shared" si="24"/>
+        <v>9999.9999999999127</v>
       </c>
       <c r="C101" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>97</v>
       </c>
       <c r="D101" s="1">
-        <f t="shared" si="19"/>
-        <v>1013</v>
+        <f t="shared" si="38"/>
+        <v>1470</v>
       </c>
       <c r="E101" s="1">
-        <f t="shared" si="27"/>
-        <v>4053</v>
+        <f t="shared" si="39"/>
+        <v>5881</v>
       </c>
       <c r="F101" s="4">
-        <f t="shared" si="20"/>
-        <v>3.0821168486051386E-5</v>
+        <f t="shared" si="40"/>
+        <v>2.5000000000000218E-5</v>
       </c>
       <c r="G101" s="4">
-        <f t="shared" ref="G101:G104" si="30">E101*F101</f>
-        <v>0.12491819587396627</v>
+        <f t="shared" si="41"/>
+        <v>0.14702500000000129</v>
       </c>
       <c r="H101" s="5">
-        <f t="shared" ref="H101:H104" si="31">INT(G101*_rate)</f>
-        <v>5508</v>
+        <f t="shared" si="42"/>
+        <v>6483</v>
       </c>
       <c r="I101" s="2">
-        <f t="shared" ref="I101:I104" si="32">E101/H101/4*_rate</f>
-        <v>8112.6225490196075</v>
+        <f t="shared" si="43"/>
+        <v>10001.237852845905</v>
       </c>
       <c r="J101" s="8">
-        <f t="shared" ref="J101:J104" si="33">(I101/B101-1)</f>
-        <v>1.6202578829194181E-4</v>
+        <f t="shared" si="44"/>
+        <v>1.2378528459922045E-4</v>
       </c>
       <c r="K101" s="1">
-        <f t="shared" si="25"/>
-        <v>4053</v>
+        <f t="shared" si="45"/>
+        <v>5881</v>
       </c>
       <c r="L101" s="2">
-        <f t="shared" si="28"/>
-        <v>5.4359733530717991</v>
-      </c>
-    </row>
-    <row r="102" spans="2:12">
-      <c r="B102" s="2">
-        <f t="shared" si="26"/>
-        <v>8697.4900261779112</v>
-      </c>
-      <c r="C102" s="1">
-        <f t="shared" si="29"/>
-        <v>98</v>
-      </c>
-      <c r="D102" s="1">
-        <f t="shared" si="19"/>
-        <v>1086</v>
-      </c>
-      <c r="E102" s="1">
-        <f t="shared" si="27"/>
-        <v>4345</v>
-      </c>
-      <c r="F102" s="4">
-        <f t="shared" si="20"/>
-        <v>2.8743924884943137E-5</v>
-      </c>
-      <c r="G102" s="4">
-        <f t="shared" si="30"/>
-        <v>0.12489235362507793</v>
-      </c>
-      <c r="H102" s="5">
-        <f t="shared" si="31"/>
-        <v>5507</v>
-      </c>
-      <c r="I102" s="2">
-        <f t="shared" si="32"/>
-        <v>8698.6789540584705</v>
-      </c>
-      <c r="J102" s="8">
-        <f t="shared" si="33"/>
-        <v>1.3669781476965959E-4</v>
-      </c>
-      <c r="K102" s="1">
-        <f t="shared" si="25"/>
-        <v>4345</v>
-      </c>
-      <c r="L102" s="2">
-        <f t="shared" si="28"/>
-        <v>5.0697353279631763</v>
-      </c>
-    </row>
-    <row r="103" spans="2:12">
-      <c r="B103" s="2">
-        <f t="shared" si="26"/>
-        <v>9326.0334688322837</v>
-      </c>
-      <c r="C103" s="1">
-        <f t="shared" si="29"/>
-        <v>99</v>
-      </c>
-      <c r="D103" s="1">
-        <f t="shared" si="19"/>
-        <v>1165</v>
-      </c>
-      <c r="E103" s="1">
-        <f t="shared" si="27"/>
-        <v>4661</v>
-      </c>
-      <c r="F103" s="4">
-        <f t="shared" si="20"/>
-        <v>2.6806680550257835E-5</v>
-      </c>
-      <c r="G103" s="4">
-        <f t="shared" si="30"/>
-        <v>0.12494593804475176</v>
-      </c>
-      <c r="H103" s="5">
-        <f t="shared" si="31"/>
-        <v>5510</v>
-      </c>
-      <c r="I103" s="2">
-        <f t="shared" si="32"/>
-        <v>9326.2295825771325</v>
-      </c>
-      <c r="J103" s="8">
-        <f t="shared" si="33"/>
-        <v>2.1028634038744443E-5</v>
-      </c>
-      <c r="K103" s="1">
-        <f t="shared" si="25"/>
-        <v>4661</v>
-      </c>
-      <c r="L103" s="2">
-        <f t="shared" si="28"/>
-        <v>4.7285990130873206</v>
-      </c>
-    </row>
-    <row r="104" spans="2:12">
-      <c r="B104" s="2">
-        <f t="shared" si="26"/>
-        <v>10000.000000000093</v>
-      </c>
-      <c r="C104" s="1">
-        <f t="shared" si="29"/>
-        <v>100</v>
-      </c>
-      <c r="D104" s="1">
-        <f t="shared" si="19"/>
-        <v>1249</v>
-      </c>
-      <c r="E104" s="1">
-        <f t="shared" si="27"/>
-        <v>4997</v>
-      </c>
-      <c r="F104" s="4">
-        <f t="shared" si="20"/>
-        <v>2.4999999999999767E-5</v>
-      </c>
-      <c r="G104" s="4">
-        <f t="shared" si="30"/>
-        <v>0.12492499999999884</v>
-      </c>
-      <c r="H104" s="5">
-        <f t="shared" si="31"/>
-        <v>5509</v>
-      </c>
-      <c r="I104" s="2">
-        <f t="shared" si="32"/>
-        <v>10000.349428208387</v>
-      </c>
-      <c r="J104" s="8">
-        <f t="shared" si="33"/>
-        <v>3.4942820829275689E-5</v>
-      </c>
-      <c r="K104" s="1">
-        <f t="shared" si="25"/>
-        <v>4997</v>
-      </c>
-      <c r="L104" s="2">
-        <f t="shared" si="28"/>
-        <v>4.4098459075445264</v>
+        <f t="shared" si="46"/>
+        <v>4.4094541744601257</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>

--- a/bridgeCalc.xlsx
+++ b/bridgeCalc.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="fourCellsChart" sheetId="8" r:id="rId1"/>
     <sheet name="fourCells" sheetId="6" r:id="rId2"/>
+    <sheet name="AvgCos" sheetId="9" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_mult">fourCells!$A$9</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>N</t>
   </si>
@@ -117,6 +118,15 @@
   </si>
   <si>
     <t>Sample</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>cosine</t>
+  </si>
+  <si>
+    <t>average</t>
   </si>
 </sst>
 </file>
@@ -1471,11 +1481,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2083455384"/>
-        <c:axId val="2116245992"/>
+        <c:axId val="2146344920"/>
+        <c:axId val="2146347944"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="2083455384"/>
+        <c:axId val="2146344920"/>
         <c:scaling>
           <c:logBase val="10.0"/>
           <c:orientation val="minMax"/>
@@ -1490,14 +1500,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2116245992"/>
+        <c:crossAx val="2146347944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10.0"/>
         <c:minorUnit val="10.0"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2116245992"/>
+        <c:axId val="2146347944"/>
         <c:scaling>
           <c:logBase val="10.0"/>
           <c:orientation val="minMax"/>
@@ -1512,7 +1522,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2083455384"/>
+        <c:crossAx val="2146344920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10.0"/>
@@ -1869,11 +1879,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="2124536296"/>
-        <c:axId val="2125192216"/>
+        <c:axId val="2147062088"/>
+        <c:axId val="2147065112"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2124536296"/>
+        <c:axId val="2147062088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1882,7 +1892,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2125192216"/>
+        <c:crossAx val="2147065112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1890,7 +1900,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2125192216"/>
+        <c:axId val="2147065112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1901,7 +1911,434 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2124536296"/>
+        <c:crossAx val="2147062088"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="1.0" l="0.75" r="0.75" t="1.0" header="0.5" footer="0.5"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="118"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="18"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.236152601323608"/>
+                  <c:y val="-0.0610396436177488"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>AvgCos!$D$7:$D$106</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>0.999506560365732</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99556196460308</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.987688340595138</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.975916761938747</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.960293685676943</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.940880768954225</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.917754625683981</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.891006524188368</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.860742027003944</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.827080574274562</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.79015501237569</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.75011106963046</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.707106781186548</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.661311865323652</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.612907053652977</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.562083377852131</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.509041415750371</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.453990499739547</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.39714789063478</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.338737920245291</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.278991106039229</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.218143241396543</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.156434465040231</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.0941083133185145</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.0314107590781284</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.0314107590781283</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.0941083133185144</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.156434465040231</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.218143241396542</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.278991106039229</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.338737920245291</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.39714789063478</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.453990499739547</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.509041415750371</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.56208337785213</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.612907053652976</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.661311865323652</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.707106781186547</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.75011106963046</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.79015501237569</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.827080574274562</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.860742027003943</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.891006524188368</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-0.917754625683981</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-0.940880768954225</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-0.960293685676943</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-0.975916761938747</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-0.987688340595138</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-0.99556196460308</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-0.999506560365732</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-0.999506560365732</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-0.99556196460308</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-0.987688340595138</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-0.975916761938747</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-0.960293685676943</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-0.940880768954225</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-0.917754625683981</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-0.891006524188368</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-0.860742027003944</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-0.827080574274562</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-0.79015501237569</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-0.75011106963046</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-0.707106781186548</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-0.661311865323652</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-0.612907053652976</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-0.562083377852131</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-0.509041415750371</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-0.453990499739547</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-0.39714789063478</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-0.338737920245292</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-0.27899110603923</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-0.218143241396543</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.156434465040231</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-0.0941083133185148</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.0314107590781283</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.0314107590781279</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.0941083133185145</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.156434465040231</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.218143241396543</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.278991106039229</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.338737920245292</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.39714789063478</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.453990499739547</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.509041415750371</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.562083377852131</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.612907053652976</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.661311865323652</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.707106781186547</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.750111069630459</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.79015501237569</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.827080574274562</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.860742027003944</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.891006524188368</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.917754625683981</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.940880768954225</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.960293685676943</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.975916761938747</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.987688340595138</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.99556196460308</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.999506560365732</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="2146463160"/>
+        <c:axId val="2061631704"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2146463160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2061631704"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2061631704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1.0"/>
+          <c:min val="-1.0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2146463160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1971,6 +2408,41 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>863600</xdr:colOff>
       <xdr:row>28</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1054100</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2306,7 +2778,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2314,7 +2786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.5" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="9.5" style="1"/>
@@ -6903,6 +7375,1065 @@
         <v>4.4094541744601257</v>
       </c>
     </row>
+    <row r="103" spans="2:12">
+      <c r="H103" s="5">
+        <f>MAX(H5:H101)</f>
+        <v>6484</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12">
+      <c r="H104" s="5">
+        <f>MIN(H5:H101)</f>
+        <v>3846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C6:E107"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="5" max="5" width="12.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="3:5">
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5">
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <f>COS(C7/100*2*PI())</f>
+        <v>0.9995065603657316</v>
+      </c>
+      <c r="E7">
+        <f>AVERAGE(D7:D106)</f>
+        <v>-2.8865798640254071E-17</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5">
+      <c r="C8">
+        <f>C7+1</f>
+        <v>1.5</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="D8:D71" si="0">COS(C8/100*2*PI())</f>
+        <v>0.99556196460308</v>
+      </c>
+      <c r="E8">
+        <f>AVERAGE(D7:D107)</f>
+        <v>9.8961045580765218E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5">
+      <c r="C9">
+        <f t="shared" ref="C9:C72" si="1">C8+1</f>
+        <v>2.5</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>0.98768834059513777</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5">
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>0.97591676193874743</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5">
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>4.5</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>0.96029368567694307</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5">
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0.94088076895422545</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5">
+      <c r="C13">
+        <f t="shared" si="1"/>
+        <v>6.5</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>0.91775462568398114</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5">
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>0.8910065241883679</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5">
+      <c r="C15">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>0.86074202700394364</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5">
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>0.82708057427456183</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4">
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>0.79015501237569041</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4">
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>0.75011106963045959</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4">
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>0.70710678118654757</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4">
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>13.5</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>0.66131186532365183</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4">
+      <c r="C21">
+        <f t="shared" si="1"/>
+        <v>14.5</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>0.6129070536529766</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4">
+      <c r="C22">
+        <f t="shared" si="1"/>
+        <v>15.5</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>0.56208337785213058</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4">
+      <c r="C23">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>0.50904141575037121</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4">
+      <c r="C24">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>0.4539904997395468</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4">
+      <c r="C25">
+        <f t="shared" si="1"/>
+        <v>18.5</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>0.39714789063478056</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4">
+      <c r="C26">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>0.33873792024529148</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27">
+        <f t="shared" si="1"/>
+        <v>20.5</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>0.2789911060392295</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4">
+      <c r="C28">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>0.2181432413965427</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4">
+      <c r="C29">
+        <f t="shared" si="1"/>
+        <v>22.5</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="0"/>
+        <v>0.15643446504023092</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30">
+        <f t="shared" si="1"/>
+        <v>23.5</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>9.4108313318514505E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4">
+      <c r="C31">
+        <f t="shared" si="1"/>
+        <v>24.5</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="0"/>
+        <v>3.1410759078128396E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4">
+      <c r="C32">
+        <f t="shared" si="1"/>
+        <v>25.5</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="0"/>
+        <v>-3.1410759078128278E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33">
+        <f t="shared" si="1"/>
+        <v>26.5</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="0"/>
+        <v>-9.4108313318514381E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>-0.15643446504023104</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35">
+        <f t="shared" si="1"/>
+        <v>28.5</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>-0.21814324139654234</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4">
+      <c r="C36">
+        <f t="shared" si="1"/>
+        <v>29.5</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="0"/>
+        <v>-0.27899110603922916</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4">
+      <c r="C37">
+        <f t="shared" si="1"/>
+        <v>30.5</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="0"/>
+        <v>-0.33873792024529137</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4">
+      <c r="C38">
+        <f t="shared" si="1"/>
+        <v>31.5</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="0"/>
+        <v>-0.39714789063478045</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4">
+      <c r="C39">
+        <f t="shared" si="1"/>
+        <v>32.5</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="0"/>
+        <v>-0.45399049973954669</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4">
+      <c r="C40">
+        <f t="shared" si="1"/>
+        <v>33.5</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="0"/>
+        <v>-0.50904141575037132</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4">
+      <c r="C41">
+        <f t="shared" si="1"/>
+        <v>34.5</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="0"/>
+        <v>-0.56208337785213036</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4">
+      <c r="C42">
+        <f t="shared" si="1"/>
+        <v>35.5</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="0"/>
+        <v>-0.61290705365297626</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4">
+      <c r="C43">
+        <f t="shared" si="1"/>
+        <v>36.5</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="0"/>
+        <v>-0.66131186532365172</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4">
+      <c r="C44">
+        <f t="shared" si="1"/>
+        <v>37.5</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="0"/>
+        <v>-0.70710678118654746</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4">
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>38.5</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="0"/>
+        <v>-0.75011106963045959</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4">
+      <c r="C46">
+        <f t="shared" si="1"/>
+        <v>39.5</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="0"/>
+        <v>-0.79015501237569041</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4">
+      <c r="C47">
+        <f t="shared" si="1"/>
+        <v>40.5</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="0"/>
+        <v>-0.82708057427456194</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4">
+      <c r="C48">
+        <f t="shared" si="1"/>
+        <v>41.5</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="0"/>
+        <v>-0.86074202700394353</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4">
+      <c r="C49">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="0"/>
+        <v>-0.89100652418836779</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4">
+      <c r="C50">
+        <f t="shared" si="1"/>
+        <v>43.5</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="0"/>
+        <v>-0.91775462568398114</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4">
+      <c r="C51">
+        <f t="shared" si="1"/>
+        <v>44.5</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="0"/>
+        <v>-0.94088076895422545</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4">
+      <c r="C52">
+        <f t="shared" si="1"/>
+        <v>45.5</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="0"/>
+        <v>-0.96029368567694307</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4">
+      <c r="C53">
+        <f t="shared" si="1"/>
+        <v>46.5</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="0"/>
+        <v>-0.97591676193874743</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4">
+      <c r="C54">
+        <f t="shared" si="1"/>
+        <v>47.5</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="0"/>
+        <v>-0.98768834059513766</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4">
+      <c r="C55">
+        <f t="shared" si="1"/>
+        <v>48.5</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>-0.99556196460308</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4">
+      <c r="C56">
+        <f t="shared" si="1"/>
+        <v>49.5</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="0"/>
+        <v>-0.9995065603657316</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4">
+      <c r="C57">
+        <f t="shared" si="1"/>
+        <v>50.5</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="0"/>
+        <v>-0.9995065603657316</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4">
+      <c r="C58">
+        <f t="shared" si="1"/>
+        <v>51.5</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>-0.99556196460308</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4">
+      <c r="C59">
+        <f t="shared" si="1"/>
+        <v>52.5</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="0"/>
+        <v>-0.98768834059513777</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4">
+      <c r="C60">
+        <f t="shared" si="1"/>
+        <v>53.5</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="0"/>
+        <v>-0.97591676193874743</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4">
+      <c r="C61">
+        <f t="shared" si="1"/>
+        <v>54.5</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="0"/>
+        <v>-0.96029368567694307</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4">
+      <c r="C62">
+        <f t="shared" si="1"/>
+        <v>55.5</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="0"/>
+        <v>-0.94088076895422545</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4">
+      <c r="C63">
+        <f t="shared" si="1"/>
+        <v>56.5</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="0"/>
+        <v>-0.91775462568398136</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4">
+      <c r="C64">
+        <f t="shared" si="1"/>
+        <v>57.5</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>-0.89100652418836812</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4">
+      <c r="C65">
+        <f t="shared" si="1"/>
+        <v>58.5</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="0"/>
+        <v>-0.86074202700394387</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4">
+      <c r="C66">
+        <f t="shared" si="1"/>
+        <v>59.5</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="0"/>
+        <v>-0.82708057427456205</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4">
+      <c r="C67">
+        <f t="shared" si="1"/>
+        <v>60.5</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="0"/>
+        <v>-0.79015501237569052</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4">
+      <c r="C68">
+        <f t="shared" si="1"/>
+        <v>61.5</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="0"/>
+        <v>-0.7501110696304597</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4">
+      <c r="C69">
+        <f t="shared" si="1"/>
+        <v>62.5</v>
+      </c>
+      <c r="D69">
+        <f t="shared" si="0"/>
+        <v>-0.70710678118654768</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4">
+      <c r="C70">
+        <f t="shared" si="1"/>
+        <v>63.5</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="0"/>
+        <v>-0.66131186532365194</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4">
+      <c r="C71">
+        <f t="shared" si="1"/>
+        <v>64.5</v>
+      </c>
+      <c r="D71">
+        <f t="shared" si="0"/>
+        <v>-0.61290705365297649</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4">
+      <c r="C72">
+        <f t="shared" si="1"/>
+        <v>65.5</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ref="D72:D107" si="2">COS(C72/100*2*PI())</f>
+        <v>-0.56208337785213092</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4">
+      <c r="C73">
+        <f t="shared" ref="C73:C136" si="3">C72+1</f>
+        <v>66.5</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="2"/>
+        <v>-0.5090414157503711</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4">
+      <c r="C74">
+        <f t="shared" si="3"/>
+        <v>67.5</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="2"/>
+        <v>-0.45399049973954692</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4">
+      <c r="C75">
+        <f t="shared" si="3"/>
+        <v>68.5</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="2"/>
+        <v>-0.39714789063478029</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4">
+      <c r="C76">
+        <f t="shared" si="3"/>
+        <v>69.5</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="2"/>
+        <v>-0.3387379202452922</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4">
+      <c r="C77">
+        <f t="shared" si="3"/>
+        <v>70.5</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="2"/>
+        <v>-0.27899110603922961</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4">
+      <c r="C78">
+        <f t="shared" si="3"/>
+        <v>71.5</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="2"/>
+        <v>-0.21814324139654323</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4">
+      <c r="C79">
+        <f t="shared" si="3"/>
+        <v>72.5</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="2"/>
+        <v>-0.15643446504023104</v>
+      </c>
+    </row>
+    <row r="80" spans="3:4">
+      <c r="C80">
+        <f t="shared" si="3"/>
+        <v>73.5</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="2"/>
+        <v>-9.4108313318514852E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="3:4">
+      <c r="C81">
+        <f t="shared" si="3"/>
+        <v>74.5</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="2"/>
+        <v>-3.1410759078128299E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="3:4">
+      <c r="C82">
+        <f t="shared" si="3"/>
+        <v>75.5</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="2"/>
+        <v>3.1410759078127931E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="3:4">
+      <c r="C83">
+        <f t="shared" si="3"/>
+        <v>76.5</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="2"/>
+        <v>9.4108313318514492E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="3:4">
+      <c r="C84">
+        <f t="shared" si="3"/>
+        <v>77.5</v>
+      </c>
+      <c r="D84">
+        <f t="shared" si="2"/>
+        <v>0.15643446504023067</v>
+      </c>
+    </row>
+    <row r="85" spans="3:4">
+      <c r="C85">
+        <f t="shared" si="3"/>
+        <v>78.5</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="2"/>
+        <v>0.2181432413965429</v>
+      </c>
+    </row>
+    <row r="86" spans="3:4">
+      <c r="C86">
+        <f t="shared" si="3"/>
+        <v>79.5</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="2"/>
+        <v>0.27899110603922922</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4">
+      <c r="C87">
+        <f t="shared" si="3"/>
+        <v>80.5</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="2"/>
+        <v>0.33873792024529187</v>
+      </c>
+    </row>
+    <row r="88" spans="3:4">
+      <c r="C88">
+        <f t="shared" si="3"/>
+        <v>81.5</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="2"/>
+        <v>0.39714789063477995</v>
+      </c>
+    </row>
+    <row r="89" spans="3:4">
+      <c r="C89">
+        <f t="shared" si="3"/>
+        <v>82.5</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="2"/>
+        <v>0.45399049973954664</v>
+      </c>
+    </row>
+    <row r="90" spans="3:4">
+      <c r="C90">
+        <f t="shared" si="3"/>
+        <v>83.5</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="2"/>
+        <v>0.50904141575037087</v>
+      </c>
+    </row>
+    <row r="91" spans="3:4">
+      <c r="C91">
+        <f t="shared" si="3"/>
+        <v>84.5</v>
+      </c>
+      <c r="D91">
+        <f t="shared" si="2"/>
+        <v>0.56208337785213058</v>
+      </c>
+    </row>
+    <row r="92" spans="3:4">
+      <c r="C92">
+        <f t="shared" si="3"/>
+        <v>85.5</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="2"/>
+        <v>0.61290705365297615</v>
+      </c>
+    </row>
+    <row r="93" spans="3:4">
+      <c r="C93">
+        <f t="shared" si="3"/>
+        <v>86.5</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="2"/>
+        <v>0.66131186532365194</v>
+      </c>
+    </row>
+    <row r="94" spans="3:4">
+      <c r="C94">
+        <f t="shared" si="3"/>
+        <v>87.5</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="2"/>
+        <v>0.70710678118654735</v>
+      </c>
+    </row>
+    <row r="95" spans="3:4">
+      <c r="C95">
+        <f t="shared" si="3"/>
+        <v>88.5</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="2"/>
+        <v>0.75011106963045915</v>
+      </c>
+    </row>
+    <row r="96" spans="3:4">
+      <c r="C96">
+        <f t="shared" si="3"/>
+        <v>89.5</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="2"/>
+        <v>0.7901550123756903</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4">
+      <c r="C97">
+        <f t="shared" si="3"/>
+        <v>90.5</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="2"/>
+        <v>0.82708057427456161</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4">
+      <c r="C98">
+        <f t="shared" si="3"/>
+        <v>91.5</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="2"/>
+        <v>0.86074202700394375</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4">
+      <c r="C99">
+        <f t="shared" si="3"/>
+        <v>92.5</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="2"/>
+        <v>0.89100652418836779</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4">
+      <c r="C100">
+        <f t="shared" si="3"/>
+        <v>93.5</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="2"/>
+        <v>0.91775462568398125</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4">
+      <c r="C101">
+        <f t="shared" si="3"/>
+        <v>94.5</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="2"/>
+        <v>0.94088076895422512</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4">
+      <c r="C102">
+        <f t="shared" si="3"/>
+        <v>95.5</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="2"/>
+        <v>0.96029368567694295</v>
+      </c>
+    </row>
+    <row r="103" spans="3:4">
+      <c r="C103">
+        <f t="shared" si="3"/>
+        <v>96.5</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="2"/>
+        <v>0.97591676193874721</v>
+      </c>
+    </row>
+    <row r="104" spans="3:4">
+      <c r="C104">
+        <f t="shared" si="3"/>
+        <v>97.5</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="2"/>
+        <v>0.98768834059513766</v>
+      </c>
+    </row>
+    <row r="105" spans="3:4">
+      <c r="C105">
+        <f t="shared" si="3"/>
+        <v>98.5</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="2"/>
+        <v>0.99556196460308</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4">
+      <c r="C106">
+        <f t="shared" si="3"/>
+        <v>99.5</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="2"/>
+        <v>0.9995065603657316</v>
+      </c>
+    </row>
+    <row r="107" spans="3:4">
+      <c r="C107">
+        <f t="shared" ref="C107" si="4">C106+1</f>
+        <v>100.5</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="2"/>
+        <v>0.9995065603657316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
